--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2730A97-E963-4DD4-B725-29CB53247AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF14A11E-555C-42F6-8CE0-F8DEADAEFFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="620" windowWidth="33550" windowHeight="13040" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="130" yWindow="150" windowWidth="31410" windowHeight="13490" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="57">
   <si>
     <t>AssociateName</t>
   </si>
@@ -84,111 +84,114 @@
     <t>ReviewYear</t>
   </si>
   <si>
+    <t>Connie Serrano</t>
+  </si>
+  <si>
+    <t>Charles</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>Tara Pitula</t>
+  </si>
+  <si>
+    <t>Katie</t>
+  </si>
+  <si>
+    <t>Thomas Gordon</t>
+  </si>
+  <si>
+    <t>ManagerName</t>
+  </si>
+  <si>
+    <t>ManagerEmail</t>
+  </si>
+  <si>
+    <t>AssociateEmail</t>
+  </si>
+  <si>
+    <t>Seshu Chivukula</t>
+  </si>
+  <si>
+    <t>Charles Bumgardner</t>
+  </si>
+  <si>
+    <t>Charles.Bumgardner@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>Seshu.Chivukula@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>Connie.Serrano@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>TyKee Walmsley</t>
+  </si>
+  <si>
+    <t>TyKee.Walmsley@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>Kelly Acevedo</t>
+  </si>
+  <si>
+    <t>Kelly.Acevedo@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>Tyler Rainford</t>
+  </si>
+  <si>
+    <t>Tyler.Rainford@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>Marnia Vance</t>
+  </si>
+  <si>
+    <t>Marnia.Vance@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>Michael Chen</t>
+  </si>
+  <si>
+    <t>Michael.Chen@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>Selena Hammond</t>
+  </si>
+  <si>
+    <t>Katie Pinchac</t>
+  </si>
+  <si>
+    <t>katie.pinchac@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>Selena.Hammond@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>Zachary Miller</t>
+  </si>
+  <si>
+    <t>Zachary.Miller@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>Deja Patterson</t>
+  </si>
+  <si>
+    <t>Deja.Patterson@lplfinancial.com</t>
+  </si>
+  <si>
     <t>Raven Ingram</t>
   </si>
   <si>
-    <t>Katie</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>ManagerName</t>
-  </si>
-  <si>
-    <t>ManagerEmail</t>
-  </si>
-  <si>
-    <t>AssociateEmail</t>
-  </si>
-  <si>
-    <t>Seshu Chivukula</t>
-  </si>
-  <si>
-    <t>Charles</t>
-  </si>
-  <si>
-    <t>Charles Bumgardner</t>
-  </si>
-  <si>
-    <t>Charles.Bumgardner@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Seshu.Chivukula@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Connie Serrano</t>
-  </si>
-  <si>
-    <t>Connie.Serrano@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>TyKee Walmsley</t>
-  </si>
-  <si>
-    <t>TyKee.Walmsley@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Kelly Acevedo</t>
-  </si>
-  <si>
-    <t>Kelly.Acevedo@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Tyler Rainford</t>
-  </si>
-  <si>
-    <t>Tyler.Rainford@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Marnia Vance</t>
-  </si>
-  <si>
-    <t>Marnia.Vance@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Michael Chen</t>
-  </si>
-  <si>
-    <t>Michael.Chen@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Selena Hammond</t>
-  </si>
-  <si>
-    <t>Katie Pinchac</t>
-  </si>
-  <si>
-    <t>katie.pinchac@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Selena.Hammond@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Zachary Miller</t>
-  </si>
-  <si>
-    <t>Zachary.Miller@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Deja Patterson</t>
-  </si>
-  <si>
-    <t>Deja.Patterson@lplfinancial.com</t>
-  </si>
-  <si>
     <t>Raven.Ingram@lplfinancial.com</t>
   </si>
   <si>
-    <t>Tara Pitula</t>
-  </si>
-  <si>
     <t>Tara.Pitula@lplfinancial.com</t>
   </si>
   <si>
@@ -202,9 +205,6 @@
   </si>
   <si>
     <t>Breanna.Stringfellow@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Thomas Gordon</t>
   </si>
   <si>
     <t>Thomas.Gordon@lplfinancial.com</t>
@@ -259,7 +259,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -272,6 +272,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -319,8 +322,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O2" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:O2" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O8" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:O8" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -673,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -686,11 +689,11 @@
     <col min="8" max="8" width="31.1796875" customWidth="1"/>
     <col min="9" max="9" width="19.54296875" customWidth="1"/>
     <col min="10" max="10" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.81640625" customWidth="1"/>
-    <col min="12" max="12" width="17.81640625" customWidth="1"/>
+    <col min="11" max="11" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.1796875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.1796875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -748,22 +751,22 @@
         <v>16</v>
       </c>
       <c r="C2" s="5">
-        <v>46126</v>
+        <v>46111</v>
       </c>
       <c r="D2" s="1">
         <v>5</v>
       </c>
       <c r="E2" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H2" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1">
         <v>5</v>
@@ -775,15 +778,297 @@
         <v>18</v>
       </c>
       <c r="L2" s="1">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O2" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="5">
+        <v>46092</v>
+      </c>
+      <c r="D3" s="1">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1">
+        <v>30</v>
+      </c>
+      <c r="G3" s="1">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1">
+        <v>5</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="1">
+        <v>100</v>
+      </c>
+      <c r="M3" s="2">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="5">
+        <v>46100</v>
+      </c>
+      <c r="D4" s="1">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1">
+        <v>30</v>
+      </c>
+      <c r="G4" s="1">
+        <v>20</v>
+      </c>
+      <c r="H4" s="1">
+        <v>20</v>
+      </c>
+      <c r="I4" s="1">
+        <v>5</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="1">
+        <v>100</v>
+      </c>
+      <c r="M4" s="2">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="5">
+        <v>46093</v>
+      </c>
+      <c r="D5" s="1">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1">
+        <v>20</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20</v>
+      </c>
+      <c r="I5" s="1">
+        <v>5</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="1">
+        <v>80</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="5">
+        <v>46108</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1">
+        <v>20</v>
+      </c>
+      <c r="I6" s="1">
+        <v>5</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="1">
+        <v>90</v>
+      </c>
+      <c r="M6" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="5">
+        <v>46101</v>
+      </c>
+      <c r="D7" s="1">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1">
+        <v>20</v>
+      </c>
+      <c r="F7" s="1">
+        <v>30</v>
+      </c>
+      <c r="G7" s="1">
+        <v>20</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="1">
+        <v>5</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" s="1">
+        <v>100</v>
+      </c>
+      <c r="M7" s="6">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="5">
+        <v>46107</v>
+      </c>
+      <c r="D8" s="1">
+        <v>5</v>
+      </c>
+      <c r="E8" s="1">
+        <v>20</v>
+      </c>
+      <c r="F8" s="1">
+        <v>30</v>
+      </c>
+      <c r="G8" s="1">
+        <v>20</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="1">
+        <v>100</v>
+      </c>
+      <c r="M8" s="6">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -815,265 +1100,265 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
         <v>56</v>
@@ -1340,15 +1625,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
@@ -1359,6 +1635,15 @@
     <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1381,26 +1666,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF14A11E-555C-42F6-8CE0-F8DEADAEFFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F2FF37-1921-4B37-A7F2-210530B048F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="130" yWindow="150" windowWidth="31410" windowHeight="13490" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="5680" yWindow="350" windowWidth="21240" windowHeight="13490" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="58">
   <si>
     <t>AssociateName</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>Thomas.Gordon@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>April</t>
   </si>
 </sst>
 </file>
@@ -259,7 +262,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -274,8 +277,14 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -322,8 +331,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O8" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:O8" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O17" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:O17" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -676,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -968,7 +977,7 @@
       <c r="L6" s="1">
         <v>90</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="2">
         <v>0.9</v>
       </c>
       <c r="N6" s="1" t="s">
@@ -1015,7 +1024,7 @@
       <c r="L7" s="1">
         <v>100</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="2">
         <v>1</v>
       </c>
       <c r="N7" s="1" t="s">
@@ -1062,13 +1071,436 @@
       <c r="L8" s="1">
         <v>100</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="2">
         <v>1</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O8" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="5">
+        <v>46104</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1">
+        <v>20</v>
+      </c>
+      <c r="F9" s="1">
+        <v>30</v>
+      </c>
+      <c r="G9" s="1">
+        <v>20</v>
+      </c>
+      <c r="H9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="1">
+        <v>5</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="1">
+        <v>100</v>
+      </c>
+      <c r="M9" s="2">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="5">
+        <v>46119</v>
+      </c>
+      <c r="D10" s="1">
+        <v>5</v>
+      </c>
+      <c r="E10" s="1">
+        <v>20</v>
+      </c>
+      <c r="F10" s="1">
+        <v>30</v>
+      </c>
+      <c r="G10" s="1">
+        <v>20</v>
+      </c>
+      <c r="H10" s="1">
+        <v>15</v>
+      </c>
+      <c r="I10" s="1">
+        <v>5</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" s="1">
+        <v>95</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="5">
+        <v>46114</v>
+      </c>
+      <c r="D11" s="1">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1">
+        <v>20</v>
+      </c>
+      <c r="H11" s="1">
+        <v>10</v>
+      </c>
+      <c r="I11" s="1">
+        <v>5</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="1">
+        <v>80</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O11" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="5">
+        <v>46101</v>
+      </c>
+      <c r="D12" s="1">
+        <v>5</v>
+      </c>
+      <c r="E12" s="1">
+        <v>20</v>
+      </c>
+      <c r="F12" s="1">
+        <v>30</v>
+      </c>
+      <c r="G12" s="1">
+        <v>20</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="1">
+        <v>5</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="1">
+        <v>100</v>
+      </c>
+      <c r="M12" s="2">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="5">
+        <v>46100</v>
+      </c>
+      <c r="D13" s="1">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1">
+        <v>20</v>
+      </c>
+      <c r="F13" s="1">
+        <v>30</v>
+      </c>
+      <c r="G13" s="1">
+        <v>20</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="1">
+        <v>5</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" s="1">
+        <v>100</v>
+      </c>
+      <c r="M13" s="2">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="5">
+        <v>46094</v>
+      </c>
+      <c r="D14" s="1">
+        <v>5</v>
+      </c>
+      <c r="E14" s="1">
+        <v>20</v>
+      </c>
+      <c r="F14" s="1">
+        <v>30</v>
+      </c>
+      <c r="G14" s="1">
+        <v>20</v>
+      </c>
+      <c r="H14" s="1">
+        <v>15</v>
+      </c>
+      <c r="I14" s="1">
+        <v>5</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="1">
+        <v>95</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="5">
+        <v>46094</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5</v>
+      </c>
+      <c r="E15" s="1">
+        <v>20</v>
+      </c>
+      <c r="F15" s="1">
+        <v>30</v>
+      </c>
+      <c r="G15" s="1">
+        <v>20</v>
+      </c>
+      <c r="H15" s="1">
+        <v>20</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" s="1">
+        <v>100</v>
+      </c>
+      <c r="M15" s="2">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O15" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="5">
+        <v>46101</v>
+      </c>
+      <c r="D16" s="1">
+        <v>5</v>
+      </c>
+      <c r="E16" s="1">
+        <v>20</v>
+      </c>
+      <c r="F16" s="1">
+        <v>30</v>
+      </c>
+      <c r="G16" s="1">
+        <v>20</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="1">
+        <v>5</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" s="1">
+        <v>100</v>
+      </c>
+      <c r="M16" s="2">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O16" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="7">
+        <v>46113</v>
+      </c>
+      <c r="D17" s="6">
+        <v>5</v>
+      </c>
+      <c r="E17" s="6">
+        <v>20</v>
+      </c>
+      <c r="F17" s="6">
+        <v>30</v>
+      </c>
+      <c r="G17" s="6">
+        <v>20</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6">
+        <v>5</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="6">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="O17" s="6">
         <v>2026</v>
       </c>
     </row>
@@ -1374,6 +1806,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -1624,29 +2078,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1663,29 +2120,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F2FF37-1921-4B37-A7F2-210530B048F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F56F01CB-C0D8-4268-80DE-AFE9278C4E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5680" yWindow="350" windowWidth="21240" windowHeight="13490" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="1750" yWindow="460" windowWidth="26510" windowHeight="13490" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="58">
   <si>
     <t>AssociateName</t>
   </si>
@@ -108,6 +108,24 @@
     <t>Thomas Gordon</t>
   </si>
   <si>
+    <t>Deja Patterson</t>
+  </si>
+  <si>
+    <t>Marcus McDowell</t>
+  </si>
+  <si>
+    <t>Raven Ingram</t>
+  </si>
+  <si>
+    <t>Selena Hammond</t>
+  </si>
+  <si>
+    <t>Kelly Acevedo</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
     <t>ManagerName</t>
   </si>
   <si>
@@ -138,9 +156,6 @@
     <t>TyKee.Walmsley@lplfinancial.com</t>
   </si>
   <si>
-    <t>Kelly Acevedo</t>
-  </si>
-  <si>
     <t>Kelly.Acevedo@lplfinancial.com</t>
   </si>
   <si>
@@ -162,9 +177,6 @@
     <t>Michael.Chen@lplfinancial.com</t>
   </si>
   <si>
-    <t>Selena Hammond</t>
-  </si>
-  <si>
     <t>Katie Pinchac</t>
   </si>
   <si>
@@ -180,24 +192,15 @@
     <t>Zachary.Miller@lplfinancial.com</t>
   </si>
   <si>
-    <t>Deja Patterson</t>
-  </si>
-  <si>
     <t>Deja.Patterson@lplfinancial.com</t>
   </si>
   <si>
-    <t>Raven Ingram</t>
-  </si>
-  <si>
     <t>Raven.Ingram@lplfinancial.com</t>
   </si>
   <si>
     <t>Tara.Pitula@lplfinancial.com</t>
   </si>
   <si>
-    <t>Marcus McDowell</t>
-  </si>
-  <si>
     <t>Marcus.McDowell@lplfinancial.com</t>
   </si>
   <si>
@@ -208,9 +211,6 @@
   </si>
   <si>
     <t>Thomas.Gordon@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>April</t>
   </si>
 </sst>
 </file>
@@ -262,7 +262,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -277,14 +277,8 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -331,8 +325,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O17" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:O17" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O20" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:O20" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -685,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -698,11 +692,11 @@
     <col min="8" max="8" width="31.1796875" customWidth="1"/>
     <col min="9" max="9" width="19.54296875" customWidth="1"/>
     <col min="10" max="10" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.1796875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.1796875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -942,7 +936,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>21</v>
@@ -989,7 +983,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>21</v>
@@ -1036,7 +1030,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>21</v>
@@ -1083,7 +1077,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>21</v>
@@ -1130,7 +1124,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>16</v>
@@ -1169,7 +1163,7 @@
         <v>0.95</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="O10" s="1">
         <v>2026</v>
@@ -1216,7 +1210,7 @@
         <v>0.8</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="O11" s="1">
         <v>2026</v>
@@ -1318,7 +1312,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>21</v>
@@ -1365,7 +1359,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>21</v>
@@ -1412,7 +1406,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>21</v>
@@ -1457,50 +1451,191 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="6" t="s">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="5">
+        <v>46093</v>
+      </c>
+      <c r="D17" s="1">
+        <v>5</v>
+      </c>
+      <c r="E17" s="1">
+        <v>20</v>
+      </c>
+      <c r="F17" s="1">
+        <v>30</v>
+      </c>
+      <c r="G17" s="1">
+        <v>20</v>
+      </c>
+      <c r="H17" s="1">
+        <v>5</v>
+      </c>
+      <c r="I17" s="1">
+        <v>5</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" s="1">
+        <v>85</v>
+      </c>
+      <c r="M17" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O17" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="7">
-        <v>46113</v>
-      </c>
-      <c r="D17" s="6">
-        <v>5</v>
-      </c>
-      <c r="E17" s="6">
-        <v>20</v>
-      </c>
-      <c r="F17" s="6">
+      <c r="C18" s="5">
+        <v>46119</v>
+      </c>
+      <c r="D18" s="1">
+        <v>5</v>
+      </c>
+      <c r="E18" s="1">
+        <v>5</v>
+      </c>
+      <c r="F18" s="1">
         <v>30</v>
       </c>
-      <c r="G17" s="6">
-        <v>20</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0</v>
-      </c>
-      <c r="I17" s="6">
-        <v>5</v>
-      </c>
-      <c r="J17" s="6" t="s">
+      <c r="G18" s="1">
+        <v>20</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="1">
+        <v>5</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18" s="1">
+        <v>85</v>
+      </c>
+      <c r="M18" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O18" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="5">
+        <v>46120</v>
+      </c>
+      <c r="D19" s="1">
+        <v>5</v>
+      </c>
+      <c r="E19" s="1">
+        <v>20</v>
+      </c>
+      <c r="F19" s="1">
+        <v>25</v>
+      </c>
+      <c r="G19" s="1">
+        <v>15</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="1">
+        <v>5</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L17" s="6">
-        <v>0</v>
-      </c>
-      <c r="M17" s="8">
-        <v>0</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="O17" s="6">
+      <c r="K19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" s="1">
+        <v>90</v>
+      </c>
+      <c r="M19" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O19" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="5">
+        <v>46107</v>
+      </c>
+      <c r="D20" s="1">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1">
+        <v>20</v>
+      </c>
+      <c r="F20" s="1">
+        <v>30</v>
+      </c>
+      <c r="G20" s="1">
+        <v>20</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>5</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" s="1">
+        <v>85</v>
+      </c>
+      <c r="M20" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O20" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -1532,30 +1667,30 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1566,166 +1701,166 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1736,47 +1871,47 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -1787,13 +1922,13 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1806,15 +1941,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
@@ -1827,7 +1953,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -2078,32 +2204,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2120,4 +2247,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F56F01CB-C0D8-4268-80DE-AFE9278C4E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{802A1E98-F0A2-46EE-BF49-63C3E9C1EF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1750" yWindow="460" windowWidth="26510" windowHeight="13490" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="1110" yWindow="140" windowWidth="22240" windowHeight="13490" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="58">
   <si>
     <t>AssociateName</t>
   </si>
@@ -126,6 +126,12 @@
     <t>April</t>
   </si>
   <si>
+    <t>Marnia Vance</t>
+  </si>
+  <si>
+    <t>Michael Chen</t>
+  </si>
+  <si>
     <t>ManagerName</t>
   </si>
   <si>
@@ -165,13 +171,7 @@
     <t>Tyler.Rainford@lplfinancial.com</t>
   </si>
   <si>
-    <t>Marnia Vance</t>
-  </si>
-  <si>
     <t>Marnia.Vance@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Michael Chen</t>
   </si>
   <si>
     <t>Michael.Chen@lplfinancial.com</t>
@@ -325,8 +325,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O20" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:O20" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O28" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:O28" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -679,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -1488,7 +1488,7 @@
       <c r="L17" s="1">
         <v>85</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="2">
         <v>0.85</v>
       </c>
       <c r="N17" s="1" t="s">
@@ -1500,7 +1500,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
@@ -1535,7 +1535,7 @@
       <c r="L18" s="1">
         <v>85</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="2">
         <v>0.85</v>
       </c>
       <c r="N18" s="1" t="s">
@@ -1547,7 +1547,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>16</v>
@@ -1582,7 +1582,7 @@
       <c r="L19" s="1">
         <v>90</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="2">
         <v>0.9</v>
       </c>
       <c r="N19" s="1" t="s">
@@ -1629,13 +1629,389 @@
       <c r="L20" s="1">
         <v>85</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="2">
         <v>0.85</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O20" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="5">
+        <v>46101</v>
+      </c>
+      <c r="D21" s="1">
+        <v>5</v>
+      </c>
+      <c r="E21" s="1">
+        <v>20</v>
+      </c>
+      <c r="F21" s="1">
+        <v>30</v>
+      </c>
+      <c r="G21" s="1">
+        <v>20</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="1">
+        <v>5</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L21" s="1">
+        <v>100</v>
+      </c>
+      <c r="M21" s="6">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O21" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="5">
+        <v>46113</v>
+      </c>
+      <c r="D22" s="1">
+        <v>5</v>
+      </c>
+      <c r="E22" s="1">
+        <v>20</v>
+      </c>
+      <c r="F22" s="1">
+        <v>30</v>
+      </c>
+      <c r="G22" s="1">
+        <v>20</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="1">
+        <v>5</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" s="1">
+        <v>100</v>
+      </c>
+      <c r="M22" s="6">
+        <v>1</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O22" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="5">
+        <v>46120</v>
+      </c>
+      <c r="D23" s="1">
+        <v>5</v>
+      </c>
+      <c r="E23" s="1">
+        <v>20</v>
+      </c>
+      <c r="F23" s="1">
+        <v>30</v>
+      </c>
+      <c r="G23" s="1">
+        <v>20</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="I23" s="1">
+        <v>5</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" s="1">
+        <v>100</v>
+      </c>
+      <c r="M23" s="6">
+        <v>1</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O23" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="5">
+        <v>46121</v>
+      </c>
+      <c r="D24" s="1">
+        <v>5</v>
+      </c>
+      <c r="E24" s="1">
+        <v>20</v>
+      </c>
+      <c r="F24" s="1">
+        <v>30</v>
+      </c>
+      <c r="G24" s="1">
+        <v>20</v>
+      </c>
+      <c r="H24" s="1">
+        <v>20</v>
+      </c>
+      <c r="I24" s="1">
+        <v>5</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L24" s="1">
+        <v>100</v>
+      </c>
+      <c r="M24" s="6">
+        <v>1</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O24" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="5">
+        <v>46120</v>
+      </c>
+      <c r="D25" s="1">
+        <v>5</v>
+      </c>
+      <c r="E25" s="1">
+        <v>20</v>
+      </c>
+      <c r="F25" s="1">
+        <v>30</v>
+      </c>
+      <c r="G25" s="1">
+        <v>20</v>
+      </c>
+      <c r="H25" s="1">
+        <v>10</v>
+      </c>
+      <c r="I25" s="1">
+        <v>5</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L25" s="1">
+        <v>90</v>
+      </c>
+      <c r="M25" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O25" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="5">
+        <v>46121</v>
+      </c>
+      <c r="D26" s="1">
+        <v>5</v>
+      </c>
+      <c r="E26" s="1">
+        <v>20</v>
+      </c>
+      <c r="F26" s="1">
+        <v>30</v>
+      </c>
+      <c r="G26" s="1">
+        <v>10</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>5</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="6">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O26" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="5">
+        <v>46100</v>
+      </c>
+      <c r="D27" s="1">
+        <v>5</v>
+      </c>
+      <c r="E27" s="1">
+        <v>20</v>
+      </c>
+      <c r="F27" s="1">
+        <v>30</v>
+      </c>
+      <c r="G27" s="1">
+        <v>20</v>
+      </c>
+      <c r="H27" s="1">
+        <v>20</v>
+      </c>
+      <c r="I27" s="1">
+        <v>5</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L27" s="1">
+        <v>100</v>
+      </c>
+      <c r="M27" s="6">
+        <v>1</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O27" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="5">
+        <v>46100</v>
+      </c>
+      <c r="D28" s="1">
+        <v>5</v>
+      </c>
+      <c r="E28" s="1">
+        <v>10</v>
+      </c>
+      <c r="F28" s="1">
+        <v>15</v>
+      </c>
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
+      <c r="H28" s="1">
+        <v>10</v>
+      </c>
+      <c r="I28" s="1">
+        <v>5</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L28" s="1">
+        <v>55</v>
+      </c>
+      <c r="M28" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O28" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -1667,30 +2043,30 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1701,30 +2077,30 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -1735,61 +2111,61 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
         <v>45</v>
@@ -1905,10 +2281,10 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
         <v>56</v>
@@ -2216,15 +2592,15 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{802A1E98-F0A2-46EE-BF49-63C3E9C1EF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8E0DFE8-41F6-4D59-A57B-E03ACA22F020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="140" windowWidth="22240" windowHeight="13490" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="470" yWindow="0" windowWidth="22910" windowHeight="13490" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="58">
   <si>
     <t>AssociateName</t>
   </si>
@@ -132,6 +132,18 @@
     <t>Michael Chen</t>
   </si>
   <si>
+    <t>TyKee Walmsley</t>
+  </si>
+  <si>
+    <t>Tyler Rainford</t>
+  </si>
+  <si>
+    <t>Seshu Chivukula</t>
+  </si>
+  <si>
+    <t>Breanna Stringfellow</t>
+  </si>
+  <si>
     <t>ManagerName</t>
   </si>
   <si>
@@ -141,9 +153,6 @@
     <t>AssociateEmail</t>
   </si>
   <si>
-    <t>Seshu Chivukula</t>
-  </si>
-  <si>
     <t>Charles Bumgardner</t>
   </si>
   <si>
@@ -156,18 +165,12 @@
     <t>Connie.Serrano@lplfinancial.com</t>
   </si>
   <si>
-    <t>TyKee Walmsley</t>
-  </si>
-  <si>
     <t>TyKee.Walmsley@lplfinancial.com</t>
   </si>
   <si>
     <t>Kelly.Acevedo@lplfinancial.com</t>
   </si>
   <si>
-    <t>Tyler Rainford</t>
-  </si>
-  <si>
     <t>Tyler.Rainford@lplfinancial.com</t>
   </si>
   <si>
@@ -202,9 +205,6 @@
   </si>
   <si>
     <t>Marcus.McDowell@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Breanna Stringfellow</t>
   </si>
   <si>
     <t>Breanna.Stringfellow@lplfinancial.com</t>
@@ -325,8 +325,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O28" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:O28" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O37" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:O37" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -679,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -1676,7 +1676,7 @@
       <c r="L21" s="1">
         <v>100</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="2">
         <v>1</v>
       </c>
       <c r="N21" s="1" t="s">
@@ -1688,7 +1688,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>16</v>
@@ -1723,7 +1723,7 @@
       <c r="L22" s="1">
         <v>100</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="2">
         <v>1</v>
       </c>
       <c r="N22" s="1" t="s">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>16</v>
@@ -1770,7 +1770,7 @@
       <c r="L23" s="1">
         <v>100</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="2">
         <v>1</v>
       </c>
       <c r="N23" s="1" t="s">
@@ -1782,7 +1782,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>16</v>
@@ -1817,7 +1817,7 @@
       <c r="L24" s="1">
         <v>100</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24" s="2">
         <v>1</v>
       </c>
       <c r="N24" s="1" t="s">
@@ -1829,7 +1829,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>16</v>
@@ -1864,7 +1864,7 @@
       <c r="L25" s="1">
         <v>90</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25" s="2">
         <v>0.9</v>
       </c>
       <c r="N25" s="1" t="s">
@@ -1911,7 +1911,7 @@
       <c r="L26" s="1">
         <v>0</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M26" s="2">
         <v>0</v>
       </c>
       <c r="N26" s="1" t="s">
@@ -1958,7 +1958,7 @@
       <c r="L27" s="1">
         <v>100</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="2">
         <v>1</v>
       </c>
       <c r="N27" s="1" t="s">
@@ -2005,13 +2005,436 @@
       <c r="L28" s="1">
         <v>55</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="2">
         <v>0.55000000000000004</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O28" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="5">
+        <v>46106</v>
+      </c>
+      <c r="D29" s="1">
+        <v>5</v>
+      </c>
+      <c r="E29" s="1">
+        <v>20</v>
+      </c>
+      <c r="F29" s="1">
+        <v>30</v>
+      </c>
+      <c r="G29" s="1">
+        <v>20</v>
+      </c>
+      <c r="H29" s="1">
+        <v>20</v>
+      </c>
+      <c r="I29" s="1">
+        <v>5</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L29" s="1">
+        <v>100</v>
+      </c>
+      <c r="M29" s="6">
+        <v>1</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O29" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="5">
+        <v>46106</v>
+      </c>
+      <c r="D30" s="1">
+        <v>5</v>
+      </c>
+      <c r="E30" s="1">
+        <v>20</v>
+      </c>
+      <c r="F30" s="1">
+        <v>30</v>
+      </c>
+      <c r="G30" s="1">
+        <v>20</v>
+      </c>
+      <c r="H30" s="1">
+        <v>20</v>
+      </c>
+      <c r="I30" s="1">
+        <v>5</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L30" s="1">
+        <v>100</v>
+      </c>
+      <c r="M30" s="6">
+        <v>1</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O30" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="5">
+        <v>46127</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
+      <c r="E31" s="1">
+        <v>20</v>
+      </c>
+      <c r="F31" s="1">
+        <v>30</v>
+      </c>
+      <c r="G31" s="1">
+        <v>20</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="6">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O31" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="5">
+        <v>46128</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>20</v>
+      </c>
+      <c r="F32" s="1">
+        <v>30</v>
+      </c>
+      <c r="G32" s="1">
+        <v>20</v>
+      </c>
+      <c r="H32" s="1">
+        <v>20</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O32" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="5">
+        <v>46127</v>
+      </c>
+      <c r="D33" s="1">
+        <v>5</v>
+      </c>
+      <c r="E33" s="1">
+        <v>20</v>
+      </c>
+      <c r="F33" s="1">
+        <v>30</v>
+      </c>
+      <c r="G33" s="1">
+        <v>20</v>
+      </c>
+      <c r="H33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="1">
+        <v>5</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33" s="1">
+        <v>100</v>
+      </c>
+      <c r="M33" s="6">
+        <v>1</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O33" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="5">
+        <v>46127</v>
+      </c>
+      <c r="D34" s="1">
+        <v>5</v>
+      </c>
+      <c r="E34" s="1">
+        <v>20</v>
+      </c>
+      <c r="F34" s="1">
+        <v>30</v>
+      </c>
+      <c r="G34" s="1">
+        <v>20</v>
+      </c>
+      <c r="H34" s="1">
+        <v>20</v>
+      </c>
+      <c r="I34" s="1">
+        <v>5</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L34" s="1">
+        <v>100</v>
+      </c>
+      <c r="M34" s="6">
+        <v>1</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O34" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="5">
+        <v>46128</v>
+      </c>
+      <c r="D35" s="1">
+        <v>5</v>
+      </c>
+      <c r="E35" s="1">
+        <v>20</v>
+      </c>
+      <c r="F35" s="1">
+        <v>30</v>
+      </c>
+      <c r="G35" s="1">
+        <v>20</v>
+      </c>
+      <c r="H35" s="1">
+        <v>20</v>
+      </c>
+      <c r="I35" s="1">
+        <v>5</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35" s="1">
+        <v>100</v>
+      </c>
+      <c r="M35" s="6">
+        <v>1</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O35" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="5">
+        <v>46127</v>
+      </c>
+      <c r="D36" s="1">
+        <v>5</v>
+      </c>
+      <c r="E36" s="1">
+        <v>20</v>
+      </c>
+      <c r="F36" s="1">
+        <v>30</v>
+      </c>
+      <c r="G36" s="1">
+        <v>20</v>
+      </c>
+      <c r="H36" s="1">
+        <v>20</v>
+      </c>
+      <c r="I36" s="1">
+        <v>5</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L36" s="1">
+        <v>100</v>
+      </c>
+      <c r="M36" s="6">
+        <v>1</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O36" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="5">
+        <v>46128</v>
+      </c>
+      <c r="D37" s="1">
+        <v>5</v>
+      </c>
+      <c r="E37" s="1">
+        <v>20</v>
+      </c>
+      <c r="F37" s="1">
+        <v>30</v>
+      </c>
+      <c r="G37" s="1">
+        <v>20</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>5</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="6">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O37" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -2043,30 +2466,30 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -2077,30 +2500,30 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -2111,30 +2534,30 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -2145,13 +2568,13 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -2162,13 +2585,13 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2179,30 +2602,30 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -2213,13 +2636,13 @@
         <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -2230,13 +2653,13 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -2247,13 +2670,13 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -2264,27 +2687,27 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s">
         <v>56</v>
@@ -2298,10 +2721,10 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
         <v>57</v>
@@ -2592,16 +3015,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8E0DFE8-41F6-4D59-A57B-E03ACA22F020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DE82187-698C-4490-B793-932701D9FE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="470" yWindow="0" windowWidth="22910" windowHeight="13490" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="-60" yWindow="460" windowWidth="28450" windowHeight="12670" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="58">
   <si>
     <t>AssociateName</t>
   </si>
@@ -325,8 +325,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O37" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:O37" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O52" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:O52" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -679,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -2052,7 +2052,7 @@
       <c r="L29" s="1">
         <v>100</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29" s="2">
         <v>1</v>
       </c>
       <c r="N29" s="1" t="s">
@@ -2099,7 +2099,7 @@
       <c r="L30" s="1">
         <v>100</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30" s="2">
         <v>1</v>
       </c>
       <c r="N30" s="1" t="s">
@@ -2146,7 +2146,7 @@
       <c r="L31" s="1">
         <v>0</v>
       </c>
-      <c r="M31" s="6">
+      <c r="M31" s="2">
         <v>0</v>
       </c>
       <c r="N31" s="1" t="s">
@@ -2193,7 +2193,7 @@
       <c r="L32" s="1">
         <v>0</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32" s="2">
         <v>0</v>
       </c>
       <c r="N32" s="1" t="s">
@@ -2240,7 +2240,7 @@
       <c r="L33" s="1">
         <v>100</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33" s="2">
         <v>1</v>
       </c>
       <c r="N33" s="1" t="s">
@@ -2287,7 +2287,7 @@
       <c r="L34" s="1">
         <v>100</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="2">
         <v>1</v>
       </c>
       <c r="N34" s="1" t="s">
@@ -2334,7 +2334,7 @@
       <c r="L35" s="1">
         <v>100</v>
       </c>
-      <c r="M35" s="6">
+      <c r="M35" s="2">
         <v>1</v>
       </c>
       <c r="N35" s="1" t="s">
@@ -2381,7 +2381,7 @@
       <c r="L36" s="1">
         <v>100</v>
       </c>
-      <c r="M36" s="6">
+      <c r="M36" s="2">
         <v>1</v>
       </c>
       <c r="N36" s="1" t="s">
@@ -2428,13 +2428,718 @@
       <c r="L37" s="1">
         <v>0</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37" s="2">
         <v>0</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>28</v>
       </c>
       <c r="O37" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="5">
+        <v>46125</v>
+      </c>
+      <c r="D38" s="1">
+        <v>5</v>
+      </c>
+      <c r="E38" s="1">
+        <v>5</v>
+      </c>
+      <c r="F38" s="1">
+        <v>25</v>
+      </c>
+      <c r="G38" s="1">
+        <v>20</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>5</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O38" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="5">
+        <v>46128</v>
+      </c>
+      <c r="D39" s="1">
+        <v>5</v>
+      </c>
+      <c r="E39" s="1">
+        <v>20</v>
+      </c>
+      <c r="F39" s="1">
+        <v>25</v>
+      </c>
+      <c r="G39" s="1">
+        <v>20</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O39" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="5">
+        <v>46104</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1">
+        <v>20</v>
+      </c>
+      <c r="F40" s="1">
+        <v>30</v>
+      </c>
+      <c r="G40" s="1">
+        <v>20</v>
+      </c>
+      <c r="H40" s="1">
+        <v>20</v>
+      </c>
+      <c r="I40" s="1">
+        <v>5</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O40" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="5">
+        <v>46112</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
+        <v>10</v>
+      </c>
+      <c r="F41" s="1">
+        <v>30</v>
+      </c>
+      <c r="G41" s="1">
+        <v>20</v>
+      </c>
+      <c r="H41" s="1">
+        <v>20</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O41" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="5">
+        <v>46111</v>
+      </c>
+      <c r="D42" s="1">
+        <v>5</v>
+      </c>
+      <c r="E42" s="1">
+        <v>20</v>
+      </c>
+      <c r="F42" s="1">
+        <v>30</v>
+      </c>
+      <c r="G42" s="1">
+        <v>20</v>
+      </c>
+      <c r="H42" s="1">
+        <v>20</v>
+      </c>
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L42" s="1">
+        <v>100</v>
+      </c>
+      <c r="M42" s="2">
+        <v>1</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O42" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="5">
+        <v>46111</v>
+      </c>
+      <c r="D43" s="1">
+        <v>5</v>
+      </c>
+      <c r="E43" s="1">
+        <v>20</v>
+      </c>
+      <c r="F43" s="1">
+        <v>30</v>
+      </c>
+      <c r="G43" s="1">
+        <v>20</v>
+      </c>
+      <c r="H43" s="1">
+        <v>20</v>
+      </c>
+      <c r="I43" s="1">
+        <v>5</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" s="1">
+        <v>100</v>
+      </c>
+      <c r="M43" s="2">
+        <v>1</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O43" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="5">
+        <v>46129</v>
+      </c>
+      <c r="D44" s="1">
+        <v>5</v>
+      </c>
+      <c r="E44" s="1">
+        <v>20</v>
+      </c>
+      <c r="F44" s="1">
+        <v>30</v>
+      </c>
+      <c r="G44" s="1">
+        <v>15</v>
+      </c>
+      <c r="H44" s="1">
+        <v>20</v>
+      </c>
+      <c r="I44" s="1">
+        <v>5</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44" s="1">
+        <v>95</v>
+      </c>
+      <c r="M44" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O44" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="5">
+        <v>46108</v>
+      </c>
+      <c r="D45" s="1">
+        <v>5</v>
+      </c>
+      <c r="E45" s="1">
+        <v>20</v>
+      </c>
+      <c r="F45" s="1">
+        <v>30</v>
+      </c>
+      <c r="G45" s="1">
+        <v>20</v>
+      </c>
+      <c r="H45" s="1">
+        <v>10</v>
+      </c>
+      <c r="I45" s="1">
+        <v>5</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L45" s="1">
+        <v>90</v>
+      </c>
+      <c r="M45" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O45" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="5">
+        <v>46126</v>
+      </c>
+      <c r="D46" s="1">
+        <v>5</v>
+      </c>
+      <c r="E46" s="1">
+        <v>20</v>
+      </c>
+      <c r="F46" s="1">
+        <v>30</v>
+      </c>
+      <c r="G46" s="1">
+        <v>20</v>
+      </c>
+      <c r="H46" s="1">
+        <v>20</v>
+      </c>
+      <c r="I46" s="1">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46" s="1">
+        <v>100</v>
+      </c>
+      <c r="M46" s="2">
+        <v>1</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O46" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="5">
+        <v>46108</v>
+      </c>
+      <c r="D47" s="1">
+        <v>5</v>
+      </c>
+      <c r="E47" s="1">
+        <v>20</v>
+      </c>
+      <c r="F47" s="1">
+        <v>30</v>
+      </c>
+      <c r="G47" s="1">
+        <v>20</v>
+      </c>
+      <c r="H47" s="1">
+        <v>10</v>
+      </c>
+      <c r="I47" s="1">
+        <v>5</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" s="1">
+        <v>90</v>
+      </c>
+      <c r="M47" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O47" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="5">
+        <v>46111</v>
+      </c>
+      <c r="D48" s="1">
+        <v>5</v>
+      </c>
+      <c r="E48" s="1">
+        <v>20</v>
+      </c>
+      <c r="F48" s="1">
+        <v>30</v>
+      </c>
+      <c r="G48" s="1">
+        <v>20</v>
+      </c>
+      <c r="H48" s="1">
+        <v>20</v>
+      </c>
+      <c r="I48" s="1">
+        <v>5</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48" s="1">
+        <v>100</v>
+      </c>
+      <c r="M48" s="2">
+        <v>1</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O48" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="5">
+        <v>46114</v>
+      </c>
+      <c r="D49" s="1">
+        <v>5</v>
+      </c>
+      <c r="E49" s="1">
+        <v>20</v>
+      </c>
+      <c r="F49" s="1">
+        <v>30</v>
+      </c>
+      <c r="G49" s="1">
+        <v>20</v>
+      </c>
+      <c r="H49" s="1">
+        <v>20</v>
+      </c>
+      <c r="I49" s="1">
+        <v>5</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49" s="1">
+        <v>100</v>
+      </c>
+      <c r="M49" s="6">
+        <v>1</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O49" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="5">
+        <v>46129</v>
+      </c>
+      <c r="D50" s="1">
+        <v>5</v>
+      </c>
+      <c r="E50" s="1">
+        <v>20</v>
+      </c>
+      <c r="F50" s="1">
+        <v>30</v>
+      </c>
+      <c r="G50" s="1">
+        <v>20</v>
+      </c>
+      <c r="H50" s="1">
+        <v>20</v>
+      </c>
+      <c r="I50" s="1">
+        <v>5</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L50" s="1">
+        <v>100</v>
+      </c>
+      <c r="M50" s="6">
+        <v>1</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O50" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="5">
+        <v>46113</v>
+      </c>
+      <c r="D51" s="1">
+        <v>5</v>
+      </c>
+      <c r="E51" s="1">
+        <v>20</v>
+      </c>
+      <c r="F51" s="1">
+        <v>30</v>
+      </c>
+      <c r="G51" s="1">
+        <v>20</v>
+      </c>
+      <c r="H51" s="1">
+        <v>20</v>
+      </c>
+      <c r="I51" s="1">
+        <v>5</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L51" s="1">
+        <v>100</v>
+      </c>
+      <c r="M51" s="6">
+        <v>1</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O51" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="5">
+        <v>46118</v>
+      </c>
+      <c r="D52" s="1">
+        <v>5</v>
+      </c>
+      <c r="E52" s="1">
+        <v>20</v>
+      </c>
+      <c r="F52" s="1">
+        <v>30</v>
+      </c>
+      <c r="G52" s="1">
+        <v>20</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>5</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L52" s="1">
+        <v>80</v>
+      </c>
+      <c r="M52" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O52" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -3015,16 +3720,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DE82187-698C-4490-B793-932701D9FE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79ED72C2-FC16-4FC4-A524-B9DAD74D4C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="460" windowWidth="28450" windowHeight="12670" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="750" yWindow="1170" windowWidth="33650" windowHeight="13230" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="58">
   <si>
     <t>AssociateName</t>
   </si>
@@ -325,8 +325,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O52" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:O52" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O78" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:O78" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -679,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -2992,7 +2992,7 @@
       <c r="L49" s="1">
         <v>100</v>
       </c>
-      <c r="M49" s="6">
+      <c r="M49" s="2">
         <v>1</v>
       </c>
       <c r="N49" s="1" t="s">
@@ -3039,7 +3039,7 @@
       <c r="L50" s="1">
         <v>100</v>
       </c>
-      <c r="M50" s="6">
+      <c r="M50" s="2">
         <v>1</v>
       </c>
       <c r="N50" s="1" t="s">
@@ -3086,7 +3086,7 @@
       <c r="L51" s="1">
         <v>100</v>
       </c>
-      <c r="M51" s="6">
+      <c r="M51" s="2">
         <v>1</v>
       </c>
       <c r="N51" s="1" t="s">
@@ -3133,13 +3133,1235 @@
       <c r="L52" s="1">
         <v>80</v>
       </c>
-      <c r="M52" s="6">
+      <c r="M52" s="2">
         <v>0.8</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>28</v>
       </c>
       <c r="O52" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="5">
+        <v>46126</v>
+      </c>
+      <c r="D53" s="1">
+        <v>5</v>
+      </c>
+      <c r="E53" s="1">
+        <v>20</v>
+      </c>
+      <c r="F53" s="1">
+        <v>30</v>
+      </c>
+      <c r="G53" s="1">
+        <v>20</v>
+      </c>
+      <c r="H53" s="1">
+        <v>15</v>
+      </c>
+      <c r="I53" s="1">
+        <v>5</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L53" s="1">
+        <v>95</v>
+      </c>
+      <c r="M53" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O53" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="5">
+        <v>46126</v>
+      </c>
+      <c r="D54" s="1">
+        <v>5</v>
+      </c>
+      <c r="E54" s="1">
+        <v>10</v>
+      </c>
+      <c r="F54" s="1">
+        <v>30</v>
+      </c>
+      <c r="G54" s="1">
+        <v>20</v>
+      </c>
+      <c r="H54" s="1">
+        <v>20</v>
+      </c>
+      <c r="I54" s="1">
+        <v>5</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L54" s="1">
+        <v>90</v>
+      </c>
+      <c r="M54" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O54" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="5">
+        <v>46121</v>
+      </c>
+      <c r="D55" s="1">
+        <v>5</v>
+      </c>
+      <c r="E55" s="1">
+        <v>20</v>
+      </c>
+      <c r="F55" s="1">
+        <v>30</v>
+      </c>
+      <c r="G55" s="1">
+        <v>20</v>
+      </c>
+      <c r="H55" s="1">
+        <v>20</v>
+      </c>
+      <c r="I55" s="1">
+        <v>5</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L55" s="1">
+        <v>100</v>
+      </c>
+      <c r="M55" s="6">
+        <v>1</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O55" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="5">
+        <v>46129</v>
+      </c>
+      <c r="D56" s="1">
+        <v>5</v>
+      </c>
+      <c r="E56" s="1">
+        <v>20</v>
+      </c>
+      <c r="F56" s="1">
+        <v>30</v>
+      </c>
+      <c r="G56" s="1">
+        <v>20</v>
+      </c>
+      <c r="H56" s="1">
+        <v>20</v>
+      </c>
+      <c r="I56" s="1">
+        <v>5</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L56" s="1">
+        <v>100</v>
+      </c>
+      <c r="M56" s="6">
+        <v>1</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O56" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="5">
+        <v>46135</v>
+      </c>
+      <c r="D57" s="1">
+        <v>5</v>
+      </c>
+      <c r="E57" s="1">
+        <v>20</v>
+      </c>
+      <c r="F57" s="1">
+        <v>25</v>
+      </c>
+      <c r="G57" s="1">
+        <v>20</v>
+      </c>
+      <c r="H57" s="1">
+        <v>20</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L57" s="1">
+        <v>90</v>
+      </c>
+      <c r="M57" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O57" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" s="5">
+        <v>46113</v>
+      </c>
+      <c r="D58" s="1">
+        <v>5</v>
+      </c>
+      <c r="E58" s="1">
+        <v>20</v>
+      </c>
+      <c r="F58" s="1">
+        <v>30</v>
+      </c>
+      <c r="G58" s="1">
+        <v>20</v>
+      </c>
+      <c r="H58" s="1">
+        <v>20</v>
+      </c>
+      <c r="I58" s="1">
+        <v>5</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L58" s="1">
+        <v>100</v>
+      </c>
+      <c r="M58" s="6">
+        <v>1</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O58" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A59" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="5">
+        <v>46135</v>
+      </c>
+      <c r="D59" s="1">
+        <v>5</v>
+      </c>
+      <c r="E59" s="1">
+        <v>20</v>
+      </c>
+      <c r="F59" s="1">
+        <v>30</v>
+      </c>
+      <c r="G59" s="1">
+        <v>20</v>
+      </c>
+      <c r="H59" s="1">
+        <v>20</v>
+      </c>
+      <c r="I59" s="1">
+        <v>5</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L59" s="1">
+        <v>100</v>
+      </c>
+      <c r="M59" s="6">
+        <v>1</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O59" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A60" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="5">
+        <v>46134</v>
+      </c>
+      <c r="D60" s="1">
+        <v>5</v>
+      </c>
+      <c r="E60" s="1">
+        <v>20</v>
+      </c>
+      <c r="F60" s="1">
+        <v>30</v>
+      </c>
+      <c r="G60" s="1">
+        <v>20</v>
+      </c>
+      <c r="H60" s="1">
+        <v>20</v>
+      </c>
+      <c r="I60" s="1">
+        <v>5</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L60" s="1">
+        <v>100</v>
+      </c>
+      <c r="M60" s="6">
+        <v>1</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O60" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A61" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="5">
+        <v>46114</v>
+      </c>
+      <c r="D61" s="1">
+        <v>5</v>
+      </c>
+      <c r="E61" s="1">
+        <v>20</v>
+      </c>
+      <c r="F61" s="1">
+        <v>30</v>
+      </c>
+      <c r="G61" s="1">
+        <v>20</v>
+      </c>
+      <c r="H61" s="1">
+        <v>20</v>
+      </c>
+      <c r="I61" s="1">
+        <v>5</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L61" s="1">
+        <v>100</v>
+      </c>
+      <c r="M61" s="6">
+        <v>1</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O61" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A62" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62" s="5">
+        <v>46135</v>
+      </c>
+      <c r="D62" s="1">
+        <v>5</v>
+      </c>
+      <c r="E62" s="1">
+        <v>20</v>
+      </c>
+      <c r="F62" s="1">
+        <v>30</v>
+      </c>
+      <c r="G62" s="1">
+        <v>20</v>
+      </c>
+      <c r="H62" s="1">
+        <v>20</v>
+      </c>
+      <c r="I62" s="1">
+        <v>5</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L62" s="1">
+        <v>100</v>
+      </c>
+      <c r="M62" s="6">
+        <v>1</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O62" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A63" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="5">
+        <v>46134</v>
+      </c>
+      <c r="D63" s="1">
+        <v>5</v>
+      </c>
+      <c r="E63" s="1">
+        <v>20</v>
+      </c>
+      <c r="F63" s="1">
+        <v>30</v>
+      </c>
+      <c r="G63" s="1">
+        <v>20</v>
+      </c>
+      <c r="H63" s="1">
+        <v>20</v>
+      </c>
+      <c r="I63" s="1">
+        <v>5</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L63" s="1">
+        <v>100</v>
+      </c>
+      <c r="M63" s="6">
+        <v>1</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O63" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="5">
+        <v>46133</v>
+      </c>
+      <c r="D64" s="1">
+        <v>5</v>
+      </c>
+      <c r="E64" s="1">
+        <v>20</v>
+      </c>
+      <c r="F64" s="1">
+        <v>30</v>
+      </c>
+      <c r="G64" s="1">
+        <v>20</v>
+      </c>
+      <c r="H64" s="1">
+        <v>20</v>
+      </c>
+      <c r="I64" s="1">
+        <v>5</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L64" s="1">
+        <v>100</v>
+      </c>
+      <c r="M64" s="6">
+        <v>1</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O64" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A65" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" s="5">
+        <v>46113</v>
+      </c>
+      <c r="D65" s="1">
+        <v>5</v>
+      </c>
+      <c r="E65" s="1">
+        <v>20</v>
+      </c>
+      <c r="F65" s="1">
+        <v>30</v>
+      </c>
+      <c r="G65" s="1">
+        <v>20</v>
+      </c>
+      <c r="H65" s="1">
+        <v>20</v>
+      </c>
+      <c r="I65" s="1">
+        <v>5</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L65" s="1">
+        <v>100</v>
+      </c>
+      <c r="M65" s="6">
+        <v>1</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O65" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="5">
+        <v>46135</v>
+      </c>
+      <c r="D66" s="1">
+        <v>5</v>
+      </c>
+      <c r="E66" s="1">
+        <v>20</v>
+      </c>
+      <c r="F66" s="1">
+        <v>30</v>
+      </c>
+      <c r="G66" s="1">
+        <v>20</v>
+      </c>
+      <c r="H66" s="1">
+        <v>20</v>
+      </c>
+      <c r="I66" s="1">
+        <v>5</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L66" s="1">
+        <v>100</v>
+      </c>
+      <c r="M66" s="6">
+        <v>1</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O66" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A67" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" s="5">
+        <v>46135</v>
+      </c>
+      <c r="D67" s="1">
+        <v>5</v>
+      </c>
+      <c r="E67" s="1">
+        <v>20</v>
+      </c>
+      <c r="F67" s="1">
+        <v>30</v>
+      </c>
+      <c r="G67" s="1">
+        <v>20</v>
+      </c>
+      <c r="H67" s="1">
+        <v>20</v>
+      </c>
+      <c r="I67" s="1">
+        <v>5</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L67" s="1">
+        <v>100</v>
+      </c>
+      <c r="M67" s="6">
+        <v>1</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O67" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="5">
+        <v>46134</v>
+      </c>
+      <c r="D68" s="1">
+        <v>5</v>
+      </c>
+      <c r="E68" s="1">
+        <v>20</v>
+      </c>
+      <c r="F68" s="1">
+        <v>30</v>
+      </c>
+      <c r="G68" s="1">
+        <v>20</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" s="1">
+        <v>5</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
+      </c>
+      <c r="M68" s="6">
+        <v>0</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O68" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A69" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" s="5">
+        <v>46113</v>
+      </c>
+      <c r="D69" s="1">
+        <v>5</v>
+      </c>
+      <c r="E69" s="1">
+        <v>20</v>
+      </c>
+      <c r="F69" s="1">
+        <v>30</v>
+      </c>
+      <c r="G69" s="1">
+        <v>20</v>
+      </c>
+      <c r="H69" s="1">
+        <v>20</v>
+      </c>
+      <c r="I69" s="1">
+        <v>5</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L69" s="1">
+        <v>100</v>
+      </c>
+      <c r="M69" s="6">
+        <v>1</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O69" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A70" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" s="5">
+        <v>46118</v>
+      </c>
+      <c r="D70" s="1">
+        <v>5</v>
+      </c>
+      <c r="E70" s="1">
+        <v>20</v>
+      </c>
+      <c r="F70" s="1">
+        <v>30</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <v>10</v>
+      </c>
+      <c r="I70" s="1">
+        <v>5</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L70" s="1">
+        <v>70</v>
+      </c>
+      <c r="M70" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O70" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A71" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" s="5">
+        <v>46122</v>
+      </c>
+      <c r="D71" s="1">
+        <v>5</v>
+      </c>
+      <c r="E71" s="1">
+        <v>20</v>
+      </c>
+      <c r="F71" s="1">
+        <v>30</v>
+      </c>
+      <c r="G71" s="1">
+        <v>20</v>
+      </c>
+      <c r="H71" s="1">
+        <v>15</v>
+      </c>
+      <c r="I71" s="1">
+        <v>5</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L71" s="1">
+        <v>95</v>
+      </c>
+      <c r="M71" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O71" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A72" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C72" s="5">
+        <v>46119</v>
+      </c>
+      <c r="D72" s="1">
+        <v>5</v>
+      </c>
+      <c r="E72" s="1">
+        <v>20</v>
+      </c>
+      <c r="F72" s="1">
+        <v>30</v>
+      </c>
+      <c r="G72" s="1">
+        <v>20</v>
+      </c>
+      <c r="H72" s="1">
+        <v>20</v>
+      </c>
+      <c r="I72" s="1">
+        <v>5</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L72" s="1">
+        <v>100</v>
+      </c>
+      <c r="M72" s="6">
+        <v>1</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O72" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C73" s="5">
+        <v>46122</v>
+      </c>
+      <c r="D73" s="1">
+        <v>5</v>
+      </c>
+      <c r="E73" s="1">
+        <v>15</v>
+      </c>
+      <c r="F73" s="1">
+        <v>30</v>
+      </c>
+      <c r="G73" s="1">
+        <v>20</v>
+      </c>
+      <c r="H73" s="1">
+        <v>20</v>
+      </c>
+      <c r="I73" s="1">
+        <v>5</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L73" s="1">
+        <v>95</v>
+      </c>
+      <c r="M73" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O73" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C74" s="5">
+        <v>46135</v>
+      </c>
+      <c r="D74" s="1">
+        <v>5</v>
+      </c>
+      <c r="E74" s="1">
+        <v>20</v>
+      </c>
+      <c r="F74" s="1">
+        <v>30</v>
+      </c>
+      <c r="G74" s="1">
+        <v>20</v>
+      </c>
+      <c r="H74" s="1">
+        <v>20</v>
+      </c>
+      <c r="I74" s="1">
+        <v>5</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L74" s="1">
+        <v>100</v>
+      </c>
+      <c r="M74" s="6">
+        <v>1</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O74" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C75" s="5">
+        <v>46120</v>
+      </c>
+      <c r="D75" s="1">
+        <v>5</v>
+      </c>
+      <c r="E75" s="1">
+        <v>15</v>
+      </c>
+      <c r="F75" s="1">
+        <v>30</v>
+      </c>
+      <c r="G75" s="1">
+        <v>20</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+      <c r="I75" s="1">
+        <v>5</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L75" s="1">
+        <v>0</v>
+      </c>
+      <c r="M75" s="6">
+        <v>0</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O75" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A76" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" s="5">
+        <v>46122</v>
+      </c>
+      <c r="D76" s="1">
+        <v>5</v>
+      </c>
+      <c r="E76" s="1">
+        <v>20</v>
+      </c>
+      <c r="F76" s="1">
+        <v>30</v>
+      </c>
+      <c r="G76" s="1">
+        <v>20</v>
+      </c>
+      <c r="H76" s="1">
+        <v>20</v>
+      </c>
+      <c r="I76" s="1">
+        <v>5</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L76" s="1">
+        <v>100</v>
+      </c>
+      <c r="M76" s="6">
+        <v>1</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O76" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A77" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C77" s="5">
+        <v>46122</v>
+      </c>
+      <c r="D77" s="1">
+        <v>5</v>
+      </c>
+      <c r="E77" s="1">
+        <v>20</v>
+      </c>
+      <c r="F77" s="1">
+        <v>30</v>
+      </c>
+      <c r="G77" s="1">
+        <v>20</v>
+      </c>
+      <c r="H77" s="1">
+        <v>20</v>
+      </c>
+      <c r="I77" s="1">
+        <v>5</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L77" s="1">
+        <v>100</v>
+      </c>
+      <c r="M77" s="6">
+        <v>1</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O77" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A78" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78" s="5">
+        <v>46121</v>
+      </c>
+      <c r="D78" s="1">
+        <v>5</v>
+      </c>
+      <c r="E78" s="1">
+        <v>20</v>
+      </c>
+      <c r="F78" s="1">
+        <v>30</v>
+      </c>
+      <c r="G78" s="1">
+        <v>20</v>
+      </c>
+      <c r="H78" s="1">
+        <v>20</v>
+      </c>
+      <c r="I78" s="1">
+        <v>5</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L78" s="1">
+        <v>100</v>
+      </c>
+      <c r="M78" s="6">
+        <v>1</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O78" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -3445,6 +4667,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
@@ -3457,7 +4688,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -3708,33 +4939,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3751,12 +4981,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79ED72C2-FC16-4FC4-A524-B9DAD74D4C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CB20C51-9AB3-4FF1-A475-B2AACF372333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="1170" windowWidth="33650" windowHeight="13230" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="80" yWindow="630" windowWidth="18970" windowHeight="13230" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="58">
   <si>
     <t>AssociateName</t>
   </si>
@@ -262,7 +262,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -275,9 +275,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -325,8 +322,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O78" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:O78" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O87" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:O87" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -679,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -3180,7 +3177,7 @@
       <c r="L53" s="1">
         <v>95</v>
       </c>
-      <c r="M53" s="6">
+      <c r="M53" s="2">
         <v>0.95</v>
       </c>
       <c r="N53" s="1" t="s">
@@ -3227,7 +3224,7 @@
       <c r="L54" s="1">
         <v>90</v>
       </c>
-      <c r="M54" s="6">
+      <c r="M54" s="2">
         <v>0.9</v>
       </c>
       <c r="N54" s="1" t="s">
@@ -3274,7 +3271,7 @@
       <c r="L55" s="1">
         <v>100</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M55" s="2">
         <v>1</v>
       </c>
       <c r="N55" s="1" t="s">
@@ -3321,7 +3318,7 @@
       <c r="L56" s="1">
         <v>100</v>
       </c>
-      <c r="M56" s="6">
+      <c r="M56" s="2">
         <v>1</v>
       </c>
       <c r="N56" s="1" t="s">
@@ -3368,7 +3365,7 @@
       <c r="L57" s="1">
         <v>90</v>
       </c>
-      <c r="M57" s="6">
+      <c r="M57" s="2">
         <v>0.9</v>
       </c>
       <c r="N57" s="1" t="s">
@@ -3415,7 +3412,7 @@
       <c r="L58" s="1">
         <v>100</v>
       </c>
-      <c r="M58" s="6">
+      <c r="M58" s="2">
         <v>1</v>
       </c>
       <c r="N58" s="1" t="s">
@@ -3462,7 +3459,7 @@
       <c r="L59" s="1">
         <v>100</v>
       </c>
-      <c r="M59" s="6">
+      <c r="M59" s="2">
         <v>1</v>
       </c>
       <c r="N59" s="1" t="s">
@@ -3509,7 +3506,7 @@
       <c r="L60" s="1">
         <v>100</v>
       </c>
-      <c r="M60" s="6">
+      <c r="M60" s="2">
         <v>1</v>
       </c>
       <c r="N60" s="1" t="s">
@@ -3556,7 +3553,7 @@
       <c r="L61" s="1">
         <v>100</v>
       </c>
-      <c r="M61" s="6">
+      <c r="M61" s="2">
         <v>1</v>
       </c>
       <c r="N61" s="1" t="s">
@@ -3603,7 +3600,7 @@
       <c r="L62" s="1">
         <v>100</v>
       </c>
-      <c r="M62" s="6">
+      <c r="M62" s="2">
         <v>1</v>
       </c>
       <c r="N62" s="1" t="s">
@@ -3650,7 +3647,7 @@
       <c r="L63" s="1">
         <v>100</v>
       </c>
-      <c r="M63" s="6">
+      <c r="M63" s="2">
         <v>1</v>
       </c>
       <c r="N63" s="1" t="s">
@@ -3697,7 +3694,7 @@
       <c r="L64" s="1">
         <v>100</v>
       </c>
-      <c r="M64" s="6">
+      <c r="M64" s="2">
         <v>1</v>
       </c>
       <c r="N64" s="1" t="s">
@@ -3744,7 +3741,7 @@
       <c r="L65" s="1">
         <v>100</v>
       </c>
-      <c r="M65" s="6">
+      <c r="M65" s="2">
         <v>1</v>
       </c>
       <c r="N65" s="1" t="s">
@@ -3791,7 +3788,7 @@
       <c r="L66" s="1">
         <v>100</v>
       </c>
-      <c r="M66" s="6">
+      <c r="M66" s="2">
         <v>1</v>
       </c>
       <c r="N66" s="1" t="s">
@@ -3838,7 +3835,7 @@
       <c r="L67" s="1">
         <v>100</v>
       </c>
-      <c r="M67" s="6">
+      <c r="M67" s="2">
         <v>1</v>
       </c>
       <c r="N67" s="1" t="s">
@@ -3885,7 +3882,7 @@
       <c r="L68" s="1">
         <v>0</v>
       </c>
-      <c r="M68" s="6">
+      <c r="M68" s="2">
         <v>0</v>
       </c>
       <c r="N68" s="1" t="s">
@@ -3932,7 +3929,7 @@
       <c r="L69" s="1">
         <v>100</v>
       </c>
-      <c r="M69" s="6">
+      <c r="M69" s="2">
         <v>1</v>
       </c>
       <c r="N69" s="1" t="s">
@@ -3979,7 +3976,7 @@
       <c r="L70" s="1">
         <v>70</v>
       </c>
-      <c r="M70" s="6">
+      <c r="M70" s="2">
         <v>0.7</v>
       </c>
       <c r="N70" s="1" t="s">
@@ -4026,7 +4023,7 @@
       <c r="L71" s="1">
         <v>95</v>
       </c>
-      <c r="M71" s="6">
+      <c r="M71" s="2">
         <v>0.95</v>
       </c>
       <c r="N71" s="1" t="s">
@@ -4073,7 +4070,7 @@
       <c r="L72" s="1">
         <v>100</v>
       </c>
-      <c r="M72" s="6">
+      <c r="M72" s="2">
         <v>1</v>
       </c>
       <c r="N72" s="1" t="s">
@@ -4120,7 +4117,7 @@
       <c r="L73" s="1">
         <v>95</v>
       </c>
-      <c r="M73" s="6">
+      <c r="M73" s="2">
         <v>0.95</v>
       </c>
       <c r="N73" s="1" t="s">
@@ -4167,7 +4164,7 @@
       <c r="L74" s="1">
         <v>100</v>
       </c>
-      <c r="M74" s="6">
+      <c r="M74" s="2">
         <v>1</v>
       </c>
       <c r="N74" s="1" t="s">
@@ -4214,7 +4211,7 @@
       <c r="L75" s="1">
         <v>0</v>
       </c>
-      <c r="M75" s="6">
+      <c r="M75" s="2">
         <v>0</v>
       </c>
       <c r="N75" s="1" t="s">
@@ -4261,7 +4258,7 @@
       <c r="L76" s="1">
         <v>100</v>
       </c>
-      <c r="M76" s="6">
+      <c r="M76" s="2">
         <v>1</v>
       </c>
       <c r="N76" s="1" t="s">
@@ -4308,7 +4305,7 @@
       <c r="L77" s="1">
         <v>100</v>
       </c>
-      <c r="M77" s="6">
+      <c r="M77" s="2">
         <v>1</v>
       </c>
       <c r="N77" s="1" t="s">
@@ -4355,13 +4352,436 @@
       <c r="L78" s="1">
         <v>100</v>
       </c>
-      <c r="M78" s="6">
+      <c r="M78" s="2">
         <v>1</v>
       </c>
       <c r="N78" s="1" t="s">
         <v>28</v>
       </c>
       <c r="O78" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A79" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" s="5">
+        <v>46142</v>
+      </c>
+      <c r="D79" s="1">
+        <v>5</v>
+      </c>
+      <c r="E79" s="1">
+        <v>20</v>
+      </c>
+      <c r="F79" s="1">
+        <v>30</v>
+      </c>
+      <c r="G79" s="1">
+        <v>20</v>
+      </c>
+      <c r="H79" s="1">
+        <v>20</v>
+      </c>
+      <c r="I79" s="1">
+        <v>5</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L79" s="1">
+        <v>100</v>
+      </c>
+      <c r="M79" s="2">
+        <v>1</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O79" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="5">
+        <v>46141</v>
+      </c>
+      <c r="D80" s="1">
+        <v>5</v>
+      </c>
+      <c r="E80" s="1">
+        <v>20</v>
+      </c>
+      <c r="F80" s="1">
+        <v>30</v>
+      </c>
+      <c r="G80" s="1">
+        <v>20</v>
+      </c>
+      <c r="H80" s="1">
+        <v>20</v>
+      </c>
+      <c r="I80" s="1">
+        <v>5</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L80" s="1">
+        <v>100</v>
+      </c>
+      <c r="M80" s="2">
+        <v>1</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O80" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A81" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" s="5">
+        <v>46140</v>
+      </c>
+      <c r="D81" s="1">
+        <v>5</v>
+      </c>
+      <c r="E81" s="1">
+        <v>20</v>
+      </c>
+      <c r="F81" s="1">
+        <v>30</v>
+      </c>
+      <c r="G81" s="1">
+        <v>20</v>
+      </c>
+      <c r="H81" s="1">
+        <v>20</v>
+      </c>
+      <c r="I81" s="1">
+        <v>5</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L81" s="1">
+        <v>100</v>
+      </c>
+      <c r="M81" s="2">
+        <v>1</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O81" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A82" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" s="5">
+        <v>46141</v>
+      </c>
+      <c r="D82" s="1">
+        <v>5</v>
+      </c>
+      <c r="E82" s="1">
+        <v>20</v>
+      </c>
+      <c r="F82" s="1">
+        <v>30</v>
+      </c>
+      <c r="G82" s="1">
+        <v>15</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+      <c r="I82" s="1">
+        <v>5</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L82" s="1">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2">
+        <v>0</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O82" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="5">
+        <v>46141</v>
+      </c>
+      <c r="D83" s="1">
+        <v>5</v>
+      </c>
+      <c r="E83" s="1">
+        <v>20</v>
+      </c>
+      <c r="F83" s="1">
+        <v>30</v>
+      </c>
+      <c r="G83" s="1">
+        <v>20</v>
+      </c>
+      <c r="H83" s="1">
+        <v>20</v>
+      </c>
+      <c r="I83" s="1">
+        <v>5</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L83" s="1">
+        <v>100</v>
+      </c>
+      <c r="M83" s="2">
+        <v>1</v>
+      </c>
+      <c r="N83" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O83" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A84" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" s="5">
+        <v>46142</v>
+      </c>
+      <c r="D84" s="1">
+        <v>5</v>
+      </c>
+      <c r="E84" s="1">
+        <v>20</v>
+      </c>
+      <c r="F84" s="1">
+        <v>30</v>
+      </c>
+      <c r="G84" s="1">
+        <v>20</v>
+      </c>
+      <c r="H84" s="1">
+        <v>20</v>
+      </c>
+      <c r="I84" s="1">
+        <v>5</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L84" s="1">
+        <v>100</v>
+      </c>
+      <c r="M84" s="2">
+        <v>1</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O84" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A85" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" s="5">
+        <v>46141</v>
+      </c>
+      <c r="D85" s="1">
+        <v>5</v>
+      </c>
+      <c r="E85" s="1">
+        <v>20</v>
+      </c>
+      <c r="F85" s="1">
+        <v>30</v>
+      </c>
+      <c r="G85" s="1">
+        <v>20</v>
+      </c>
+      <c r="H85" s="1">
+        <v>20</v>
+      </c>
+      <c r="I85" s="1">
+        <v>5</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L85" s="1">
+        <v>100</v>
+      </c>
+      <c r="M85" s="2">
+        <v>1</v>
+      </c>
+      <c r="N85" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O85" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A86" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="5">
+        <v>46140</v>
+      </c>
+      <c r="D86" s="1">
+        <v>5</v>
+      </c>
+      <c r="E86" s="1">
+        <v>15</v>
+      </c>
+      <c r="F86" s="1">
+        <v>30</v>
+      </c>
+      <c r="G86" s="1">
+        <v>20</v>
+      </c>
+      <c r="H86" s="1">
+        <v>20</v>
+      </c>
+      <c r="I86" s="1">
+        <v>5</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L86" s="1">
+        <v>95</v>
+      </c>
+      <c r="M86" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O86" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A87" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" s="5">
+        <v>46135</v>
+      </c>
+      <c r="D87" s="1">
+        <v>5</v>
+      </c>
+      <c r="E87" s="1">
+        <v>20</v>
+      </c>
+      <c r="F87" s="1">
+        <v>20</v>
+      </c>
+      <c r="G87" s="1">
+        <v>15</v>
+      </c>
+      <c r="H87" s="1">
+        <v>0</v>
+      </c>
+      <c r="I87" s="1">
+        <v>5</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L87" s="1">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2">
+        <v>0</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O87" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -4380,8 +4800,8 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="32.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4667,15 +5087,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
@@ -4688,7 +5099,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -4939,32 +5350,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4981,4 +5393,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CB20C51-9AB3-4FF1-A475-B2AACF372333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF6E91CA-7754-410E-96E4-7F4B9D1929F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="630" windowWidth="18970" windowHeight="13230" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="13610" yWindow="0" windowWidth="20840" windowHeight="13770" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="58">
   <si>
     <t>AssociateName</t>
   </si>
@@ -262,7 +262,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -275,6 +275,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -322,8 +325,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O87" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:O87" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O93" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:O93" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -676,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -4526,7 +4529,7 @@
         <v>15</v>
       </c>
       <c r="H82" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I82" s="1">
         <v>5</v>
@@ -4535,13 +4538,13 @@
         <v>17</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L82" s="1">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M82" s="2">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="N82" s="1" t="s">
         <v>28</v>
@@ -4782,6 +4785,288 @@
         <v>28</v>
       </c>
       <c r="O87" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A88" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" s="5">
+        <v>46142</v>
+      </c>
+      <c r="D88" s="1">
+        <v>5</v>
+      </c>
+      <c r="E88" s="1">
+        <v>20</v>
+      </c>
+      <c r="F88" s="1">
+        <v>30</v>
+      </c>
+      <c r="G88" s="1">
+        <v>20</v>
+      </c>
+      <c r="H88" s="1">
+        <v>20</v>
+      </c>
+      <c r="I88" s="1">
+        <v>5</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L88" s="1">
+        <v>100</v>
+      </c>
+      <c r="M88" s="6">
+        <v>1</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O88" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C89" s="5">
+        <v>46141</v>
+      </c>
+      <c r="D89" s="1">
+        <v>5</v>
+      </c>
+      <c r="E89" s="1">
+        <v>20</v>
+      </c>
+      <c r="F89" s="1">
+        <v>30</v>
+      </c>
+      <c r="G89" s="1">
+        <v>20</v>
+      </c>
+      <c r="H89" s="1">
+        <v>10</v>
+      </c>
+      <c r="I89" s="1">
+        <v>5</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L89" s="1">
+        <v>90</v>
+      </c>
+      <c r="M89" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O89" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A90" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" s="5">
+        <v>46142</v>
+      </c>
+      <c r="D90" s="1">
+        <v>5</v>
+      </c>
+      <c r="E90" s="1">
+        <v>10</v>
+      </c>
+      <c r="F90" s="1">
+        <v>30</v>
+      </c>
+      <c r="G90" s="1">
+        <v>10</v>
+      </c>
+      <c r="H90" s="1">
+        <v>10</v>
+      </c>
+      <c r="I90" s="1">
+        <v>5</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L90" s="1">
+        <v>70</v>
+      </c>
+      <c r="M90" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="N90" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O90" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A91" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" s="5">
+        <v>46142</v>
+      </c>
+      <c r="D91" s="1">
+        <v>5</v>
+      </c>
+      <c r="E91" s="1">
+        <v>10</v>
+      </c>
+      <c r="F91" s="1">
+        <v>30</v>
+      </c>
+      <c r="G91" s="1">
+        <v>20</v>
+      </c>
+      <c r="H91" s="1">
+        <v>20</v>
+      </c>
+      <c r="I91" s="1">
+        <v>5</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L91" s="1">
+        <v>90</v>
+      </c>
+      <c r="M91" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O91" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A92" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" s="5">
+        <v>46142</v>
+      </c>
+      <c r="D92" s="1">
+        <v>5</v>
+      </c>
+      <c r="E92" s="1">
+        <v>20</v>
+      </c>
+      <c r="F92" s="1">
+        <v>30</v>
+      </c>
+      <c r="G92" s="1">
+        <v>20</v>
+      </c>
+      <c r="H92" s="1">
+        <v>20</v>
+      </c>
+      <c r="I92" s="1">
+        <v>5</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L92" s="1">
+        <v>100</v>
+      </c>
+      <c r="M92" s="6">
+        <v>1</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O92" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A93" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C93" s="5">
+        <v>46142</v>
+      </c>
+      <c r="D93" s="1">
+        <v>5</v>
+      </c>
+      <c r="E93" s="1">
+        <v>20</v>
+      </c>
+      <c r="F93" s="1">
+        <v>20</v>
+      </c>
+      <c r="G93" s="1">
+        <v>20</v>
+      </c>
+      <c r="H93" s="1">
+        <v>20</v>
+      </c>
+      <c r="I93" s="1">
+        <v>5</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L93" s="1">
+        <v>90</v>
+      </c>
+      <c r="M93" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O93" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -5100,6 +5385,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -5350,33 +5644,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5393,12 +5686,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF6E91CA-7754-410E-96E4-7F4B9D1929F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{370AD02E-4819-4E2C-ABA1-ADBCE76976F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13610" yWindow="0" windowWidth="20840" windowHeight="13770" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="17970" windowHeight="13360" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="59">
   <si>
     <t>AssociateName</t>
   </si>
@@ -212,6 +212,9 @@
   <si>
     <t>Thomas.Gordon@lplfinancial.com</t>
   </si>
+  <si>
+    <t>May</t>
+  </si>
 </sst>
 </file>
 
@@ -325,8 +328,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O93" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:O93" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O104" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:O104" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -679,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O104"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -4825,7 +4828,7 @@
       <c r="L88" s="1">
         <v>100</v>
       </c>
-      <c r="M88" s="6">
+      <c r="M88" s="2">
         <v>1</v>
       </c>
       <c r="N88" s="1" t="s">
@@ -4872,7 +4875,7 @@
       <c r="L89" s="1">
         <v>90</v>
       </c>
-      <c r="M89" s="6">
+      <c r="M89" s="2">
         <v>0.9</v>
       </c>
       <c r="N89" s="1" t="s">
@@ -4919,7 +4922,7 @@
       <c r="L90" s="1">
         <v>70</v>
       </c>
-      <c r="M90" s="6">
+      <c r="M90" s="2">
         <v>0.7</v>
       </c>
       <c r="N90" s="1" t="s">
@@ -4966,7 +4969,7 @@
       <c r="L91" s="1">
         <v>90</v>
       </c>
-      <c r="M91" s="6">
+      <c r="M91" s="2">
         <v>0.9</v>
       </c>
       <c r="N91" s="1" t="s">
@@ -5013,7 +5016,7 @@
       <c r="L92" s="1">
         <v>100</v>
       </c>
-      <c r="M92" s="6">
+      <c r="M92" s="2">
         <v>1</v>
       </c>
       <c r="N92" s="1" t="s">
@@ -5060,13 +5063,530 @@
       <c r="L93" s="1">
         <v>90</v>
       </c>
-      <c r="M93" s="6">
+      <c r="M93" s="2">
         <v>0.9</v>
       </c>
       <c r="N93" s="1" t="s">
         <v>28</v>
       </c>
       <c r="O93" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A94" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" s="5">
+        <v>46147</v>
+      </c>
+      <c r="D94" s="1">
+        <v>5</v>
+      </c>
+      <c r="E94" s="1">
+        <v>20</v>
+      </c>
+      <c r="F94" s="1">
+        <v>30</v>
+      </c>
+      <c r="G94" s="1">
+        <v>20</v>
+      </c>
+      <c r="H94" s="1">
+        <v>20</v>
+      </c>
+      <c r="I94" s="1">
+        <v>5</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L94" s="1">
+        <v>100</v>
+      </c>
+      <c r="M94" s="6">
+        <v>1</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O94" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A95" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="5">
+        <v>46148</v>
+      </c>
+      <c r="D95" s="1">
+        <v>5</v>
+      </c>
+      <c r="E95" s="1">
+        <v>20</v>
+      </c>
+      <c r="F95" s="1">
+        <v>30</v>
+      </c>
+      <c r="G95" s="1">
+        <v>20</v>
+      </c>
+      <c r="H95" s="1">
+        <v>20</v>
+      </c>
+      <c r="I95" s="1">
+        <v>5</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L95" s="1">
+        <v>100</v>
+      </c>
+      <c r="M95" s="6">
+        <v>1</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O95" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A96" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" s="5">
+        <v>46147</v>
+      </c>
+      <c r="D96" s="1">
+        <v>5</v>
+      </c>
+      <c r="E96" s="1">
+        <v>20</v>
+      </c>
+      <c r="F96" s="1">
+        <v>30</v>
+      </c>
+      <c r="G96" s="1">
+        <v>20</v>
+      </c>
+      <c r="H96" s="1">
+        <v>20</v>
+      </c>
+      <c r="I96" s="1">
+        <v>5</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L96" s="1">
+        <v>100</v>
+      </c>
+      <c r="M96" s="6">
+        <v>1</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O96" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A97" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" s="5">
+        <v>46149</v>
+      </c>
+      <c r="D97" s="1">
+        <v>5</v>
+      </c>
+      <c r="E97" s="1">
+        <v>20</v>
+      </c>
+      <c r="F97" s="1">
+        <v>30</v>
+      </c>
+      <c r="G97" s="1">
+        <v>20</v>
+      </c>
+      <c r="H97" s="1">
+        <v>20</v>
+      </c>
+      <c r="I97" s="1">
+        <v>5</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L97" s="1">
+        <v>100</v>
+      </c>
+      <c r="M97" s="6">
+        <v>1</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O97" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" s="5">
+        <v>46143</v>
+      </c>
+      <c r="D98" s="1">
+        <v>5</v>
+      </c>
+      <c r="E98" s="1">
+        <v>20</v>
+      </c>
+      <c r="F98" s="1">
+        <v>30</v>
+      </c>
+      <c r="G98" s="1">
+        <v>20</v>
+      </c>
+      <c r="H98" s="1">
+        <v>20</v>
+      </c>
+      <c r="I98" s="1">
+        <v>5</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L98" s="1">
+        <v>100</v>
+      </c>
+      <c r="M98" s="6">
+        <v>1</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O98" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A99" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" s="5">
+        <v>46148</v>
+      </c>
+      <c r="D99" s="1">
+        <v>5</v>
+      </c>
+      <c r="E99" s="1">
+        <v>20</v>
+      </c>
+      <c r="F99" s="1">
+        <v>30</v>
+      </c>
+      <c r="G99" s="1">
+        <v>20</v>
+      </c>
+      <c r="H99" s="1">
+        <v>20</v>
+      </c>
+      <c r="I99" s="1">
+        <v>5</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L99" s="1">
+        <v>100</v>
+      </c>
+      <c r="M99" s="6">
+        <v>1</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O99" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A100" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" s="5">
+        <v>46149</v>
+      </c>
+      <c r="D100" s="1">
+        <v>5</v>
+      </c>
+      <c r="E100" s="1">
+        <v>20</v>
+      </c>
+      <c r="F100" s="1">
+        <v>30</v>
+      </c>
+      <c r="G100" s="1">
+        <v>20</v>
+      </c>
+      <c r="H100" s="1">
+        <v>20</v>
+      </c>
+      <c r="I100" s="1">
+        <v>5</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L100" s="1">
+        <v>100</v>
+      </c>
+      <c r="M100" s="6">
+        <v>1</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O100" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C101" s="5">
+        <v>46149</v>
+      </c>
+      <c r="D101" s="1">
+        <v>5</v>
+      </c>
+      <c r="E101" s="1">
+        <v>20</v>
+      </c>
+      <c r="F101" s="1">
+        <v>30</v>
+      </c>
+      <c r="G101" s="1">
+        <v>20</v>
+      </c>
+      <c r="H101" s="1">
+        <v>20</v>
+      </c>
+      <c r="I101" s="1">
+        <v>5</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L101" s="1">
+        <v>100</v>
+      </c>
+      <c r="M101" s="6">
+        <v>1</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O101" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A102" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C102" s="5">
+        <v>46149</v>
+      </c>
+      <c r="D102" s="1">
+        <v>5</v>
+      </c>
+      <c r="E102" s="1">
+        <v>20</v>
+      </c>
+      <c r="F102" s="1">
+        <v>20</v>
+      </c>
+      <c r="G102" s="1">
+        <v>20</v>
+      </c>
+      <c r="H102" s="1">
+        <v>20</v>
+      </c>
+      <c r="I102" s="1">
+        <v>5</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L102" s="1">
+        <v>90</v>
+      </c>
+      <c r="M102" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O102" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A103" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C103" s="5">
+        <v>46149</v>
+      </c>
+      <c r="D103" s="1">
+        <v>5</v>
+      </c>
+      <c r="E103" s="1">
+        <v>20</v>
+      </c>
+      <c r="F103" s="1">
+        <v>30</v>
+      </c>
+      <c r="G103" s="1">
+        <v>20</v>
+      </c>
+      <c r="H103" s="1">
+        <v>20</v>
+      </c>
+      <c r="I103" s="1">
+        <v>5</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L103" s="1">
+        <v>100</v>
+      </c>
+      <c r="M103" s="6">
+        <v>1</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O103" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A104" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C104" s="5">
+        <v>46148</v>
+      </c>
+      <c r="D104" s="1">
+        <v>5</v>
+      </c>
+      <c r="E104" s="1">
+        <v>20</v>
+      </c>
+      <c r="F104" s="1">
+        <v>30</v>
+      </c>
+      <c r="G104" s="1">
+        <v>20</v>
+      </c>
+      <c r="H104" s="1">
+        <v>20</v>
+      </c>
+      <c r="I104" s="1">
+        <v>5</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L104" s="1">
+        <v>100</v>
+      </c>
+      <c r="M104" s="6">
+        <v>1</v>
+      </c>
+      <c r="N104" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O104" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -5372,28 +5892,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -5644,32 +6142,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5686,4 +6181,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{370AD02E-4819-4E2C-ABA1-ADBCE76976F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D11FECCD-A1E0-428A-B8FE-E954922ED624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="17970" windowHeight="13360" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="440" yWindow="660" windowWidth="21170" windowHeight="12630" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="59">
   <si>
     <t>AssociateName</t>
   </si>
@@ -144,6 +144,9 @@
     <t>Breanna Stringfellow</t>
   </si>
   <si>
+    <t>May</t>
+  </si>
+  <si>
     <t>ManagerName</t>
   </si>
   <si>
@@ -211,9 +214,6 @@
   </si>
   <si>
     <t>Thomas.Gordon@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>May</t>
   </si>
 </sst>
 </file>
@@ -328,8 +328,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O104" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:O104" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:O113" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:O113" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -682,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -5110,11 +5110,11 @@
       <c r="L94" s="1">
         <v>100</v>
       </c>
-      <c r="M94" s="6">
+      <c r="M94" s="2">
         <v>1</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="O94" s="1">
         <v>2026</v>
@@ -5157,11 +5157,11 @@
       <c r="L95" s="1">
         <v>100</v>
       </c>
-      <c r="M95" s="6">
+      <c r="M95" s="2">
         <v>1</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="O95" s="1">
         <v>2026</v>
@@ -5204,11 +5204,11 @@
       <c r="L96" s="1">
         <v>100</v>
       </c>
-      <c r="M96" s="6">
+      <c r="M96" s="2">
         <v>1</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="O96" s="1">
         <v>2026</v>
@@ -5251,11 +5251,11 @@
       <c r="L97" s="1">
         <v>100</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M97" s="2">
         <v>1</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="O97" s="1">
         <v>2026</v>
@@ -5298,11 +5298,11 @@
       <c r="L98" s="1">
         <v>100</v>
       </c>
-      <c r="M98" s="6">
+      <c r="M98" s="2">
         <v>1</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="O98" s="1">
         <v>2026</v>
@@ -5345,11 +5345,11 @@
       <c r="L99" s="1">
         <v>100</v>
       </c>
-      <c r="M99" s="6">
+      <c r="M99" s="2">
         <v>1</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="O99" s="1">
         <v>2026</v>
@@ -5392,11 +5392,11 @@
       <c r="L100" s="1">
         <v>100</v>
       </c>
-      <c r="M100" s="6">
+      <c r="M100" s="2">
         <v>1</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="O100" s="1">
         <v>2026</v>
@@ -5439,11 +5439,11 @@
       <c r="L101" s="1">
         <v>100</v>
       </c>
-      <c r="M101" s="6">
+      <c r="M101" s="2">
         <v>1</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="O101" s="1">
         <v>2026</v>
@@ -5486,11 +5486,11 @@
       <c r="L102" s="1">
         <v>90</v>
       </c>
-      <c r="M102" s="6">
+      <c r="M102" s="2">
         <v>0.9</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="O102" s="1">
         <v>2026</v>
@@ -5533,11 +5533,11 @@
       <c r="L103" s="1">
         <v>100</v>
       </c>
-      <c r="M103" s="6">
+      <c r="M103" s="2">
         <v>1</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="O103" s="1">
         <v>2026</v>
@@ -5580,13 +5580,436 @@
       <c r="L104" s="1">
         <v>100</v>
       </c>
-      <c r="M104" s="6">
+      <c r="M104" s="2">
         <v>1</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="O104" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" s="5">
+        <v>46154</v>
+      </c>
+      <c r="D105" s="1">
+        <v>5</v>
+      </c>
+      <c r="E105" s="1">
+        <v>20</v>
+      </c>
+      <c r="F105" s="1">
+        <v>30</v>
+      </c>
+      <c r="G105" s="1">
+        <v>20</v>
+      </c>
+      <c r="H105" s="1">
+        <v>20</v>
+      </c>
+      <c r="I105" s="1">
+        <v>5</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L105" s="1">
+        <v>100</v>
+      </c>
+      <c r="M105" s="6">
+        <v>1</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O105" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A106" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" s="5">
+        <v>46154</v>
+      </c>
+      <c r="D106" s="1">
+        <v>5</v>
+      </c>
+      <c r="E106" s="1">
+        <v>20</v>
+      </c>
+      <c r="F106" s="1">
+        <v>30</v>
+      </c>
+      <c r="G106" s="1">
+        <v>20</v>
+      </c>
+      <c r="H106" s="1">
+        <v>20</v>
+      </c>
+      <c r="I106" s="1">
+        <v>5</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L106" s="1">
+        <v>100</v>
+      </c>
+      <c r="M106" s="6">
+        <v>1</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O106" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A107" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" s="5">
+        <v>46156</v>
+      </c>
+      <c r="D107" s="1">
+        <v>5</v>
+      </c>
+      <c r="E107" s="1">
+        <v>15</v>
+      </c>
+      <c r="F107" s="1">
+        <v>30</v>
+      </c>
+      <c r="G107" s="1">
+        <v>20</v>
+      </c>
+      <c r="H107" s="1">
+        <v>20</v>
+      </c>
+      <c r="I107" s="1">
+        <v>5</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L107" s="1">
+        <v>95</v>
+      </c>
+      <c r="M107" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="N107" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O107" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A108" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" s="5">
+        <v>46157</v>
+      </c>
+      <c r="D108" s="1">
+        <v>5</v>
+      </c>
+      <c r="E108" s="1">
+        <v>20</v>
+      </c>
+      <c r="F108" s="1">
+        <v>30</v>
+      </c>
+      <c r="G108" s="1">
+        <v>20</v>
+      </c>
+      <c r="H108" s="1">
+        <v>20</v>
+      </c>
+      <c r="I108" s="1">
+        <v>5</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L108" s="1">
+        <v>100</v>
+      </c>
+      <c r="M108" s="6">
+        <v>1</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O108" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" s="5">
+        <v>46155</v>
+      </c>
+      <c r="D109" s="1">
+        <v>5</v>
+      </c>
+      <c r="E109" s="1">
+        <v>20</v>
+      </c>
+      <c r="F109" s="1">
+        <v>30</v>
+      </c>
+      <c r="G109" s="1">
+        <v>20</v>
+      </c>
+      <c r="H109" s="1">
+        <v>20</v>
+      </c>
+      <c r="I109" s="1">
+        <v>5</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L109" s="1">
+        <v>100</v>
+      </c>
+      <c r="M109" s="6">
+        <v>1</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O109" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A110" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" s="5">
+        <v>46153</v>
+      </c>
+      <c r="D110" s="1">
+        <v>5</v>
+      </c>
+      <c r="E110" s="1">
+        <v>20</v>
+      </c>
+      <c r="F110" s="1">
+        <v>30</v>
+      </c>
+      <c r="G110" s="1">
+        <v>20</v>
+      </c>
+      <c r="H110" s="1">
+        <v>20</v>
+      </c>
+      <c r="I110" s="1">
+        <v>0</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L110" s="1">
+        <v>95</v>
+      </c>
+      <c r="M110" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="N110" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O110" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A111" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C111" s="5">
+        <v>46150</v>
+      </c>
+      <c r="D111" s="1">
+        <v>5</v>
+      </c>
+      <c r="E111" s="1">
+        <v>20</v>
+      </c>
+      <c r="F111" s="1">
+        <v>30</v>
+      </c>
+      <c r="G111" s="1">
+        <v>20</v>
+      </c>
+      <c r="H111" s="1">
+        <v>20</v>
+      </c>
+      <c r="I111" s="1">
+        <v>5</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L111" s="1">
+        <v>100</v>
+      </c>
+      <c r="M111" s="6">
+        <v>1</v>
+      </c>
+      <c r="N111" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O111" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" s="5">
+        <v>46155</v>
+      </c>
+      <c r="D112" s="1">
+        <v>5</v>
+      </c>
+      <c r="E112" s="1">
+        <v>20</v>
+      </c>
+      <c r="F112" s="1">
+        <v>30</v>
+      </c>
+      <c r="G112" s="1">
+        <v>20</v>
+      </c>
+      <c r="H112" s="1">
+        <v>20</v>
+      </c>
+      <c r="I112" s="1">
+        <v>5</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L112" s="1">
+        <v>100</v>
+      </c>
+      <c r="M112" s="6">
+        <v>1</v>
+      </c>
+      <c r="N112" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O112" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A113" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C113" s="5">
+        <v>46157</v>
+      </c>
+      <c r="D113" s="1">
+        <v>5</v>
+      </c>
+      <c r="E113" s="1">
+        <v>10</v>
+      </c>
+      <c r="F113" s="1">
+        <v>15</v>
+      </c>
+      <c r="G113" s="1">
+        <v>20</v>
+      </c>
+      <c r="H113" s="1">
+        <v>0</v>
+      </c>
+      <c r="I113" s="1">
+        <v>5</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L113" s="1">
+        <v>0</v>
+      </c>
+      <c r="M113" s="6">
+        <v>0</v>
+      </c>
+      <c r="N113" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O113" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -5618,13 +6041,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -5635,13 +6058,13 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -5652,13 +6075,13 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -5669,13 +6092,13 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -5686,13 +6109,13 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -5703,13 +6126,13 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -5720,13 +6143,13 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -5737,13 +6160,13 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -5754,30 +6177,30 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -5788,13 +6211,13 @@
         <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -5805,13 +6228,13 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -5822,13 +6245,13 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -5839,13 +6262,13 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -5856,13 +6279,13 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -5873,13 +6296,13 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -6143,6 +6566,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
@@ -6153,15 +6585,6 @@
     <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6184,26 +6607,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE995F87-077E-421A-B111-DDF4989CB468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-130" yWindow="0" windowWidth="19290" windowHeight="13670" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="8760" yWindow="4305" windowWidth="38700" windowHeight="15225" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -662,20 +662,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
   <dimension ref="A1:I98"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.54296875" customWidth="1"/>
-    <col min="2" max="2" width="18.7265625" customWidth="1"/>
-    <col min="3" max="3" width="15.1796875" customWidth="1"/>
-    <col min="4" max="4" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.1796875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" style="3" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -704,7 +704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
@@ -733,7 +733,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -762,7 +762,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -791,7 +791,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -820,7 +820,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -849,7 +849,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -878,7 +878,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -907,7 +907,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -936,7 +936,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -965,7 +965,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -994,7 +994,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>27</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>13</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>18</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>15</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>16</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>16</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>23</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>24</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>27</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>22</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>20</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>9</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>25</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>17</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>18</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>13</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>26</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>24</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>25</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>9</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>23</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>22</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>15</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>20</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>27</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>15</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>9</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>24</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>9</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>22</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>25</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>26</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>27</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>16</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>23</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>20</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>17</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>18</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>13</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>15</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>26</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>17</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>27</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>23</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>20</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>24</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>13</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>22</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>16</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>17</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>18</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>18</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>16</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>15</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>24</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>27</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>20</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>13</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>18</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>26</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>16</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>23</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>18</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>15</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>15</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>22</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>16</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>17</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>15</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>17</v>
       </c>
@@ -3529,15 +3529,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324C68B5-B5AE-49F4-BF99-B0AAB6EC270F}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="32.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -3605,7 +3605,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -3639,7 +3639,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3819,6 +3819,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -4069,19 +4082,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -4092,6 +4092,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4110,23 +4127,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE995F87-077E-421A-B111-DDF4989CB468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716AD3BD-E99B-433C-A88F-ADF341FD66BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8760" yWindow="4305" windowWidth="38700" windowHeight="15225" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="14310" yWindow="90" windowWidth="36075" windowHeight="19665" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="52">
   <si>
     <t>AssociateName</t>
   </si>
@@ -304,11 +304,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I98" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I98" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I98">
-    <sortCondition ref="C1:C98"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I102" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I102" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -326,13 +323,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}" name="tblAssociateReference" displayName="tblAssociateReference" ref="A1:E16" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:E16" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Katie"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E16" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8E0548F5-70FF-454C-A4FF-1E3FA7D9C27E}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{E9A01728-B3EB-48F3-9A95-B8C7D6681247}" name="ManagerTeam"/>
@@ -661,18 +652,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="6" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18" style="3" customWidth="1"/>
+    <col min="8" max="8" width="20.5703125" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -706,13 +696,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="5">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>12</v>
@@ -721,10 +711,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G2" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>21</v>
@@ -735,13 +725,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="5">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>12</v>
@@ -750,10 +740,10 @@
         <v>11</v>
       </c>
       <c r="F3" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G3" s="2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>21</v>
@@ -764,13 +754,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4" s="5">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>12</v>
@@ -779,10 +769,10 @@
         <v>11</v>
       </c>
       <c r="F4" s="1">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G4" s="2">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>21</v>
@@ -793,13 +783,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>12</v>
@@ -808,10 +798,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>21</v>
@@ -822,10 +812,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5">
         <v>46113</v>
@@ -851,13 +841,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C7" s="5">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>12</v>
@@ -866,10 +856,10 @@
         <v>11</v>
       </c>
       <c r="F7" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>21</v>
@@ -880,13 +870,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>12</v>
@@ -909,25 +899,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9" s="5">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G9" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>21</v>
@@ -938,25 +928,25 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5">
-        <v>46118</v>
+        <v>46121</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>21</v>
@@ -967,25 +957,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" s="5">
-        <v>46118</v>
+        <v>46127</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>21</v>
@@ -996,25 +986,25 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="5">
-        <v>46119</v>
+        <v>46128</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>21</v>
@@ -1025,13 +1015,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="5">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>12</v>
@@ -1040,10 +1030,10 @@
         <v>11</v>
       </c>
       <c r="F13" s="1">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G13" s="2">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>21</v>
@@ -1054,13 +1044,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C14" s="5">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>12</v>
@@ -1083,13 +1073,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="5">
-        <v>46120</v>
+        <v>46128</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>12</v>
@@ -1098,10 +1088,10 @@
         <v>11</v>
       </c>
       <c r="F15" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G15" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>21</v>
@@ -1112,13 +1102,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>12</v>
@@ -1141,25 +1131,25 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>46120</v>
+        <v>46128</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>21</v>
@@ -1170,16 +1160,16 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>12</v>
@@ -1199,25 +1189,25 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="5">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>21</v>
@@ -1228,25 +1218,25 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C20" s="5">
-        <v>46121</v>
+        <v>46129</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G20" s="2">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>21</v>
@@ -1257,13 +1247,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="5">
-        <v>46121</v>
+        <v>46126</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>12</v>
@@ -1286,13 +1276,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="5">
-        <v>46121</v>
+        <v>46114</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>12</v>
@@ -1315,13 +1305,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="5">
-        <v>46122</v>
+        <v>46129</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>12</v>
@@ -1330,10 +1320,10 @@
         <v>11</v>
       </c>
       <c r="F23" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G23" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>21</v>
@@ -1350,7 +1340,7 @@
         <v>14</v>
       </c>
       <c r="C24" s="5">
-        <v>46122</v>
+        <v>46113</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>12</v>
@@ -1359,10 +1349,10 @@
         <v>11</v>
       </c>
       <c r="F24" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G24" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>21</v>
@@ -1379,7 +1369,7 @@
         <v>14</v>
       </c>
       <c r="C25" s="5">
-        <v>46122</v>
+        <v>46118</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>12</v>
@@ -1388,10 +1378,10 @@
         <v>11</v>
       </c>
       <c r="F25" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G25" s="2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>21</v>
@@ -1402,13 +1392,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C26" s="5">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>12</v>
@@ -1417,10 +1407,10 @@
         <v>11</v>
       </c>
       <c r="F26" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>21</v>
@@ -1431,25 +1421,25 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C27" s="5">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G27" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>21</v>
@@ -1460,13 +1450,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C28" s="5">
-        <v>46126</v>
+        <v>46121</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>12</v>
@@ -1489,13 +1479,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C29" s="5">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>12</v>
@@ -1504,10 +1494,10 @@
         <v>11</v>
       </c>
       <c r="F29" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G29" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>21</v>
@@ -1518,16 +1508,16 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>46126</v>
+        <v>46135</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>11</v>
@@ -1547,25 +1537,25 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C31" s="5">
-        <v>46127</v>
+        <v>46113</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>21</v>
@@ -1576,13 +1566,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>12</v>
@@ -1605,13 +1595,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>12</v>
@@ -1634,13 +1624,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C34" s="5">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>12</v>
@@ -1663,25 +1653,25 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C35" s="5">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>21</v>
@@ -1692,13 +1682,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>12</v>
@@ -1721,25 +1711,25 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>46128</v>
+        <v>46133</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>21</v>
@@ -1750,25 +1740,25 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C38" s="5">
-        <v>46128</v>
+        <v>46113</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>21</v>
@@ -1779,13 +1769,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C39" s="5">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>12</v>
@@ -1794,10 +1784,10 @@
         <v>11</v>
       </c>
       <c r="F39" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G39" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>21</v>
@@ -1808,13 +1798,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C40" s="5">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>12</v>
@@ -1837,25 +1827,25 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C41" s="5">
-        <v>46129</v>
+        <v>46134</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>21</v>
@@ -1866,13 +1856,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C42" s="5">
-        <v>46133</v>
+        <v>46113</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>12</v>
@@ -1895,13 +1885,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C43" s="5">
-        <v>46134</v>
+        <v>46118</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>12</v>
@@ -1910,10 +1900,10 @@
         <v>11</v>
       </c>
       <c r="F43" s="1">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G43" s="2">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>21</v>
@@ -1924,13 +1914,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C44" s="5">
-        <v>46134</v>
+        <v>46122</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>12</v>
@@ -1939,10 +1929,10 @@
         <v>11</v>
       </c>
       <c r="F44" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G44" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>21</v>
@@ -1953,25 +1943,25 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C45" s="5">
-        <v>46134</v>
+        <v>46119</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>21</v>
@@ -1982,25 +1972,25 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C46" s="5">
-        <v>46135</v>
+        <v>46122</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F46" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G46" s="2">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>21</v>
@@ -2011,16 +2001,16 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C47" s="5">
         <v>46135</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>11</v>
@@ -2040,25 +2030,25 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C48" s="5">
-        <v>46135</v>
+        <v>46120</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F48" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>21</v>
@@ -2069,13 +2059,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C49" s="5">
-        <v>46135</v>
+        <v>46122</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>12</v>
@@ -2098,13 +2088,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C50" s="5">
-        <v>46135</v>
+        <v>46122</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>12</v>
@@ -2127,16 +2117,16 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C51" s="5">
-        <v>46135</v>
+        <v>46121</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>11</v>
@@ -2156,25 +2146,25 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C52" s="5">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F52" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>21</v>
@@ -2185,13 +2175,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C53" s="5">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>12</v>
@@ -2214,7 +2204,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>10</v>
@@ -2229,10 +2219,10 @@
         <v>11</v>
       </c>
       <c r="F54" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G54" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>21</v>
@@ -2243,7 +2233,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>10</v>
@@ -2252,16 +2242,16 @@
         <v>46141</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F55" s="1">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G55" s="2">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>21</v>
@@ -2272,7 +2262,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>10</v>
@@ -2281,16 +2271,16 @@
         <v>46141</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F56" s="1">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G56" s="2">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>21</v>
@@ -2301,13 +2291,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="5">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>12</v>
@@ -2359,13 +2349,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C59" s="5">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>12</v>
@@ -2374,10 +2364,10 @@
         <v>11</v>
       </c>
       <c r="F59" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G59" s="2">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>21</v>
@@ -2388,25 +2378,25 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="5">
-        <v>46142</v>
+        <v>46135</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G60" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>21</v>
@@ -2417,10 +2407,10 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C61" s="5">
         <v>46142</v>
@@ -2446,13 +2436,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C62" s="5">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>12</v>
@@ -2461,10 +2451,10 @@
         <v>11</v>
       </c>
       <c r="F62" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G62" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>21</v>
@@ -2591,13 +2581,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="5">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>12</v>
@@ -2620,13 +2610,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C68" s="5">
-        <v>46143</v>
+        <v>46148</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>12</v>
@@ -2649,7 +2639,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>10</v>
@@ -2678,13 +2668,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="5">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>12</v>
@@ -2707,13 +2697,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="5">
-        <v>46148</v>
+        <v>46143</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>12</v>
@@ -2765,13 +2755,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C73" s="5">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>12</v>
@@ -2794,10 +2784,10 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C74" s="5">
         <v>46149</v>
@@ -2823,7 +2813,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>14</v>
@@ -2838,10 +2828,10 @@
         <v>11</v>
       </c>
       <c r="F75" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G75" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>28</v>
@@ -2852,7 +2842,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>14</v>
@@ -2881,13 +2871,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C77" s="5">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>12</v>
@@ -2896,10 +2886,10 @@
         <v>11</v>
       </c>
       <c r="F77" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G77" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>28</v>
@@ -2910,13 +2900,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C78" s="5">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>12</v>
@@ -2939,13 +2929,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C79" s="5">
-        <v>46149</v>
+        <v>46154</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>12</v>
@@ -2968,13 +2958,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C80" s="5">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>12</v>
@@ -2983,10 +2973,10 @@
         <v>11</v>
       </c>
       <c r="F80" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G80" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>28</v>
@@ -2997,13 +2987,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C81" s="5">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>12</v>
@@ -3026,13 +3016,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="5">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>12</v>
@@ -3041,10 +3031,10 @@
         <v>11</v>
       </c>
       <c r="F82" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G82" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>28</v>
@@ -3055,13 +3045,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="5">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>12</v>
@@ -3070,10 +3060,10 @@
         <v>11</v>
       </c>
       <c r="F83" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G83" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>28</v>
@@ -3084,13 +3074,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C84" s="5">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>12</v>
@@ -3113,13 +3103,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C85" s="5">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>12</v>
@@ -3142,25 +3132,25 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C86" s="5">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F86" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>28</v>
@@ -3171,13 +3161,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C87" s="5">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>12</v>
@@ -3186,10 +3176,10 @@
         <v>11</v>
       </c>
       <c r="F87" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G87" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>28</v>
@@ -3200,13 +3190,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C88" s="5">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>12</v>
@@ -3229,13 +3219,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C89" s="5">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>12</v>
@@ -3258,10 +3248,10 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C90" s="5">
         <v>46156</v>
@@ -3273,10 +3263,10 @@
         <v>11</v>
       </c>
       <c r="F90" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G90" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>28</v>
@@ -3287,13 +3277,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C91" s="5">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>12</v>
@@ -3345,13 +3335,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C93" s="5">
-        <v>46156</v>
+        <v>46143</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>12</v>
@@ -3374,13 +3364,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C94" s="5">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>12</v>
@@ -3403,25 +3393,25 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C95" s="5">
-        <v>46157</v>
+        <v>46149</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G95" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>28</v>
@@ -3432,13 +3422,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C96" s="5">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>12</v>
@@ -3447,10 +3437,10 @@
         <v>11</v>
       </c>
       <c r="F96" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G96" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>28</v>
@@ -3461,13 +3451,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C97" s="5">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>12</v>
@@ -3490,13 +3480,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C98" s="5">
-        <v>46162</v>
+        <v>46149</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>12</v>
@@ -3514,6 +3504,122 @@
         <v>28</v>
       </c>
       <c r="I98" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C99" s="5">
+        <v>46148</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="1">
+        <v>100</v>
+      </c>
+      <c r="G99" s="2">
+        <v>1</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I99" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C100" s="5">
+        <v>46168</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="1">
+        <v>100</v>
+      </c>
+      <c r="G100" s="2">
+        <v>1</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I100" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C101" s="5">
+        <v>46155</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="1">
+        <v>100</v>
+      </c>
+      <c r="G101" s="2">
+        <v>1</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I101" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" s="5">
+        <v>46147</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="1">
+        <v>100</v>
+      </c>
+      <c r="G102" s="2">
+        <v>1</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I102" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -3554,7 +3660,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -3571,7 +3677,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3588,7 +3694,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -3605,7 +3711,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -3622,7 +3728,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -3639,7 +3745,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3656,7 +3762,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3775,7 +3881,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -3819,19 +3925,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -4082,6 +4175,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -4092,23 +4198,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4127,6 +4216,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716AD3BD-E99B-433C-A88F-ADF341FD66BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF891112-C2DF-4C9B-A99C-1128C0EA23E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14310" yWindow="90" windowWidth="36075" windowHeight="19665" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="15675" yWindow="0" windowWidth="36075" windowHeight="20985" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -305,7 +305,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I102" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I102" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+  <autoFilter ref="A1:I102" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Katie"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -694,7 +700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -740,10 +746,10 @@
         <v>11</v>
       </c>
       <c r="F3" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>21</v>
@@ -752,7 +758,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -781,7 +787,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -810,7 +816,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -839,7 +845,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -868,7 +874,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
@@ -897,7 +903,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>27</v>
       </c>
@@ -926,7 +932,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -955,7 +961,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -984,7 +990,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1013,7 +1019,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -1042,7 +1048,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -1071,7 +1077,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -1100,7 +1106,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
@@ -1129,7 +1135,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
@@ -1158,7 +1164,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -1187,7 +1193,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -1506,7 +1512,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>23</v>
       </c>
@@ -1564,7 +1570,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>22</v>
       </c>
@@ -1593,7 +1599,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>24</v>
       </c>
@@ -1680,7 +1686,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>25</v>
       </c>
@@ -1709,7 +1715,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>26</v>
       </c>
@@ -1767,7 +1773,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>20</v>
       </c>
@@ -1796,7 +1802,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>27</v>
       </c>
@@ -1825,7 +1831,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>9</v>
       </c>
@@ -2144,7 +2150,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>23</v>
       </c>
@@ -2173,7 +2179,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>22</v>
       </c>
@@ -2202,7 +2208,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>24</v>
       </c>
@@ -2231,7 +2237,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,7 +2266,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>26</v>
       </c>
@@ -2289,7 +2295,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,7 +2324,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>27</v>
       </c>
@@ -2347,7 +2353,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>9</v>
       </c>
@@ -2376,7 +2382,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>9</v>
       </c>
@@ -2579,7 +2585,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>27</v>
       </c>
@@ -2608,7 +2614,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>20</v>
       </c>
@@ -2637,7 +2643,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>23</v>
       </c>
@@ -2666,7 +2672,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>22</v>
       </c>
@@ -2695,7 +2701,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>26</v>
       </c>
@@ -2724,7 +2730,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>24</v>
       </c>
@@ -2898,7 +2904,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>27</v>
       </c>
@@ -2927,7 +2933,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>20</v>
       </c>
@@ -2956,7 +2962,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>23</v>
       </c>
@@ -2985,7 +2991,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>22</v>
       </c>
@@ -3014,7 +3020,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>26</v>
       </c>
@@ -3043,7 +3049,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>24</v>
       </c>
@@ -4176,6 +4182,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
@@ -4186,15 +4201,6 @@
     <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4217,6 +4223,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -4231,12 +4245,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF891112-C2DF-4C9B-A99C-1128C0EA23E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF1F5C4-1590-4E4A-BBA4-756430BA685D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15675" yWindow="0" windowWidth="36075" windowHeight="20985" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="5870" yWindow="20" windowWidth="26770" windowHeight="13520" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="52">
   <si>
     <t>AssociateName</t>
   </si>
@@ -244,7 +244,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -257,6 +257,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -304,14 +307,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I102" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I102" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Katie"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I107" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I107" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -658,20 +655,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I102"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I107"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7109375" customWidth="1"/>
-    <col min="5" max="6" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.7265625" customWidth="1"/>
+    <col min="5" max="6" width="17.453125" customWidth="1"/>
     <col min="7" max="7" width="18" style="3" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="8" max="8" width="20.54296875" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -700,7 +697,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -729,7 +726,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -758,7 +755,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -787,7 +784,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -816,7 +813,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -845,7 +842,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -874,7 +871,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
@@ -903,7 +900,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>27</v>
       </c>
@@ -932,7 +929,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -961,7 +958,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -990,7 +987,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1019,7 +1016,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -1048,7 +1045,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -1077,7 +1074,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -1106,7 +1103,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>27</v>
       </c>
@@ -1135,7 +1132,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,7 +1161,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -1193,7 +1190,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -1222,7 +1219,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
@@ -1251,7 +1248,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
@@ -1280,7 +1277,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>13</v>
       </c>
@@ -1309,7 +1306,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1338,7 +1335,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1367,7 +1364,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>18</v>
       </c>
@@ -1396,7 +1393,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>16</v>
       </c>
@@ -1425,7 +1422,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>16</v>
       </c>
@@ -1454,7 +1451,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>13</v>
       </c>
@@ -1483,7 +1480,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>13</v>
       </c>
@@ -1512,7 +1509,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>23</v>
       </c>
@@ -1541,7 +1538,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -1570,7 +1567,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>22</v>
       </c>
@@ -1599,7 +1596,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,7 +1625,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>16</v>
       </c>
@@ -1657,7 +1654,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>15</v>
       </c>
@@ -1686,7 +1683,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>25</v>
       </c>
@@ -1715,7 +1712,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>26</v>
       </c>
@@ -1744,7 +1741,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>18</v>
       </c>
@@ -1773,7 +1770,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,7 +1799,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>27</v>
       </c>
@@ -1831,7 +1828,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>9</v>
       </c>
@@ -1860,7 +1857,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
@@ -1889,7 +1886,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>17</v>
       </c>
@@ -1918,7 +1915,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>17</v>
       </c>
@@ -1947,7 +1944,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>15</v>
       </c>
@@ -1976,7 +1973,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -2005,7 +2002,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>15</v>
       </c>
@@ -2034,7 +2031,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>16</v>
       </c>
@@ -2063,7 +2060,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>18</v>
       </c>
@@ -2092,7 +2089,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>15</v>
       </c>
@@ -2121,7 +2118,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -2150,7 +2147,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,7 +2176,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>22</v>
       </c>
@@ -2208,7 +2205,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>24</v>
       </c>
@@ -2237,7 +2234,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>25</v>
       </c>
@@ -2266,7 +2263,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>26</v>
       </c>
@@ -2295,7 +2292,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>20</v>
       </c>
@@ -2324,7 +2321,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>27</v>
       </c>
@@ -2353,7 +2350,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>9</v>
       </c>
@@ -2382,7 +2379,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>9</v>
       </c>
@@ -2411,7 +2408,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -2440,7 +2437,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>16</v>
       </c>
@@ -2469,7 +2466,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>17</v>
       </c>
@@ -2498,7 +2495,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>18</v>
       </c>
@@ -2527,7 +2524,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>13</v>
       </c>
@@ -2556,7 +2553,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>15</v>
       </c>
@@ -2585,7 +2582,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>27</v>
       </c>
@@ -2614,7 +2611,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>20</v>
       </c>
@@ -2643,7 +2640,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>23</v>
       </c>
@@ -2672,7 +2669,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>22</v>
       </c>
@@ -2701,7 +2698,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>26</v>
       </c>
@@ -2730,7 +2727,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>24</v>
       </c>
@@ -2759,7 +2756,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -2788,7 +2785,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>16</v>
       </c>
@@ -2817,7 +2814,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>17</v>
       </c>
@@ -2846,7 +2843,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>18</v>
       </c>
@@ -2875,7 +2872,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>13</v>
       </c>
@@ -2904,7 +2901,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>27</v>
       </c>
@@ -2933,7 +2930,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>20</v>
       </c>
@@ -2962,7 +2959,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>23</v>
       </c>
@@ -2991,7 +2988,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>22</v>
       </c>
@@ -3020,7 +3017,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>26</v>
       </c>
@@ -3049,7 +3046,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>24</v>
       </c>
@@ -3078,7 +3075,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>15</v>
       </c>
@@ -3107,7 +3104,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -3136,7 +3133,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>16</v>
       </c>
@@ -3165,7 +3162,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>17</v>
       </c>
@@ -3194,7 +3191,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>18</v>
       </c>
@@ -3223,7 +3220,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>13</v>
       </c>
@@ -3252,7 +3249,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>15</v>
       </c>
@@ -3281,7 +3278,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>15</v>
       </c>
@@ -3310,7 +3307,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>15</v>
       </c>
@@ -3339,7 +3336,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>17</v>
       </c>
@@ -3368,7 +3365,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>17</v>
       </c>
@@ -3397,7 +3394,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>18</v>
       </c>
@@ -3426,7 +3423,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>18</v>
       </c>
@@ -3455,7 +3452,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>16</v>
       </c>
@@ -3484,7 +3481,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>16</v>
       </c>
@@ -3513,7 +3510,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -3542,7 +3539,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -3571,7 +3568,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>13</v>
       </c>
@@ -3600,7 +3597,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>13</v>
       </c>
@@ -3626,6 +3623,151 @@
         <v>28</v>
       </c>
       <c r="I102" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A103" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="5">
+        <v>46169</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" s="1">
+        <v>95</v>
+      </c>
+      <c r="G103" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I103" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A104" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="5">
+        <v>46168</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="1">
+        <v>100</v>
+      </c>
+      <c r="G104" s="6">
+        <v>1</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I104" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="5">
+        <v>46170</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F105" s="1">
+        <v>100</v>
+      </c>
+      <c r="G105" s="6">
+        <v>1</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I105" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A106" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" s="5">
+        <v>46170</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="1">
+        <v>100</v>
+      </c>
+      <c r="G106" s="6">
+        <v>1</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I106" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A107" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" s="5">
+        <v>46168</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F107" s="1">
+        <v>0</v>
+      </c>
+      <c r="G107" s="6">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I107" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -3641,15 +3783,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324C68B5-B5AE-49F4-BF99-B0AAB6EC270F}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="32.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3666,7 +3808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -3683,7 +3825,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3700,7 +3842,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -3717,7 +3859,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -3734,7 +3876,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -3751,7 +3893,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3768,7 +3910,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -3785,7 +3927,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -3802,7 +3944,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -3819,7 +3961,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3836,7 +3978,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -3853,7 +3995,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -3870,7 +4012,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -3887,7 +4029,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -3904,7 +4046,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3931,6 +4073,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -4181,15 +4332,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4204,6 +4346,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4222,27 +4372,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF1F5C4-1590-4E4A-BBA4-756430BA685D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5B7A29-6FE2-4D7F-8C68-CB8F7E8876D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5870" yWindow="20" windowWidth="26770" windowHeight="13520" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="90" yWindow="160" windowWidth="26740" windowHeight="13520" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="52">
   <si>
     <t>AssociateName</t>
   </si>
@@ -244,7 +244,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -257,9 +257,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -307,8 +304,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I107" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I107" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I113" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I113" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -655,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -3645,7 +3642,7 @@
       <c r="F103" s="1">
         <v>95</v>
       </c>
-      <c r="G103" s="6">
+      <c r="G103" s="2">
         <v>0.95</v>
       </c>
       <c r="H103" s="1" t="s">
@@ -3674,7 +3671,7 @@
       <c r="F104" s="1">
         <v>100</v>
       </c>
-      <c r="G104" s="6">
+      <c r="G104" s="2">
         <v>1</v>
       </c>
       <c r="H104" s="1" t="s">
@@ -3703,7 +3700,7 @@
       <c r="F105" s="1">
         <v>100</v>
       </c>
-      <c r="G105" s="6">
+      <c r="G105" s="2">
         <v>1</v>
       </c>
       <c r="H105" s="1" t="s">
@@ -3732,7 +3729,7 @@
       <c r="F106" s="1">
         <v>100</v>
       </c>
-      <c r="G106" s="6">
+      <c r="G106" s="2">
         <v>1</v>
       </c>
       <c r="H106" s="1" t="s">
@@ -3756,18 +3753,192 @@
         <v>12</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1">
+        <v>100</v>
+      </c>
+      <c r="G107" s="2">
+        <v>1</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I107" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A108" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108" s="5">
+        <v>46170</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="1">
+        <v>100</v>
+      </c>
+      <c r="G108" s="2">
+        <v>1</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I108" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109" s="5">
+        <v>46170</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" s="1">
         <v>0</v>
       </c>
-      <c r="G107" s="6">
+      <c r="G109" s="2">
         <v>0</v>
       </c>
-      <c r="H107" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I107" s="1">
+      <c r="H109" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I109" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A110" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110" s="5">
+        <v>46171</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F110" s="1">
+        <v>90</v>
+      </c>
+      <c r="G110" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I110" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A111" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C111" s="5">
+        <v>46171</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" s="1">
+        <v>0</v>
+      </c>
+      <c r="G111" s="2">
+        <v>0</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I111" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A112" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C112" s="5">
+        <v>46171</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="1">
+        <v>100</v>
+      </c>
+      <c r="G112" s="2">
+        <v>1</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I112" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A113" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C113" s="5">
+        <v>46170</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" s="1">
+        <v>100</v>
+      </c>
+      <c r="G113" s="2">
+        <v>1</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I113" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -4073,15 +4244,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -4332,7 +4494,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
@@ -4345,15 +4507,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4372,19 +4535,27 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5B7A29-6FE2-4D7F-8C68-CB8F7E8876D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4394C36-17A7-4EB5-9EF6-8BD5001C81FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="160" windowWidth="26740" windowHeight="13520" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="19000" yWindow="40" windowWidth="15390" windowHeight="13520" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="52">
   <si>
     <t>AssociateName</t>
   </si>
@@ -304,8 +304,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I113" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I113" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I114" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I114" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -652,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -3939,6 +3939,35 @@
         <v>28</v>
       </c>
       <c r="I113" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A114" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C114" s="5">
+        <v>46169</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="1">
+        <v>100</v>
+      </c>
+      <c r="G114" s="2">
+        <v>1</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I114" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -4538,16 +4567,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4394C36-17A7-4EB5-9EF6-8BD5001C81FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280F69CD-C803-4C98-A3D6-7276BF680D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19000" yWindow="40" windowWidth="15390" windowHeight="13520" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="790" yWindow="160" windowWidth="32080" windowHeight="13480" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="53">
   <si>
     <t>AssociateName</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>May</t>
+  </si>
+  <si>
+    <t>June</t>
   </si>
   <si>
     <t>ManagerName</t>
@@ -244,7 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -257,6 +260,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -304,8 +310,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I114" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I114" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I120" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I120" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -652,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -3968,6 +3974,180 @@
         <v>28</v>
       </c>
       <c r="I114" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A115" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C115" s="5">
+        <v>46175</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F115" s="1">
+        <v>100</v>
+      </c>
+      <c r="G115" s="2">
+        <v>1</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I115" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A116" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" s="5">
+        <v>46175</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" s="1">
+        <v>100</v>
+      </c>
+      <c r="G116" s="6">
+        <v>1</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I116" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A117" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C117" s="5">
+        <v>46176</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F117" s="1">
+        <v>90</v>
+      </c>
+      <c r="G117" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I117" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A118" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118" s="5">
+        <v>46174</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" s="1">
+        <v>100</v>
+      </c>
+      <c r="G118" s="6">
+        <v>1</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I118" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A119" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C119" s="5">
+        <v>46178</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" s="1">
+        <v>100</v>
+      </c>
+      <c r="G119" s="6">
+        <v>1</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I119" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A120" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C120" s="5">
+        <v>46174</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" s="1">
+        <v>100</v>
+      </c>
+      <c r="G120" s="6">
+        <v>1</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I120" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -3999,13 +4179,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -4016,13 +4196,13 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -4033,13 +4213,13 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -4050,13 +4230,13 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -4067,13 +4247,13 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -4084,13 +4264,13 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -4101,13 +4281,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -4118,13 +4298,13 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -4135,30 +4315,30 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -4169,13 +4349,13 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -4186,13 +4366,13 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -4203,13 +4383,13 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -4220,13 +4400,13 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -4237,13 +4417,13 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -4254,13 +4434,13 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -4273,6 +4453,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -4523,29 +4725,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4562,29 +4767,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280F69CD-C803-4C98-A3D6-7276BF680D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76E3834-F7FC-416A-AEA2-04DAD0B03CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="790" yWindow="160" windowWidth="32080" windowHeight="13480" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="490" yWindow="230" windowWidth="30620" windowHeight="13480" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="53">
   <si>
     <t>AssociateName</t>
   </si>
@@ -310,8 +310,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I120" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I120" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I126" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I126" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -658,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -4025,7 +4025,7 @@
       <c r="F116" s="1">
         <v>100</v>
       </c>
-      <c r="G116" s="6">
+      <c r="G116" s="2">
         <v>1</v>
       </c>
       <c r="H116" s="1" t="s">
@@ -4054,7 +4054,7 @@
       <c r="F117" s="1">
         <v>90</v>
       </c>
-      <c r="G117" s="6">
+      <c r="G117" s="2">
         <v>0.9</v>
       </c>
       <c r="H117" s="1" t="s">
@@ -4083,7 +4083,7 @@
       <c r="F118" s="1">
         <v>100</v>
       </c>
-      <c r="G118" s="6">
+      <c r="G118" s="2">
         <v>1</v>
       </c>
       <c r="H118" s="1" t="s">
@@ -4112,7 +4112,7 @@
       <c r="F119" s="1">
         <v>100</v>
       </c>
-      <c r="G119" s="6">
+      <c r="G119" s="2">
         <v>1</v>
       </c>
       <c r="H119" s="1" t="s">
@@ -4141,13 +4141,187 @@
       <c r="F120" s="1">
         <v>100</v>
       </c>
-      <c r="G120" s="6">
+      <c r="G120" s="2">
         <v>1</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I120" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A121" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C121" s="5">
+        <v>46178</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="1">
+        <v>100</v>
+      </c>
+      <c r="G121" s="6">
+        <v>1</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I121" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A122" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C122" s="5">
+        <v>46178</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="1">
+        <v>100</v>
+      </c>
+      <c r="G122" s="6">
+        <v>1</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I122" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A123" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C123" s="5">
+        <v>46178</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="1">
+        <v>90</v>
+      </c>
+      <c r="G123" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I123" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A124" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C124" s="5">
+        <v>46177</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F124" s="1">
+        <v>100</v>
+      </c>
+      <c r="G124" s="6">
+        <v>1</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I124" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A125" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C125" s="5">
+        <v>46178</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F125" s="1">
+        <v>95</v>
+      </c>
+      <c r="G125" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I125" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A126" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C126" s="5">
+        <v>46178</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" s="1">
+        <v>100</v>
+      </c>
+      <c r="G126" s="6">
+        <v>1</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I126" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -4453,28 +4627,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -4725,32 +4877,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4767,4 +4916,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76E3834-F7FC-416A-AEA2-04DAD0B03CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE27928-E5AA-4D7C-854E-46F55DC843ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="490" yWindow="230" windowWidth="30620" windowHeight="13480" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="690" yWindow="220" windowWidth="23680" windowHeight="13140" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="53">
   <si>
     <t>AssociateName</t>
   </si>
@@ -247,7 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -260,9 +260,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -310,8 +307,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I126" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I126" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I134" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I134" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I134">
+    <sortCondition ref="C1:C134"/>
+  </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
@@ -658,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I126"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -702,13 +702,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="5">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>12</v>
@@ -717,10 +717,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>21</v>
@@ -731,13 +731,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="5">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>12</v>
@@ -760,13 +760,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C4" s="5">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>12</v>
@@ -775,10 +775,10 @@
         <v>11</v>
       </c>
       <c r="F4" s="1">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>21</v>
@@ -789,13 +789,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C5" s="5">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>12</v>
@@ -804,10 +804,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>21</v>
@@ -818,10 +818,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6" s="5">
         <v>46113</v>
@@ -847,13 +847,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C7" s="5">
-        <v>46120</v>
+        <v>46114</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>12</v>
@@ -876,13 +876,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C8" s="5">
-        <v>46121</v>
+        <v>46114</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>12</v>
@@ -905,25 +905,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5">
-        <v>46120</v>
+        <v>46114</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G9" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>21</v>
@@ -934,25 +934,25 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C10" s="5">
-        <v>46121</v>
+        <v>46118</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G10" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>21</v>
@@ -963,25 +963,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C11" s="5">
-        <v>46127</v>
+        <v>46118</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>21</v>
@@ -992,25 +992,25 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="5">
-        <v>46128</v>
+        <v>46119</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G12" s="2">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>21</v>
@@ -1021,13 +1021,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="5">
-        <v>46127</v>
+        <v>46119</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>12</v>
@@ -1036,10 +1036,10 @@
         <v>11</v>
       </c>
       <c r="F13" s="1">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G13" s="2">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>21</v>
@@ -1050,13 +1050,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C14" s="5">
-        <v>46127</v>
+        <v>46119</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>12</v>
@@ -1079,13 +1079,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="5">
-        <v>46128</v>
+        <v>46120</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>12</v>
@@ -1094,10 +1094,10 @@
         <v>11</v>
       </c>
       <c r="F15" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>21</v>
@@ -1108,13 +1108,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>12</v>
@@ -1137,25 +1137,25 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>46128</v>
+        <v>46120</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G17" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>21</v>
@@ -1166,16 +1166,16 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C18" s="5">
-        <v>46125</v>
+        <v>46120</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>12</v>
@@ -1195,25 +1195,25 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="5">
-        <v>46128</v>
+        <v>46121</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>21</v>
@@ -1224,25 +1224,25 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C20" s="5">
-        <v>46129</v>
+        <v>46121</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>21</v>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="5">
-        <v>46126</v>
+        <v>46121</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>12</v>
@@ -1282,13 +1282,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="5">
-        <v>46114</v>
+        <v>46121</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>12</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="5">
-        <v>46129</v>
+        <v>46122</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>12</v>
@@ -1326,10 +1326,10 @@
         <v>11</v>
       </c>
       <c r="F23" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G23" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>21</v>
@@ -1346,7 +1346,7 @@
         <v>14</v>
       </c>
       <c r="C24" s="5">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>12</v>
@@ -1355,10 +1355,10 @@
         <v>11</v>
       </c>
       <c r="F24" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G24" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>21</v>
@@ -1375,7 +1375,7 @@
         <v>14</v>
       </c>
       <c r="C25" s="5">
-        <v>46118</v>
+        <v>46122</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>12</v>
@@ -1384,10 +1384,10 @@
         <v>11</v>
       </c>
       <c r="F25" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G25" s="2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>21</v>
@@ -1398,13 +1398,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C26" s="5">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>12</v>
@@ -1413,10 +1413,10 @@
         <v>11</v>
       </c>
       <c r="F26" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G26" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>21</v>
@@ -1427,25 +1427,25 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C27" s="5">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>21</v>
@@ -1456,13 +1456,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C28" s="5">
-        <v>46121</v>
+        <v>46126</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>12</v>
@@ -1485,13 +1485,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C29" s="5">
-        <v>46129</v>
+        <v>46126</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>12</v>
@@ -1500,10 +1500,10 @@
         <v>11</v>
       </c>
       <c r="F29" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G29" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>21</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C30" s="5">
-        <v>46135</v>
+        <v>46126</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>11</v>
@@ -1543,25 +1543,25 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>46113</v>
+        <v>46127</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>21</v>
@@ -1572,13 +1572,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>46135</v>
+        <v>46127</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>12</v>
@@ -1601,13 +1601,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>46134</v>
+        <v>46127</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>12</v>
@@ -1630,13 +1630,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>46114</v>
+        <v>46127</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>12</v>
@@ -1659,25 +1659,25 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>46135</v>
+        <v>46128</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>21</v>
@@ -1688,13 +1688,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>46134</v>
+        <v>46128</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>12</v>
@@ -1717,25 +1717,25 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>46133</v>
+        <v>46128</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>21</v>
@@ -1746,25 +1746,25 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>46113</v>
+        <v>46128</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>21</v>
@@ -1775,13 +1775,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C39" s="5">
-        <v>46135</v>
+        <v>46129</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>12</v>
@@ -1790,10 +1790,10 @@
         <v>11</v>
       </c>
       <c r="F39" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G39" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>21</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C40" s="5">
-        <v>46135</v>
+        <v>46129</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>12</v>
@@ -1833,25 +1833,25 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C41" s="5">
-        <v>46134</v>
+        <v>46129</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>21</v>
@@ -1862,13 +1862,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C42" s="5">
-        <v>46113</v>
+        <v>46133</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>12</v>
@@ -1891,13 +1891,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C43" s="5">
-        <v>46118</v>
+        <v>46134</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>12</v>
@@ -1906,10 +1906,10 @@
         <v>11</v>
       </c>
       <c r="F43" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G43" s="2">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>21</v>
@@ -1920,13 +1920,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C44" s="5">
-        <v>46122</v>
+        <v>46134</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>12</v>
@@ -1935,10 +1935,10 @@
         <v>11</v>
       </c>
       <c r="F44" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G44" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>21</v>
@@ -1949,25 +1949,25 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C45" s="5">
-        <v>46119</v>
+        <v>46134</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>21</v>
@@ -1978,25 +1978,25 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C46" s="5">
-        <v>46122</v>
+        <v>46135</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F46" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G46" s="2">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>21</v>
@@ -2007,16 +2007,16 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C47" s="5">
         <v>46135</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>11</v>
@@ -2036,25 +2036,25 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C48" s="5">
-        <v>46120</v>
+        <v>46135</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>21</v>
@@ -2065,13 +2065,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C49" s="5">
-        <v>46122</v>
+        <v>46135</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>12</v>
@@ -2094,13 +2094,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C50" s="5">
-        <v>46122</v>
+        <v>46135</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>12</v>
@@ -2123,16 +2123,16 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C51" s="5">
-        <v>46121</v>
+        <v>46135</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>11</v>
@@ -2152,25 +2152,25 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C52" s="5">
-        <v>46142</v>
+        <v>46135</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F52" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>21</v>
@@ -2181,13 +2181,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C53" s="5">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>12</v>
@@ -2210,7 +2210,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>10</v>
@@ -2225,10 +2225,10 @@
         <v>11</v>
       </c>
       <c r="F54" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G54" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>21</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>10</v>
@@ -2248,16 +2248,16 @@
         <v>46141</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F55" s="1">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G55" s="2">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>21</v>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>10</v>
@@ -2277,16 +2277,16 @@
         <v>46141</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F56" s="1">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G56" s="2">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>21</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C57" s="5">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>12</v>
@@ -2355,13 +2355,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C59" s="5">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>12</v>
@@ -2370,10 +2370,10 @@
         <v>11</v>
       </c>
       <c r="F59" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G59" s="2">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>21</v>
@@ -2384,25 +2384,25 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="5">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G60" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>21</v>
@@ -2413,10 +2413,10 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C61" s="5">
         <v>46142</v>
@@ -2442,13 +2442,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C62" s="5">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>12</v>
@@ -2457,10 +2457,10 @@
         <v>11</v>
       </c>
       <c r="F62" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G62" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>21</v>
@@ -2587,13 +2587,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="5">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>12</v>
@@ -2616,13 +2616,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C68" s="5">
-        <v>46148</v>
+        <v>46143</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>12</v>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>10</v>
@@ -2674,13 +2674,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="5">
-        <v>46149</v>
+        <v>46147</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>12</v>
@@ -2703,13 +2703,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C71" s="5">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>12</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>10</v>
@@ -2761,13 +2761,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C73" s="5">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>12</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C74" s="5">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>12</v>
@@ -2819,13 +2819,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C75" s="5">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>12</v>
@@ -2834,10 +2834,10 @@
         <v>11</v>
       </c>
       <c r="F75" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G75" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>28</v>
@@ -2848,10 +2848,10 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C76" s="5">
         <v>46149</v>
@@ -2877,13 +2877,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C77" s="5">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>12</v>
@@ -2906,13 +2906,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C78" s="5">
-        <v>46154</v>
+        <v>46149</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>12</v>
@@ -2935,13 +2935,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C79" s="5">
-        <v>46154</v>
+        <v>46149</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>12</v>
@@ -2950,10 +2950,10 @@
         <v>11</v>
       </c>
       <c r="F79" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G79" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>28</v>
@@ -2964,13 +2964,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C80" s="5">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>12</v>
@@ -2979,10 +2979,10 @@
         <v>11</v>
       </c>
       <c r="F80" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G80" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>28</v>
@@ -2993,13 +2993,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C81" s="5">
-        <v>46157</v>
+        <v>46149</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>12</v>
@@ -3022,13 +3022,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C82" s="5">
-        <v>46155</v>
+        <v>46149</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>12</v>
@@ -3051,13 +3051,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C83" s="5">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>12</v>
@@ -3066,10 +3066,10 @@
         <v>11</v>
       </c>
       <c r="F83" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G83" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>28</v>
@@ -3080,13 +3080,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C84" s="5">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>12</v>
@@ -3095,10 +3095,10 @@
         <v>11</v>
       </c>
       <c r="F84" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G84" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>28</v>
@@ -3109,13 +3109,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C85" s="5">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>12</v>
@@ -3138,25 +3138,25 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C86" s="5">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F86" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G86" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>28</v>
@@ -3167,13 +3167,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C87" s="5">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>12</v>
@@ -3182,10 +3182,10 @@
         <v>11</v>
       </c>
       <c r="F87" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G87" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>28</v>
@@ -3202,7 +3202,7 @@
         <v>14</v>
       </c>
       <c r="C88" s="5">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>12</v>
@@ -3225,13 +3225,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C89" s="5">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>12</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C90" s="5">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>12</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C91" s="5">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>12</v>
@@ -3312,13 +3312,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C92" s="5">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>12</v>
@@ -3341,13 +3341,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C93" s="5">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>12</v>
@@ -3356,10 +3356,10 @@
         <v>11</v>
       </c>
       <c r="F93" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G93" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>28</v>
@@ -3370,13 +3370,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C94" s="5">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>12</v>
@@ -3399,13 +3399,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C95" s="5">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>12</v>
@@ -3428,13 +3428,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C96" s="5">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>12</v>
@@ -3457,13 +3457,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C97" s="5">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>12</v>
@@ -3492,19 +3492,19 @@
         <v>14</v>
       </c>
       <c r="C98" s="5">
-        <v>46149</v>
+        <v>46157</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F98" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G98" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>28</v>
@@ -3515,13 +3515,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C99" s="5">
-        <v>46148</v>
+        <v>46157</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>12</v>
@@ -3530,10 +3530,10 @@
         <v>11</v>
       </c>
       <c r="F99" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G99" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>28</v>
@@ -3544,13 +3544,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C100" s="5">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>12</v>
@@ -3573,13 +3573,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C101" s="5">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>12</v>
@@ -3602,13 +3602,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C102" s="5">
-        <v>46147</v>
+        <v>46168</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>12</v>
@@ -3631,25 +3631,25 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C103" s="5">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F103" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G103" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>28</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>10</v>
@@ -3689,25 +3689,25 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C105" s="5">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F105" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G105" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>28</v>
@@ -3718,16 +3718,16 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C106" s="5">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>11</v>
@@ -3747,13 +3747,13 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C107" s="5">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>12</v>
@@ -3776,16 +3776,16 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C108" s="5">
         <v>46170</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>11</v>
@@ -3805,7 +3805,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>14</v>
@@ -3817,13 +3817,13 @@
         <v>12</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G109" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>28</v>
@@ -3834,25 +3834,25 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C110" s="5">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F110" s="1">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G110" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>28</v>
@@ -3863,25 +3863,25 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C111" s="5">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F111" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>28</v>
@@ -3892,7 +3892,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>14</v>
@@ -3907,10 +3907,10 @@
         <v>11</v>
       </c>
       <c r="F112" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G112" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>28</v>
@@ -3921,25 +3921,25 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C113" s="5">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F113" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G113" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>28</v>
@@ -3950,13 +3950,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C114" s="5">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>12</v>
@@ -3979,13 +3979,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C115" s="5">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>12</v>
@@ -4008,13 +4008,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C116" s="5">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>12</v>
@@ -4037,13 +4037,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C117" s="5">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>12</v>
@@ -4052,10 +4052,10 @@
         <v>11</v>
       </c>
       <c r="F117" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G117" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>29</v>
@@ -4066,13 +4066,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C118" s="5">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>12</v>
@@ -4095,13 +4095,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C119" s="5">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>12</v>
@@ -4110,10 +4110,10 @@
         <v>11</v>
       </c>
       <c r="F119" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G119" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>29</v>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C120" s="5">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>12</v>
@@ -4153,10 +4153,10 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C121" s="5">
         <v>46178</v>
@@ -4170,7 +4170,7 @@
       <c r="F121" s="1">
         <v>100</v>
       </c>
-      <c r="G121" s="6">
+      <c r="G121" s="2">
         <v>1</v>
       </c>
       <c r="H121" s="1" t="s">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>10</v>
@@ -4199,7 +4199,7 @@
       <c r="F122" s="1">
         <v>100</v>
       </c>
-      <c r="G122" s="6">
+      <c r="G122" s="2">
         <v>1</v>
       </c>
       <c r="H122" s="1" t="s">
@@ -4211,7 +4211,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>10</v>
@@ -4226,10 +4226,10 @@
         <v>11</v>
       </c>
       <c r="F123" s="1">
-        <v>90</v>
-      </c>
-      <c r="G123" s="6">
-        <v>0.9</v>
+        <v>100</v>
+      </c>
+      <c r="G123" s="2">
+        <v>1</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>29</v>
@@ -4240,13 +4240,13 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C124" s="5">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>12</v>
@@ -4255,10 +4255,10 @@
         <v>11</v>
       </c>
       <c r="F124" s="1">
-        <v>100</v>
-      </c>
-      <c r="G124" s="6">
-        <v>1</v>
+        <v>90</v>
+      </c>
+      <c r="G124" s="2">
+        <v>0.9</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>29</v>
@@ -4286,7 +4286,7 @@
       <c r="F125" s="1">
         <v>95</v>
       </c>
-      <c r="G125" s="6">
+      <c r="G125" s="2">
         <v>0.95</v>
       </c>
       <c r="H125" s="1" t="s">
@@ -4315,13 +4315,245 @@
       <c r="F126" s="1">
         <v>100</v>
       </c>
-      <c r="G126" s="6">
+      <c r="G126" s="2">
         <v>1</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I126" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A127" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C127" s="5">
+        <v>46182</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" s="1">
+        <v>100</v>
+      </c>
+      <c r="G127" s="2">
+        <v>1</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I127" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A128" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C128" s="5">
+        <v>46182</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F128" s="1">
+        <v>100</v>
+      </c>
+      <c r="G128" s="2">
+        <v>1</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I128" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A129" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C129" s="5">
+        <v>46182</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F129" s="1">
+        <v>100</v>
+      </c>
+      <c r="G129" s="2">
+        <v>1</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I129" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A130" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C130" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F130" s="1">
+        <v>100</v>
+      </c>
+      <c r="G130" s="2">
+        <v>1</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I130" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A131" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C131" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F131" s="1">
+        <v>100</v>
+      </c>
+      <c r="G131" s="2">
+        <v>1</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I131" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A132" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C132" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" s="1">
+        <v>95</v>
+      </c>
+      <c r="G132" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I132" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A133" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C133" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" s="1">
+        <v>100</v>
+      </c>
+      <c r="G133" s="2">
+        <v>1</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I133" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A134" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C134" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" s="1">
+        <v>90</v>
+      </c>
+      <c r="G134" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I134" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -4627,6 +4859,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -4877,15 +5118,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4900,6 +5132,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4918,27 +5158,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE27928-E5AA-4D7C-854E-46F55DC843ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0DF42F-6905-4EFC-AD6B-9531E9285938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="220" windowWidth="23680" windowHeight="13140" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="4520" yWindow="90" windowWidth="25150" windowHeight="13590" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="53">
   <si>
     <t>AssociateName</t>
   </si>
@@ -307,8 +307,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I134" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I134" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I139" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I139" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I134">
     <sortCondition ref="C1:C134"/>
   </sortState>
@@ -658,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -4554,6 +4554,151 @@
         <v>29</v>
       </c>
       <c r="I134" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A135" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C135" s="5">
+        <v>46183</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F135" s="1">
+        <v>90</v>
+      </c>
+      <c r="G135" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I135" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A136" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C136" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F136" s="1">
+        <v>100</v>
+      </c>
+      <c r="G136" s="2">
+        <v>1</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I136" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A137" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C137" s="5">
+        <v>46182</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F137" s="1">
+        <v>100</v>
+      </c>
+      <c r="G137" s="2">
+        <v>1</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I137" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A138" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C138" s="5">
+        <v>46185</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F138" s="1">
+        <v>100</v>
+      </c>
+      <c r="G138" s="2">
+        <v>1</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I138" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A139" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C139" s="5">
+        <v>46181</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" s="1">
+        <v>100</v>
+      </c>
+      <c r="G139" s="2">
+        <v>1</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I139" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -4868,6 +5013,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -5118,19 +5276,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>
@@ -5140,6 +5285,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5156,21 +5318,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0DF42F-6905-4EFC-AD6B-9531E9285938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1E9591-AA0D-4DB7-80D0-A230867435E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4520" yWindow="90" windowWidth="25150" windowHeight="13590" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="710" yWindow="100" windowWidth="33750" windowHeight="13580" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="53">
   <si>
     <t>AssociateName</t>
   </si>
@@ -66,22 +66,16 @@
     <t>ReviewYear</t>
   </si>
   <si>
-    <t>Connie Serrano</t>
+    <t>Tara Pitula</t>
   </si>
   <si>
-    <t>Charles</t>
-  </si>
-  <si>
-    <t>No</t>
+    <t>Katie</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>Tara Pitula</t>
-  </si>
-  <si>
-    <t>Katie</t>
+    <t>No</t>
   </si>
   <si>
     <t>Thomas Gordon</t>
@@ -90,19 +84,28 @@
     <t>Deja Patterson</t>
   </si>
   <si>
-    <t>Marcus McDowell</t>
-  </si>
-  <si>
     <t>Raven Ingram</t>
   </si>
   <si>
     <t>Selena Hammond</t>
   </si>
   <si>
-    <t>Kelly Acevedo</t>
+    <t>Marcus McDowell</t>
+  </si>
+  <si>
+    <t>Connie Serrano</t>
+  </si>
+  <si>
+    <t>Charles</t>
+  </si>
+  <si>
+    <t>TyKee Walmsley</t>
   </si>
   <si>
     <t>April</t>
+  </si>
+  <si>
+    <t>Kelly Acevedo</t>
   </si>
   <si>
     <t>Marnia Vance</t>
@@ -111,16 +114,13 @@
     <t>Michael Chen</t>
   </si>
   <si>
-    <t>TyKee Walmsley</t>
-  </si>
-  <si>
     <t>Tyler Rainford</t>
   </si>
   <si>
-    <t>Seshu Chivukula</t>
+    <t>Breanna Stringfellow</t>
   </si>
   <si>
-    <t>Breanna Stringfellow</t>
+    <t>Seshu Chivukula</t>
   </si>
   <si>
     <t>May</t>
@@ -247,7 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -260,6 +260,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -307,10 +310,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I139" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I139" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I134">
-    <sortCondition ref="C1:C134"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I158" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I158" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I158">
+    <sortCondition ref="C1:C158"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
@@ -658,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I139"/>
+  <dimension ref="A1:I158"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -702,19 +705,19 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C2" s="5">
         <v>46113</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1">
         <v>100</v>
@@ -731,19 +734,19 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C3" s="5">
         <v>46113</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1">
         <v>100</v>
@@ -760,19 +763,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4" s="5">
         <v>46113</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1">
         <v>100</v>
@@ -789,19 +792,19 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5" s="5">
         <v>46113</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1">
         <v>100</v>
@@ -818,19 +821,19 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5">
         <v>46113</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="1">
         <v>100</v>
@@ -847,19 +850,19 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C7" s="5">
         <v>46114</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1">
         <v>100</v>
@@ -876,19 +879,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5">
         <v>46114</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1">
         <v>100</v>
@@ -905,19 +908,19 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9" s="5">
         <v>46114</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1">
         <v>100</v>
@@ -934,19 +937,19 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5">
         <v>46118</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1">
         <v>80</v>
@@ -966,16 +969,16 @@
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" s="5">
         <v>46118</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1">
         <v>70</v>
@@ -992,19 +995,19 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C12" s="5">
         <v>46119</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1">
         <v>95</v>
@@ -1021,19 +1024,19 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" s="5">
         <v>46119</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1">
         <v>85</v>
@@ -1050,19 +1053,19 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C14" s="5">
         <v>46119</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1">
         <v>100</v>
@@ -1079,19 +1082,19 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C15" s="5">
         <v>46120</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1">
         <v>90</v>
@@ -1111,16 +1114,16 @@
         <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C16" s="5">
         <v>46120</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -1137,19 +1140,19 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C17" s="5">
         <v>46120</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1">
         <v>90</v>
@@ -1166,19 +1169,19 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C18" s="5">
         <v>46120</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1195,19 +1198,19 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C19" s="5">
         <v>46121</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1">
         <v>100</v>
@@ -1224,19 +1227,19 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C20" s="5">
         <v>46121</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1253,19 +1256,19 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C21" s="5">
         <v>46121</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1">
         <v>100</v>
@@ -1282,19 +1285,19 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C22" s="5">
         <v>46121</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1">
         <v>100</v>
@@ -1314,16 +1317,16 @@
         <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C23" s="5">
         <v>46122</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F23" s="1">
         <v>95</v>
@@ -1340,19 +1343,19 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C24" s="5">
         <v>46122</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1">
         <v>95</v>
@@ -1369,19 +1372,19 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C25" s="5">
         <v>46122</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1">
         <v>100</v>
@@ -1398,19 +1401,19 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C26" s="5">
         <v>46122</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1">
         <v>100</v>
@@ -1430,16 +1433,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C27" s="5">
         <v>46125</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -1459,16 +1462,16 @@
         <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C28" s="5">
         <v>46126</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1">
         <v>100</v>
@@ -1485,19 +1488,19 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C29" s="5">
         <v>46126</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1">
         <v>95</v>
@@ -1514,19 +1517,19 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C30" s="5">
         <v>46126</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1">
         <v>90</v>
@@ -1543,19 +1546,19 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C31" s="5">
         <v>46127</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -1572,19 +1575,19 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C32" s="5">
         <v>46127</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F32" s="1">
         <v>100</v>
@@ -1601,19 +1604,19 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C33" s="5">
         <v>46127</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1">
         <v>100</v>
@@ -1630,19 +1633,19 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C34" s="5">
         <v>46127</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F34" s="1">
         <v>100</v>
@@ -1659,19 +1662,19 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C35" s="5">
         <v>46128</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -1688,19 +1691,19 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C36" s="5">
         <v>46128</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F36" s="1">
         <v>100</v>
@@ -1717,19 +1720,19 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C37" s="5">
         <v>46128</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -1749,16 +1752,16 @@
         <v>25</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C38" s="5">
         <v>46128</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -1778,16 +1781,16 @@
         <v>17</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C39" s="5">
         <v>46129</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F39" s="1">
         <v>95</v>
@@ -1804,19 +1807,19 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C40" s="5">
         <v>46129</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F40" s="1">
         <v>100</v>
@@ -1833,19 +1836,19 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C41" s="5">
         <v>46129</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1">
         <v>100</v>
@@ -1862,19 +1865,19 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C42" s="5">
         <v>46133</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F42" s="1">
         <v>100</v>
@@ -1891,19 +1894,19 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C43" s="5">
         <v>46134</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F43" s="1">
         <v>100</v>
@@ -1923,16 +1926,16 @@
         <v>25</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C44" s="5">
         <v>46134</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F44" s="1">
         <v>100</v>
@@ -1949,19 +1952,19 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C45" s="5">
         <v>46134</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -1978,19 +1981,19 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C46" s="5">
         <v>46135</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F46" s="1">
         <v>90</v>
@@ -2007,19 +2010,19 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C47" s="5">
         <v>46135</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F47" s="1">
         <v>100</v>
@@ -2036,19 +2039,19 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C48" s="5">
         <v>46135</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F48" s="1">
         <v>100</v>
@@ -2065,19 +2068,19 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C49" s="5">
         <v>46135</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1">
         <v>100</v>
@@ -2094,19 +2097,19 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C50" s="5">
         <v>46135</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1">
         <v>100</v>
@@ -2123,19 +2126,19 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C51" s="5">
         <v>46135</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F51" s="1">
         <v>100</v>
@@ -2152,19 +2155,19 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C52" s="5">
         <v>46135</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -2181,19 +2184,19 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C53" s="5">
         <v>46140</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F53" s="1">
         <v>100</v>
@@ -2210,19 +2213,19 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C54" s="5">
         <v>46140</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F54" s="1">
         <v>95</v>
@@ -2239,19 +2242,19 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C55" s="5">
         <v>46141</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F55" s="1">
         <v>100</v>
@@ -2271,16 +2274,16 @@
         <v>25</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C56" s="5">
         <v>46141</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1">
         <v>85</v>
@@ -2297,19 +2300,19 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C57" s="5">
         <v>46141</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F57" s="1">
         <v>100</v>
@@ -2326,19 +2329,19 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C58" s="5">
         <v>46141</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1">
         <v>100</v>
@@ -2355,19 +2358,19 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C59" s="5">
         <v>46141</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F59" s="1">
         <v>90</v>
@@ -2384,19 +2387,19 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C60" s="5">
         <v>46142</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60" s="1">
         <v>100</v>
@@ -2413,19 +2416,19 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C61" s="5">
         <v>46142</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1">
         <v>100</v>
@@ -2442,19 +2445,19 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C62" s="5">
         <v>46142</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F62" s="1">
         <v>100</v>
@@ -2474,16 +2477,16 @@
         <v>17</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C63" s="5">
         <v>46142</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F63" s="1">
         <v>70</v>
@@ -2500,19 +2503,19 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C64" s="5">
         <v>46142</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1">
         <v>90</v>
@@ -2529,19 +2532,19 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C65" s="5">
         <v>46142</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1">
         <v>100</v>
@@ -2558,19 +2561,19 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C66" s="5">
         <v>46142</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1">
         <v>90</v>
@@ -2587,19 +2590,19 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C67" s="5">
         <v>46143</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F67" s="1">
         <v>100</v>
@@ -2619,16 +2622,16 @@
         <v>17</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C68" s="5">
         <v>46143</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F68" s="1">
         <v>100</v>
@@ -2645,19 +2648,19 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C69" s="5">
         <v>46147</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F69" s="1">
         <v>100</v>
@@ -2674,19 +2677,19 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C70" s="5">
         <v>46147</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F70" s="1">
         <v>100</v>
@@ -2703,19 +2706,19 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C71" s="5">
         <v>46147</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F71" s="1">
         <v>100</v>
@@ -2732,19 +2735,19 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C72" s="5">
         <v>46148</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F72" s="1">
         <v>100</v>
@@ -2761,19 +2764,19 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C73" s="5">
         <v>46148</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F73" s="1">
         <v>100</v>
@@ -2790,19 +2793,19 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C74" s="5">
         <v>46148</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1">
         <v>100</v>
@@ -2819,19 +2822,19 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C75" s="5">
         <v>46148</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F75" s="1">
         <v>100</v>
@@ -2848,19 +2851,19 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C76" s="5">
         <v>46149</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1">
         <v>100</v>
@@ -2877,19 +2880,19 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C77" s="5">
         <v>46149</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F77" s="1">
         <v>100</v>
@@ -2906,19 +2909,19 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C78" s="5">
         <v>46149</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F78" s="1">
         <v>100</v>
@@ -2938,16 +2941,16 @@
         <v>17</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C79" s="5">
         <v>46149</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1">
         <v>90</v>
@@ -2964,19 +2967,19 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C80" s="5">
         <v>46149</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1">
         <v>100</v>
@@ -2993,19 +2996,19 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C81" s="5">
         <v>46149</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1">
         <v>100</v>
@@ -3022,19 +3025,19 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C82" s="5">
         <v>46149</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" s="1">
         <v>100</v>
@@ -3051,19 +3054,19 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C83" s="5">
         <v>46150</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F83" s="1">
         <v>100</v>
@@ -3080,19 +3083,19 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C84" s="5">
         <v>46153</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F84" s="1">
         <v>95</v>
@@ -3109,19 +3112,19 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C85" s="5">
         <v>46154</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F85" s="1">
         <v>100</v>
@@ -3138,19 +3141,19 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C86" s="5">
         <v>46154</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F86" s="1">
         <v>100</v>
@@ -3167,19 +3170,19 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C87" s="5">
         <v>46154</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F87" s="1">
         <v>100</v>
@@ -3196,19 +3199,19 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C88" s="5">
         <v>46154</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F88" s="1">
         <v>100</v>
@@ -3225,19 +3228,19 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C89" s="5">
         <v>46155</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F89" s="1">
         <v>100</v>
@@ -3254,19 +3257,19 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C90" s="5">
         <v>46155</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1">
         <v>100</v>
@@ -3283,19 +3286,19 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C91" s="5">
         <v>46155</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F91" s="1">
         <v>100</v>
@@ -3312,19 +3315,19 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C92" s="5">
         <v>46155</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F92" s="1">
         <v>100</v>
@@ -3341,19 +3344,19 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C93" s="5">
         <v>46156</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1">
         <v>95</v>
@@ -3370,19 +3373,19 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C94" s="5">
         <v>46156</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1">
         <v>100</v>
@@ -3399,19 +3402,19 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C95" s="5">
         <v>46156</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1">
         <v>100</v>
@@ -3428,19 +3431,19 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C96" s="5">
         <v>46156</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1">
         <v>100</v>
@@ -3457,19 +3460,19 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C97" s="5">
         <v>46157</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F97" s="1">
         <v>100</v>
@@ -3486,19 +3489,19 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C98" s="5">
         <v>46157</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -3518,16 +3521,16 @@
         <v>17</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C99" s="5">
         <v>46157</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F99" s="1">
         <v>90</v>
@@ -3544,19 +3547,19 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C100" s="5">
         <v>46161</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1">
         <v>100</v>
@@ -3576,16 +3579,16 @@
         <v>17</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C101" s="5">
         <v>46162</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1">
         <v>100</v>
@@ -3602,19 +3605,19 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C102" s="5">
         <v>46168</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1">
         <v>100</v>
@@ -3631,19 +3634,19 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C103" s="5">
         <v>46168</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1">
         <v>100</v>
@@ -3660,19 +3663,19 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C104" s="5">
         <v>46168</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1">
         <v>100</v>
@@ -3689,19 +3692,19 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C105" s="5">
         <v>46169</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F105" s="1">
         <v>95</v>
@@ -3718,19 +3721,19 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C106" s="5">
         <v>46169</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F106" s="1">
         <v>100</v>
@@ -3747,19 +3750,19 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C107" s="5">
         <v>46170</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F107" s="1">
         <v>100</v>
@@ -3776,19 +3779,19 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C108" s="5">
         <v>46170</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F108" s="1">
         <v>100</v>
@@ -3805,19 +3808,19 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C109" s="5">
         <v>46170</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F109" s="1">
         <v>100</v>
@@ -3834,19 +3837,19 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C110" s="5">
         <v>46170</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -3863,19 +3866,19 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C111" s="5">
         <v>46170</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F111" s="1">
         <v>100</v>
@@ -3892,19 +3895,19 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C112" s="5">
         <v>46171</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F112" s="1">
         <v>90</v>
@@ -3924,16 +3927,16 @@
         <v>17</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C113" s="5">
         <v>46171</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
@@ -3950,19 +3953,19 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C114" s="5">
         <v>46171</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F114" s="1">
         <v>100</v>
@@ -3982,16 +3985,16 @@
         <v>17</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C115" s="5">
         <v>46174</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F115" s="1">
         <v>100</v>
@@ -4008,19 +4011,19 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C116" s="5">
         <v>46174</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F116" s="1">
         <v>100</v>
@@ -4037,24 +4040,24 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C117" s="5">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F117" s="1">
         <v>100</v>
       </c>
-      <c r="G117" s="2">
+      <c r="G117" s="6">
         <v>1</v>
       </c>
       <c r="H117" s="1" t="s">
@@ -4069,16 +4072,16 @@
         <v>15</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C118" s="5">
         <v>46175</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F118" s="1">
         <v>100</v>
@@ -4095,25 +4098,25 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C119" s="5">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F119" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G119" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>29</v>
@@ -4124,25 +4127,25 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C120" s="5">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G120" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>29</v>
@@ -4153,24 +4156,24 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C121" s="5">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F121" s="1">
         <v>100</v>
       </c>
-      <c r="G121" s="2">
+      <c r="G121" s="6">
         <v>1</v>
       </c>
       <c r="H121" s="1" t="s">
@@ -4182,19 +4185,19 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C122" s="5">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F122" s="1">
         <v>100</v>
@@ -4211,19 +4214,19 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C123" s="5">
         <v>46178</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F123" s="1">
         <v>100</v>
@@ -4240,25 +4243,25 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C124" s="5">
         <v>46178</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F124" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G124" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>29</v>
@@ -4269,25 +4272,25 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C125" s="5">
         <v>46178</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F125" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G125" s="2">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>29</v>
@@ -4298,25 +4301,25 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C126" s="5">
         <v>46178</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F126" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G126" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>29</v>
@@ -4327,19 +4330,19 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C127" s="5">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F127" s="1">
         <v>100</v>
@@ -4356,19 +4359,19 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C128" s="5">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F128" s="1">
         <v>100</v>
@@ -4385,19 +4388,19 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C129" s="5">
-        <v>46182</v>
+        <v>46181</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F129" s="1">
         <v>100</v>
@@ -4414,24 +4417,24 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C130" s="5">
-        <v>46184</v>
+        <v>46181</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F130" s="1">
         <v>100</v>
       </c>
-      <c r="G130" s="2">
+      <c r="G130" s="6">
         <v>1</v>
       </c>
       <c r="H130" s="1" t="s">
@@ -4446,21 +4449,21 @@
         <v>20</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C131" s="5">
-        <v>46184</v>
+        <v>46181</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F131" s="1">
         <v>100</v>
       </c>
-      <c r="G131" s="2">
+      <c r="G131" s="6">
         <v>1</v>
       </c>
       <c r="H131" s="1" t="s">
@@ -4472,25 +4475,25 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C132" s="5">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G132" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>29</v>
@@ -4501,19 +4504,19 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C133" s="5">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1">
         <v>100</v>
@@ -4530,25 +4533,25 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C134" s="5">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F134" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G134" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>29</v>
@@ -4559,25 +4562,25 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C135" s="5">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F135" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G135" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>29</v>
@@ -4588,24 +4591,24 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C136" s="5">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F136" s="1">
         <v>100</v>
       </c>
-      <c r="G136" s="2">
+      <c r="G136" s="6">
         <v>1</v>
       </c>
       <c r="H136" s="1" t="s">
@@ -4617,25 +4620,25 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C137" s="5">
         <v>46182</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F137" s="1">
-        <v>100</v>
-      </c>
-      <c r="G137" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G137" s="6">
+        <v>0</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>29</v>
@@ -4646,24 +4649,24 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C138" s="5">
-        <v>46185</v>
+        <v>46182</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F138" s="1">
         <v>100</v>
       </c>
-      <c r="G138" s="2">
+      <c r="G138" s="6">
         <v>1</v>
       </c>
       <c r="H138" s="1" t="s">
@@ -4675,30 +4678,581 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C139" s="5">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F139" s="1">
         <v>100</v>
       </c>
-      <c r="G139" s="2">
+      <c r="G139" s="6">
         <v>1</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I139" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A140" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C140" s="5">
+        <v>46182</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" s="1">
+        <v>90</v>
+      </c>
+      <c r="G140" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I140" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A141" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C141" s="5">
+        <v>46183</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F141" s="1">
+        <v>90</v>
+      </c>
+      <c r="G141" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I141" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A142" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C142" s="5">
+        <v>46183</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" s="1">
+        <v>100</v>
+      </c>
+      <c r="G142" s="6">
+        <v>1</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I142" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A143" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C143" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F143" s="1">
+        <v>100</v>
+      </c>
+      <c r="G143" s="2">
+        <v>1</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I143" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A144" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C144" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F144" s="1">
+        <v>100</v>
+      </c>
+      <c r="G144" s="2">
+        <v>1</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I144" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A145" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C145" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F145" s="1">
+        <v>100</v>
+      </c>
+      <c r="G145" s="2">
+        <v>1</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I145" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A146" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C146" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F146" s="1">
+        <v>95</v>
+      </c>
+      <c r="G146" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I146" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A147" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C147" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F147" s="1">
+        <v>100</v>
+      </c>
+      <c r="G147" s="2">
+        <v>1</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I147" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A148" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C148" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148" s="1">
+        <v>90</v>
+      </c>
+      <c r="G148" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I148" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A149" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149" s="5">
+        <v>46184</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F149" s="1">
+        <v>100</v>
+      </c>
+      <c r="G149" s="6">
+        <v>1</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I149" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A150" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" s="5">
+        <v>46185</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F150" s="1">
+        <v>100</v>
+      </c>
+      <c r="G150" s="2">
+        <v>1</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I150" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A151" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C151" s="5">
+        <v>46185</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="1">
+        <v>100</v>
+      </c>
+      <c r="G151" s="6">
+        <v>1</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I151" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A152" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152" s="5">
+        <v>46188</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F152" s="1">
+        <v>100</v>
+      </c>
+      <c r="G152" s="6">
+        <v>1</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I152" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A153" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C153" s="5">
+        <v>46188</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F153" s="1">
+        <v>90</v>
+      </c>
+      <c r="G153" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I153" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A154" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C154" s="5">
+        <v>46188</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" s="1">
+        <v>0</v>
+      </c>
+      <c r="G154" s="6">
+        <v>0</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I154" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A155" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C155" s="5">
+        <v>46189</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F155" s="1">
+        <v>100</v>
+      </c>
+      <c r="G155" s="6">
+        <v>1</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I155" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A156" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C156" s="5">
+        <v>46189</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F156" s="1">
+        <v>100</v>
+      </c>
+      <c r="G156" s="6">
+        <v>1</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I156" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A157" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C157" s="5">
+        <v>46190</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F157" s="1">
+        <v>100</v>
+      </c>
+      <c r="G157" s="6">
+        <v>1</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I157" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A158" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C158" s="5">
+        <v>46190</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" s="1">
+        <v>100</v>
+      </c>
+      <c r="G158" s="6">
+        <v>1</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I158" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -4741,10 +5295,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
@@ -4758,10 +5312,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
@@ -4775,10 +5329,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
@@ -4792,10 +5346,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
@@ -4812,7 +5366,7 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
@@ -4826,10 +5380,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>33</v>
@@ -4843,10 +5397,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
@@ -4860,10 +5414,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
@@ -4880,7 +5434,7 @@
         <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
@@ -4894,10 +5448,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
@@ -4911,10 +5465,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
@@ -4928,10 +5482,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
@@ -4948,7 +5502,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
         <v>42</v>
@@ -4962,10 +5516,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
         <v>33</v>
@@ -4979,10 +5533,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
         <v>42</v>
@@ -5287,16 +5841,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1E9591-AA0D-4DB7-80D0-A230867435E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60639482-5D18-4E8C-AE47-A25E5079F099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="710" yWindow="100" windowWidth="33750" windowHeight="13580" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="870" yWindow="80" windowWidth="27160" windowHeight="13530" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="59">
   <si>
     <t>AssociateName</t>
   </si>
@@ -197,6 +197,24 @@
   <si>
     <t>Thomas.Gordon@lplfinancial.com</t>
   </si>
+  <si>
+    <t>Doni Lantow</t>
+  </si>
+  <si>
+    <t>Terra McGee</t>
+  </si>
+  <si>
+    <t>Bradley Kendrick</t>
+  </si>
+  <si>
+    <t>doni.lantow@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>Terra.McGee@lplfinancial.com</t>
+  </si>
+  <si>
+    <t>Bradley.Kendrick@lplfinancial.com</t>
+  </si>
 </sst>
 </file>
 
@@ -272,9 +290,6 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
@@ -296,6 +311,9 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -310,10 +328,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I158" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I158" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I158">
-    <sortCondition ref="C1:C158"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I163" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:I163" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I163">
+    <sortCondition ref="C1:C163"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
@@ -322,7 +340,7 @@
     <tableColumn id="15" xr3:uid="{156F7529-7782-4A87-B4E7-76854F1D035A}" name="IssueResolvedFirstContact"/>
     <tableColumn id="10" xr3:uid="{FA20FC87-A813-482F-AA10-876B721360F4}" name="CallFailed"/>
     <tableColumn id="11" xr3:uid="{DF145C57-18CF-4D90-A45D-FAACD0306130}" name="TotalScore"/>
-    <tableColumn id="12" xr3:uid="{0876AC93-D420-4B04-9EE3-448E495D6B83}" name="Percentage" dataDxfId="1" dataCellStyle="Percent"/>
+    <tableColumn id="12" xr3:uid="{0876AC93-D420-4B04-9EE3-448E495D6B83}" name="Percentage" dataDxfId="0" dataCellStyle="Percent"/>
     <tableColumn id="13" xr3:uid="{88DA4CA6-A215-4FB1-8A6D-379852A7EEFA}" name="ReviewMonth"/>
     <tableColumn id="14" xr3:uid="{35631D79-8CE9-47C8-A757-76CCFBACC54F}" name="ReviewYear"/>
   </tableColumns>
@@ -331,8 +349,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}" name="tblAssociateReference" displayName="tblAssociateReference" ref="A1:E16" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:E16" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}" name="tblAssociateReference" displayName="tblAssociateReference" ref="A1:E19" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:E19" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8E0548F5-70FF-454C-A4FF-1E3FA7D9C27E}" name="AssociateName"/>
     <tableColumn id="2" xr3:uid="{E9A01728-B3EB-48F3-9A95-B8C7D6681247}" name="ManagerTeam"/>
@@ -661,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I158"/>
+  <dimension ref="A1:I163"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -4057,7 +4075,7 @@
       <c r="F117" s="1">
         <v>100</v>
       </c>
-      <c r="G117" s="6">
+      <c r="G117" s="2">
         <v>1</v>
       </c>
       <c r="H117" s="1" t="s">
@@ -4173,7 +4191,7 @@
       <c r="F121" s="1">
         <v>100</v>
       </c>
-      <c r="G121" s="6">
+      <c r="G121" s="2">
         <v>1</v>
       </c>
       <c r="H121" s="1" t="s">
@@ -4434,7 +4452,7 @@
       <c r="F130" s="1">
         <v>100</v>
       </c>
-      <c r="G130" s="6">
+      <c r="G130" s="2">
         <v>1</v>
       </c>
       <c r="H130" s="1" t="s">
@@ -4463,7 +4481,7 @@
       <c r="F131" s="1">
         <v>100</v>
       </c>
-      <c r="G131" s="6">
+      <c r="G131" s="2">
         <v>1</v>
       </c>
       <c r="H131" s="1" t="s">
@@ -4608,7 +4626,7 @@
       <c r="F136" s="1">
         <v>100</v>
       </c>
-      <c r="G136" s="6">
+      <c r="G136" s="2">
         <v>1</v>
       </c>
       <c r="H136" s="1" t="s">
@@ -4637,7 +4655,7 @@
       <c r="F137" s="1">
         <v>0</v>
       </c>
-      <c r="G137" s="6">
+      <c r="G137" s="2">
         <v>0</v>
       </c>
       <c r="H137" s="1" t="s">
@@ -4666,7 +4684,7 @@
       <c r="F138" s="1">
         <v>100</v>
       </c>
-      <c r="G138" s="6">
+      <c r="G138" s="2">
         <v>1</v>
       </c>
       <c r="H138" s="1" t="s">
@@ -4695,7 +4713,7 @@
       <c r="F139" s="1">
         <v>100</v>
       </c>
-      <c r="G139" s="6">
+      <c r="G139" s="2">
         <v>1</v>
       </c>
       <c r="H139" s="1" t="s">
@@ -4724,7 +4742,7 @@
       <c r="F140" s="1">
         <v>90</v>
       </c>
-      <c r="G140" s="6">
+      <c r="G140" s="2">
         <v>0.9</v>
       </c>
       <c r="H140" s="1" t="s">
@@ -4782,7 +4800,7 @@
       <c r="F142" s="1">
         <v>100</v>
       </c>
-      <c r="G142" s="6">
+      <c r="G142" s="2">
         <v>1</v>
       </c>
       <c r="H142" s="1" t="s">
@@ -4985,7 +5003,7 @@
       <c r="F149" s="1">
         <v>100</v>
       </c>
-      <c r="G149" s="6">
+      <c r="G149" s="2">
         <v>1</v>
       </c>
       <c r="H149" s="1" t="s">
@@ -5043,7 +5061,7 @@
       <c r="F151" s="1">
         <v>100</v>
       </c>
-      <c r="G151" s="6">
+      <c r="G151" s="2">
         <v>1</v>
       </c>
       <c r="H151" s="1" t="s">
@@ -5072,7 +5090,7 @@
       <c r="F152" s="1">
         <v>100</v>
       </c>
-      <c r="G152" s="6">
+      <c r="G152" s="2">
         <v>1</v>
       </c>
       <c r="H152" s="1" t="s">
@@ -5101,7 +5119,7 @@
       <c r="F153" s="1">
         <v>90</v>
       </c>
-      <c r="G153" s="6">
+      <c r="G153" s="2">
         <v>0.9</v>
       </c>
       <c r="H153" s="1" t="s">
@@ -5130,7 +5148,7 @@
       <c r="F154" s="1">
         <v>0</v>
       </c>
-      <c r="G154" s="6">
+      <c r="G154" s="2">
         <v>0</v>
       </c>
       <c r="H154" s="1" t="s">
@@ -5142,13 +5160,13 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C155" s="5">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>11</v>
@@ -5171,25 +5189,25 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C156" s="5">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G156" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>29</v>
@@ -5200,13 +5218,13 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C157" s="5">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>11</v>
@@ -5217,7 +5235,7 @@
       <c r="F157" s="1">
         <v>100</v>
       </c>
-      <c r="G157" s="6">
+      <c r="G157" s="2">
         <v>1</v>
       </c>
       <c r="H157" s="1" t="s">
@@ -5229,13 +5247,13 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C158" s="5">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>11</v>
@@ -5246,13 +5264,158 @@
       <c r="F158" s="1">
         <v>100</v>
       </c>
-      <c r="G158" s="6">
+      <c r="G158" s="2">
         <v>1</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I158" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A159" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C159" s="5">
+        <v>46190</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F159" s="1">
+        <v>100</v>
+      </c>
+      <c r="G159" s="2">
+        <v>1</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I159" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A160" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C160" s="5">
+        <v>46190</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F160" s="1">
+        <v>100</v>
+      </c>
+      <c r="G160" s="2">
+        <v>1</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I160" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A161" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C161" s="5">
+        <v>46191</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F161" s="1">
+        <v>100</v>
+      </c>
+      <c r="G161" s="6">
+        <v>1</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I161" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A162" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C162" s="5">
+        <v>46191</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F162" s="1">
+        <v>75</v>
+      </c>
+      <c r="G162" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I162" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A163" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C163" s="5">
+        <v>46191</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F163" s="1">
+        <v>100</v>
+      </c>
+      <c r="G163" s="6">
+        <v>1</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I163" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -5267,7 +5430,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324C68B5-B5AE-49F4-BF99-B0AAB6EC270F}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
@@ -5546,6 +5709,57 @@
       </c>
       <c r="E16" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -5841,16 +6055,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60639482-5D18-4E8C-AE47-A25E5079F099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFA199F-984F-428B-97D2-66C114815452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="80" windowWidth="27160" windowHeight="13530" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="9710" yWindow="80" windowWidth="24710" windowHeight="13590" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="59">
   <si>
     <t>AssociateName</t>
   </si>
@@ -129,6 +129,12 @@
     <t>June</t>
   </si>
   <si>
+    <t>Bradley Kendrick</t>
+  </si>
+  <si>
+    <t>Doni Lantow</t>
+  </si>
+  <si>
     <t>ManagerName</t>
   </si>
   <si>
@@ -198,16 +204,10 @@
     <t>Thomas.Gordon@lplfinancial.com</t>
   </si>
   <si>
-    <t>Doni Lantow</t>
+    <t>doni.lantow@lplfinancial.com</t>
   </si>
   <si>
     <t>Terra McGee</t>
-  </si>
-  <si>
-    <t>Bradley Kendrick</t>
-  </si>
-  <si>
-    <t>doni.lantow@lplfinancial.com</t>
   </si>
   <si>
     <t>Terra.McGee@lplfinancial.com</t>
@@ -265,7 +265,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -280,15 +280,15 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
@@ -311,9 +311,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -328,8 +325,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I163" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:I163" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I183" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I183" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I163">
     <sortCondition ref="C1:C163"/>
   </sortState>
@@ -340,7 +337,7 @@
     <tableColumn id="15" xr3:uid="{156F7529-7782-4A87-B4E7-76854F1D035A}" name="IssueResolvedFirstContact"/>
     <tableColumn id="10" xr3:uid="{FA20FC87-A813-482F-AA10-876B721360F4}" name="CallFailed"/>
     <tableColumn id="11" xr3:uid="{DF145C57-18CF-4D90-A45D-FAACD0306130}" name="TotalScore"/>
-    <tableColumn id="12" xr3:uid="{0876AC93-D420-4B04-9EE3-448E495D6B83}" name="Percentage" dataDxfId="0" dataCellStyle="Percent"/>
+    <tableColumn id="12" xr3:uid="{0876AC93-D420-4B04-9EE3-448E495D6B83}" name="Percentage" dataDxfId="1" dataCellStyle="Percent"/>
     <tableColumn id="13" xr3:uid="{88DA4CA6-A215-4FB1-8A6D-379852A7EEFA}" name="ReviewMonth"/>
     <tableColumn id="14" xr3:uid="{35631D79-8CE9-47C8-A757-76CCFBACC54F}" name="ReviewYear"/>
   </tableColumns>
@@ -349,7 +346,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}" name="tblAssociateReference" displayName="tblAssociateReference" ref="A1:E19" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}" name="tblAssociateReference" displayName="tblAssociateReference" ref="A1:E19" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:E19" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8E0548F5-70FF-454C-A4FF-1E3FA7D9C27E}" name="AssociateName"/>
@@ -679,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I163"/>
+  <dimension ref="A1:I183"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -5143,13 +5140,13 @@
         <v>11</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F154" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G154" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>29</v>
@@ -5177,7 +5174,7 @@
       <c r="F155" s="1">
         <v>100</v>
       </c>
-      <c r="G155" s="6">
+      <c r="G155" s="2">
         <v>1</v>
       </c>
       <c r="H155" s="1" t="s">
@@ -5206,7 +5203,7 @@
       <c r="F156" s="1">
         <v>0</v>
       </c>
-      <c r="G156" s="6">
+      <c r="G156" s="2">
         <v>0</v>
       </c>
       <c r="H156" s="1" t="s">
@@ -5351,7 +5348,7 @@
       <c r="F161" s="1">
         <v>100</v>
       </c>
-      <c r="G161" s="6">
+      <c r="G161" s="2">
         <v>1</v>
       </c>
       <c r="H161" s="1" t="s">
@@ -5380,7 +5377,7 @@
       <c r="F162" s="1">
         <v>75</v>
       </c>
-      <c r="G162" s="6">
+      <c r="G162" s="2">
         <v>0.75</v>
       </c>
       <c r="H162" s="1" t="s">
@@ -5409,13 +5406,593 @@
       <c r="F163" s="1">
         <v>100</v>
       </c>
-      <c r="G163" s="6">
+      <c r="G163" s="2">
         <v>1</v>
       </c>
       <c r="H163" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I163" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A164" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C164" s="5">
+        <v>46188</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F164" s="1">
+        <v>0</v>
+      </c>
+      <c r="G164" s="2">
+        <v>0</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I164" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A165" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C165" s="5">
+        <v>46191</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" s="1">
+        <v>0</v>
+      </c>
+      <c r="G165" s="2">
+        <v>0</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I165" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A166" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C166" s="5">
+        <v>46188</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F166" s="1">
+        <v>100</v>
+      </c>
+      <c r="G166" s="2">
+        <v>1</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I166" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A167" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C167" s="5">
+        <v>46191</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F167" s="1">
+        <v>100</v>
+      </c>
+      <c r="G167" s="2">
+        <v>1</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I167" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A168" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" s="5">
+        <v>46189</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F168" s="1">
+        <v>100</v>
+      </c>
+      <c r="G168" s="2">
+        <v>1</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I168" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A169" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C169" s="5">
+        <v>46198</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F169" s="1">
+        <v>100</v>
+      </c>
+      <c r="G169" s="2">
+        <v>1</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I169" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A170" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C170" s="5">
+        <v>46198</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F170" s="1">
+        <v>95</v>
+      </c>
+      <c r="G170" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I170" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A171" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C171" s="5">
+        <v>46196</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F171" s="1">
+        <v>100</v>
+      </c>
+      <c r="G171" s="2">
+        <v>1</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I171" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A172" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C172" s="5">
+        <v>46195</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F172" s="1">
+        <v>100</v>
+      </c>
+      <c r="G172" s="2">
+        <v>1</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I172" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A173" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C173" s="5">
+        <v>46197</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F173" s="1">
+        <v>85</v>
+      </c>
+      <c r="G173" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I173" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A174" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C174" s="5">
+        <v>46197</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F174" s="1">
+        <v>100</v>
+      </c>
+      <c r="G174" s="2">
+        <v>1</v>
+      </c>
+      <c r="H174" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I174" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A175" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C175" s="5">
+        <v>46189</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F175" s="1">
+        <v>85</v>
+      </c>
+      <c r="G175" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="H175" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I175" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A176" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C176" s="5">
+        <v>46198</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F176" s="1">
+        <v>95</v>
+      </c>
+      <c r="G176" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H176" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I176" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A177" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C177" s="5">
+        <v>46198</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F177" s="1">
+        <v>95</v>
+      </c>
+      <c r="G177" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I177" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A178" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C178" s="5">
+        <v>46190</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F178" s="1">
+        <v>100</v>
+      </c>
+      <c r="G178" s="2">
+        <v>1</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I178" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A179" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C179" s="5">
+        <v>46191</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F179" s="1">
+        <v>100</v>
+      </c>
+      <c r="G179" s="2">
+        <v>1</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I179" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A180" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C180" s="5">
+        <v>46188</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F180" s="1">
+        <v>95</v>
+      </c>
+      <c r="G180" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I180" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A181" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C181" s="5">
+        <v>46199</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F181" s="1">
+        <v>100</v>
+      </c>
+      <c r="G181" s="2">
+        <v>1</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I181" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A182" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C182" s="5">
+        <v>46198</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F182" s="1">
+        <v>100</v>
+      </c>
+      <c r="G182" s="2">
+        <v>1</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I182" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A183" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C183" s="5">
+        <v>46198</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F183" s="1">
+        <v>50</v>
+      </c>
+      <c r="G183" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I183" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -5447,13 +6024,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -5464,13 +6041,13 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -5481,13 +6058,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -5498,13 +6075,13 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -5515,13 +6092,13 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -5532,13 +6109,13 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -5549,13 +6126,13 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -5566,13 +6143,13 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -5583,30 +6160,30 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
         <v>45</v>
       </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -5617,13 +6194,13 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -5634,13 +6211,13 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -5651,13 +6228,13 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -5668,13 +6245,13 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -5685,13 +6262,13 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -5702,44 +6279,44 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
         <v>57</v>
@@ -5747,16 +6324,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E19" t="s">
         <v>58</v>
@@ -5772,15 +6349,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
@@ -5793,7 +6361,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -6044,32 +6612,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6086,4 +6655,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFA199F-984F-428B-97D2-66C114815452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CECD59B-0581-48A0-BDD3-50CAD6437C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9710" yWindow="80" windowWidth="24710" windowHeight="13590" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="510" yWindow="20" windowWidth="33620" windowHeight="13670" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="59">
   <si>
     <t>AssociateName</t>
   </si>
@@ -265,7 +265,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -278,6 +278,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -325,8 +328,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I183" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I183" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I185" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I185" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I163">
     <sortCondition ref="C1:C163"/>
   </sortState>
@@ -676,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I183"/>
+  <dimension ref="A1:I185"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -4647,13 +4650,13 @@
         <v>11</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F137" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>29</v>
@@ -5993,6 +5996,64 @@
         <v>29</v>
       </c>
       <c r="I183" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A184" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C184" s="5">
+        <v>46198</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F184" s="1">
+        <v>95</v>
+      </c>
+      <c r="G184" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I184" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A185" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C185" s="5">
+        <v>46198</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F185" s="1">
+        <v>100</v>
+      </c>
+      <c r="G185" s="6">
+        <v>1</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I185" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -6349,19 +6410,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -6612,6 +6660,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6622,23 +6683,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6657,6 +6701,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CECD59B-0581-48A0-BDD3-50CAD6437C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F76399-EC25-470D-B2AF-EAEB2A0F53E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="20" windowWidth="33620" windowHeight="13670" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="1710" yWindow="10" windowWidth="27050" windowHeight="13670" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="60">
   <si>
     <t>AssociateName</t>
   </si>
@@ -215,6 +215,9 @@
   <si>
     <t>Bradley.Kendrick@lplfinancial.com</t>
   </si>
+  <si>
+    <t>July</t>
+  </si>
 </sst>
 </file>
 
@@ -328,8 +331,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I185" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I185" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I190" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I190" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I163">
     <sortCondition ref="C1:C163"/>
   </sortState>
@@ -679,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I185"/>
+  <dimension ref="A1:I190"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -6018,7 +6021,7 @@
       <c r="F184" s="1">
         <v>95</v>
       </c>
-      <c r="G184" s="6">
+      <c r="G184" s="2">
         <v>0.95</v>
       </c>
       <c r="H184" s="1" t="s">
@@ -6047,13 +6050,158 @@
       <c r="F185" s="1">
         <v>100</v>
       </c>
-      <c r="G185" s="6">
+      <c r="G185" s="2">
         <v>1</v>
       </c>
       <c r="H185" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I185" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A186" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C186" s="5">
+        <v>46198</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F186" s="1">
+        <v>90</v>
+      </c>
+      <c r="G186" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H186" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I186" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A187" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C187" s="5">
+        <v>46195</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F187" s="1">
+        <v>90</v>
+      </c>
+      <c r="G187" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I187" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A188" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C188" s="5">
+        <v>46233</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F188" s="1">
+        <v>0</v>
+      </c>
+      <c r="G188" s="6">
+        <v>0</v>
+      </c>
+      <c r="H188" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I188" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A189" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C189" s="5">
+        <v>46198</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F189" s="1">
+        <v>100</v>
+      </c>
+      <c r="G189" s="6">
+        <v>1</v>
+      </c>
+      <c r="H189" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I189" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A190" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C190" s="5">
+        <v>46203</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F190" s="1">
+        <v>100</v>
+      </c>
+      <c r="G190" s="6">
+        <v>1</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I190" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -6661,6 +6809,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
@@ -6671,15 +6828,6 @@
     <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6702,26 +6850,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F76399-EC25-470D-B2AF-EAEB2A0F53E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F410EF-97D6-4616-A464-9F09B20564F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1710" yWindow="10" windowWidth="27050" windowHeight="13670" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="60">
   <si>
     <t>AssociateName</t>
   </si>
@@ -135,6 +135,9 @@
     <t>Doni Lantow</t>
   </si>
   <si>
+    <t>July</t>
+  </si>
+  <si>
     <t>ManagerName</t>
   </si>
   <si>
@@ -214,9 +217,6 @@
   </si>
   <si>
     <t>Bradley.Kendrick@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>July</t>
   </si>
 </sst>
 </file>
@@ -331,10 +331,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I190" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I190" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I163">
-    <sortCondition ref="C1:C163"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I204" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I204" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I204">
+    <sortCondition ref="C1:C204"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
@@ -682,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I190"/>
+  <dimension ref="A1:I204"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -5221,25 +5221,25 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C157" s="5">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157" s="1" t="s">
         <v>29</v>
@@ -5250,13 +5250,13 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C158" s="5">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>11</v>
@@ -5279,13 +5279,13 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C159" s="5">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>11</v>
@@ -5294,10 +5294,10 @@
         <v>12</v>
       </c>
       <c r="F159" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G159" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>29</v>
@@ -5308,13 +5308,13 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C160" s="5">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>11</v>
@@ -5337,13 +5337,13 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C161" s="5">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>11</v>
@@ -5366,13 +5366,13 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C162" s="5">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>11</v>
@@ -5381,10 +5381,10 @@
         <v>12</v>
       </c>
       <c r="F162" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G162" s="2">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H162" s="1" t="s">
         <v>29</v>
@@ -5395,13 +5395,13 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C163" s="5">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>11</v>
@@ -5410,10 +5410,10 @@
         <v>12</v>
       </c>
       <c r="F163" s="1">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G163" s="2">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H163" s="1" t="s">
         <v>29</v>
@@ -5424,25 +5424,25 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C164" s="5">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F164" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G164" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>29</v>
@@ -5453,25 +5453,25 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C165" s="5">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F165" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G165" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>29</v>
@@ -5482,16 +5482,16 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C166" s="5">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>12</v>
@@ -5511,7 +5511,7 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>10</v>
@@ -5520,7 +5520,7 @@
         <v>46191</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>12</v>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C168" s="5">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>11</v>
@@ -5555,10 +5555,10 @@
         <v>12</v>
       </c>
       <c r="F168" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G168" s="2">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H168" s="1" t="s">
         <v>29</v>
@@ -5569,13 +5569,13 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C169" s="5">
-        <v>46198</v>
+        <v>46191</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>11</v>
@@ -5598,25 +5598,25 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C170" s="5">
-        <v>46198</v>
+        <v>46191</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F170" s="1">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="G170" s="2">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>29</v>
@@ -5627,16 +5627,16 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C171" s="5">
-        <v>46196</v>
+        <v>46191</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>12</v>
@@ -5656,13 +5656,13 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C172" s="5">
-        <v>46195</v>
+        <v>46191</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>11</v>
@@ -5685,25 +5685,25 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C173" s="5">
-        <v>46197</v>
+        <v>46195</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F173" s="1">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G173" s="2">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H173" s="1" t="s">
         <v>29</v>
@@ -5714,13 +5714,13 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C174" s="5">
-        <v>46197</v>
+        <v>46195</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>11</v>
@@ -5729,10 +5729,10 @@
         <v>12</v>
       </c>
       <c r="F174" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G174" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H174" s="1" t="s">
         <v>29</v>
@@ -5749,7 +5749,7 @@
         <v>19</v>
       </c>
       <c r="C175" s="5">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>11</v>
@@ -5758,10 +5758,10 @@
         <v>12</v>
       </c>
       <c r="F175" s="1">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G175" s="2">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H175" s="1" t="s">
         <v>29</v>
@@ -5772,13 +5772,13 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C176" s="5">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>12</v>
@@ -5787,10 +5787,10 @@
         <v>12</v>
       </c>
       <c r="F176" s="1">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G176" s="2">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H176" s="1" t="s">
         <v>29</v>
@@ -5801,13 +5801,13 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C177" s="5">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>11</v>
@@ -5816,10 +5816,10 @@
         <v>12</v>
       </c>
       <c r="F177" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G177" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H177" s="1" t="s">
         <v>29</v>
@@ -5830,16 +5830,16 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C178" s="5">
-        <v>46190</v>
+        <v>46198</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>12</v>
@@ -5859,13 +5859,13 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C179" s="5">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>11</v>
@@ -5874,10 +5874,10 @@
         <v>12</v>
       </c>
       <c r="F179" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G179" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H179" s="1" t="s">
         <v>29</v>
@@ -5888,16 +5888,16 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C180" s="5">
-        <v>46188</v>
+        <v>46198</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>12</v>
@@ -5917,13 +5917,13 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C181" s="5">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>11</v>
@@ -5932,10 +5932,10 @@
         <v>12</v>
       </c>
       <c r="F181" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G181" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H181" s="1" t="s">
         <v>29</v>
@@ -6079,7 +6079,7 @@
       <c r="F186" s="1">
         <v>90</v>
       </c>
-      <c r="G186" s="6">
+      <c r="G186" s="2">
         <v>0.9</v>
       </c>
       <c r="H186" s="1" t="s">
@@ -6091,13 +6091,13 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C187" s="5">
-        <v>46195</v>
+        <v>46198</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>11</v>
@@ -6106,10 +6106,10 @@
         <v>12</v>
       </c>
       <c r="F187" s="1">
-        <v>90</v>
-      </c>
-      <c r="G187" s="6">
-        <v>0.9</v>
+        <v>100</v>
+      </c>
+      <c r="G187" s="2">
+        <v>1</v>
       </c>
       <c r="H187" s="1" t="s">
         <v>29</v>
@@ -6120,28 +6120,28 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C188" s="5">
-        <v>46233</v>
+        <v>46199</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F188" s="1">
-        <v>0</v>
-      </c>
-      <c r="G188" s="6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="G188" s="2">
+        <v>1</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="I188" s="1">
         <v>2026</v>
@@ -6155,7 +6155,7 @@
         <v>10</v>
       </c>
       <c r="C189" s="5">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>11</v>
@@ -6166,7 +6166,7 @@
       <c r="F189" s="1">
         <v>100</v>
       </c>
-      <c r="G189" s="6">
+      <c r="G189" s="2">
         <v>1</v>
       </c>
       <c r="H189" s="1" t="s">
@@ -6178,30 +6178,436 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C190" s="5">
+        <v>46205</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F190" s="1">
+        <v>90</v>
+      </c>
+      <c r="G190" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I190" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A191" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C191" s="5">
+        <v>46209</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F191" s="1">
+        <v>100</v>
+      </c>
+      <c r="G191" s="6">
+        <v>1</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I191" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A192" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C192" s="5">
+        <v>46209</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F192" s="1">
+        <v>100</v>
+      </c>
+      <c r="G192" s="6">
+        <v>1</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I192" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A193" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C193" s="5">
+        <v>46209</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F193" s="1">
+        <v>100</v>
+      </c>
+      <c r="G193" s="6">
+        <v>1</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I193" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A194" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C194" s="5">
+        <v>46210</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F194" s="1">
+        <v>100</v>
+      </c>
+      <c r="G194" s="6">
+        <v>1</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I194" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A195" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C195" s="5">
+        <v>46210</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F195" s="1">
+        <v>100</v>
+      </c>
+      <c r="G195" s="6">
+        <v>1</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I195" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A196" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C196" s="5">
+        <v>46210</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F196" s="1">
+        <v>100</v>
+      </c>
+      <c r="G196" s="6">
+        <v>1</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I196" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A197" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C197" s="5">
+        <v>46212</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F197" s="1">
+        <v>100</v>
+      </c>
+      <c r="G197" s="6">
+        <v>1</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I197" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A198" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C198" s="5">
+        <v>46212</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F198" s="1">
+        <v>100</v>
+      </c>
+      <c r="G198" s="6">
+        <v>1</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I198" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A199" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C199" s="5">
+        <v>46212</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F199" s="1">
+        <v>100</v>
+      </c>
+      <c r="G199" s="6">
+        <v>1</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I199" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A200" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C200" s="5">
+        <v>46212</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F200" s="1">
+        <v>100</v>
+      </c>
+      <c r="G200" s="6">
+        <v>1</v>
+      </c>
+      <c r="H200" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I200" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A201" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C201" s="5">
+        <v>46212</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F201" s="1">
+        <v>100</v>
+      </c>
+      <c r="G201" s="6">
+        <v>1</v>
+      </c>
+      <c r="H201" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I201" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A202" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C190" s="5">
-        <v>46203</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F190" s="1">
-        <v>100</v>
-      </c>
-      <c r="G190" s="6">
-        <v>1</v>
-      </c>
-      <c r="H190" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I190" s="1">
+      <c r="B202" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C202" s="5">
+        <v>46213</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F202" s="1">
+        <v>100</v>
+      </c>
+      <c r="G202" s="6">
+        <v>1</v>
+      </c>
+      <c r="H202" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I202" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A203" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C203" s="5">
+        <v>46213</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F203" s="1">
+        <v>95</v>
+      </c>
+      <c r="G203" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H203" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I203" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A204" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C204" s="5">
+        <v>46233</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F204" s="1">
+        <v>0</v>
+      </c>
+      <c r="G204" s="2">
+        <v>0</v>
+      </c>
+      <c r="H204" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I204" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -6233,13 +6639,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -6250,13 +6656,13 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -6267,13 +6673,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -6284,13 +6690,13 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -6301,13 +6707,13 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -6318,13 +6724,13 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -6335,13 +6741,13 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -6352,13 +6758,13 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -6369,30 +6775,30 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -6403,13 +6809,13 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -6420,13 +6826,13 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -6437,13 +6843,13 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -6454,13 +6860,13 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -6471,13 +6877,13 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -6488,13 +6894,13 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -6505,30 +6911,30 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -6539,13 +6945,13 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -6558,6 +6964,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -6808,15 +7223,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -6831,6 +7237,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6849,27 +7263,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F410EF-97D6-4616-A464-9F09B20564F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1B134A-3809-4A11-9E24-356BB2157EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1710" yWindow="10" windowWidth="27050" windowHeight="13670" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="4300" yWindow="50" windowWidth="28040" windowHeight="13670" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="60">
   <si>
     <t>AssociateName</t>
   </si>
@@ -331,8 +331,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I204" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I204" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I226" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I226" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I204">
     <sortCondition ref="C1:C204"/>
   </sortState>
@@ -682,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I204"/>
+  <dimension ref="A1:I226"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -6195,7 +6195,7 @@
       <c r="F190" s="1">
         <v>90</v>
       </c>
-      <c r="G190" s="6">
+      <c r="G190" s="2">
         <v>0.9</v>
       </c>
       <c r="H190" s="1" t="s">
@@ -6224,7 +6224,7 @@
       <c r="F191" s="1">
         <v>100</v>
       </c>
-      <c r="G191" s="6">
+      <c r="G191" s="2">
         <v>1</v>
       </c>
       <c r="H191" s="1" t="s">
@@ -6253,7 +6253,7 @@
       <c r="F192" s="1">
         <v>100</v>
       </c>
-      <c r="G192" s="6">
+      <c r="G192" s="2">
         <v>1</v>
       </c>
       <c r="H192" s="1" t="s">
@@ -6282,7 +6282,7 @@
       <c r="F193" s="1">
         <v>100</v>
       </c>
-      <c r="G193" s="6">
+      <c r="G193" s="2">
         <v>1</v>
       </c>
       <c r="H193" s="1" t="s">
@@ -6311,7 +6311,7 @@
       <c r="F194" s="1">
         <v>100</v>
       </c>
-      <c r="G194" s="6">
+      <c r="G194" s="2">
         <v>1</v>
       </c>
       <c r="H194" s="1" t="s">
@@ -6340,7 +6340,7 @@
       <c r="F195" s="1">
         <v>100</v>
       </c>
-      <c r="G195" s="6">
+      <c r="G195" s="2">
         <v>1</v>
       </c>
       <c r="H195" s="1" t="s">
@@ -6369,7 +6369,7 @@
       <c r="F196" s="1">
         <v>100</v>
       </c>
-      <c r="G196" s="6">
+      <c r="G196" s="2">
         <v>1</v>
       </c>
       <c r="H196" s="1" t="s">
@@ -6398,7 +6398,7 @@
       <c r="F197" s="1">
         <v>100</v>
       </c>
-      <c r="G197" s="6">
+      <c r="G197" s="2">
         <v>1</v>
       </c>
       <c r="H197" s="1" t="s">
@@ -6427,7 +6427,7 @@
       <c r="F198" s="1">
         <v>100</v>
       </c>
-      <c r="G198" s="6">
+      <c r="G198" s="2">
         <v>1</v>
       </c>
       <c r="H198" s="1" t="s">
@@ -6456,7 +6456,7 @@
       <c r="F199" s="1">
         <v>100</v>
       </c>
-      <c r="G199" s="6">
+      <c r="G199" s="2">
         <v>1</v>
       </c>
       <c r="H199" s="1" t="s">
@@ -6480,13 +6480,13 @@
         <v>11</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F200" s="1">
-        <v>100</v>
-      </c>
-      <c r="G200" s="6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G200" s="2">
+        <v>0</v>
       </c>
       <c r="H200" s="1" t="s">
         <v>32</v>
@@ -6514,7 +6514,7 @@
       <c r="F201" s="1">
         <v>100</v>
       </c>
-      <c r="G201" s="6">
+      <c r="G201" s="2">
         <v>1</v>
       </c>
       <c r="H201" s="1" t="s">
@@ -6543,7 +6543,7 @@
       <c r="F202" s="1">
         <v>100</v>
       </c>
-      <c r="G202" s="6">
+      <c r="G202" s="2">
         <v>1</v>
       </c>
       <c r="H202" s="1" t="s">
@@ -6572,7 +6572,7 @@
       <c r="F203" s="1">
         <v>95</v>
       </c>
-      <c r="G203" s="6">
+      <c r="G203" s="2">
         <v>0.95</v>
       </c>
       <c r="H203" s="1" t="s">
@@ -6608,6 +6608,644 @@
         <v>32</v>
       </c>
       <c r="I204" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A205" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C205" s="5">
+        <v>46218</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F205" s="1">
+        <v>100</v>
+      </c>
+      <c r="G205" s="6">
+        <v>1</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I205" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A206" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C206" s="5">
+        <v>46216</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F206" s="1">
+        <v>95</v>
+      </c>
+      <c r="G206" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I206" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A207" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C207" s="5">
+        <v>46216</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F207" s="1">
+        <v>100</v>
+      </c>
+      <c r="G207" s="6">
+        <v>1</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I207" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A208" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C208" s="5">
+        <v>46219</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F208" s="1">
+        <v>100</v>
+      </c>
+      <c r="G208" s="6">
+        <v>1</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I208" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A209" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C209" s="5">
+        <v>46216</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F209" s="1">
+        <v>100</v>
+      </c>
+      <c r="G209" s="6">
+        <v>1</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I209" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A210" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C210" s="5">
+        <v>46217</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F210" s="1">
+        <v>100</v>
+      </c>
+      <c r="G210" s="6">
+        <v>1</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I210" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A211" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C211" s="5">
+        <v>46219</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F211" s="1">
+        <v>100</v>
+      </c>
+      <c r="G211" s="6">
+        <v>1</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I211" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A212" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C212" s="5">
+        <v>46216</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F212" s="1">
+        <v>90</v>
+      </c>
+      <c r="G212" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H212" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I212" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A213" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C213" s="5">
+        <v>46218</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F213" s="1">
+        <v>100</v>
+      </c>
+      <c r="G213" s="6">
+        <v>1</v>
+      </c>
+      <c r="H213" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I213" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A214" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C214" s="5">
+        <v>46218</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F214" s="1">
+        <v>100</v>
+      </c>
+      <c r="G214" s="6">
+        <v>1</v>
+      </c>
+      <c r="H214" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I214" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A215" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C215" s="5">
+        <v>46218</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F215" s="1">
+        <v>100</v>
+      </c>
+      <c r="G215" s="6">
+        <v>1</v>
+      </c>
+      <c r="H215" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I215" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A216" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C216" s="5">
+        <v>46216</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F216" s="1">
+        <v>95</v>
+      </c>
+      <c r="G216" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H216" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I216" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A217" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C217" s="5">
+        <v>46216</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F217" s="1">
+        <v>100</v>
+      </c>
+      <c r="G217" s="6">
+        <v>1</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I217" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A218" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C218" s="5">
+        <v>46216</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F218" s="1">
+        <v>100</v>
+      </c>
+      <c r="G218" s="6">
+        <v>1</v>
+      </c>
+      <c r="H218" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I218" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A219" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C219" s="5">
+        <v>46216</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F219" s="1">
+        <v>100</v>
+      </c>
+      <c r="G219" s="6">
+        <v>1</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I219" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A220" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C220" s="5">
+        <v>46220</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F220" s="1">
+        <v>85</v>
+      </c>
+      <c r="G220" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="H220" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I220" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A221" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C221" s="5">
+        <v>46220</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F221" s="1">
+        <v>100</v>
+      </c>
+      <c r="G221" s="6">
+        <v>1</v>
+      </c>
+      <c r="H221" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I221" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A222" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C222" s="5">
+        <v>46219</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F222" s="1">
+        <v>100</v>
+      </c>
+      <c r="G222" s="6">
+        <v>1</v>
+      </c>
+      <c r="H222" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I222" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A223" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C223" s="5">
+        <v>46220</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F223" s="1">
+        <v>100</v>
+      </c>
+      <c r="G223" s="6">
+        <v>1</v>
+      </c>
+      <c r="H223" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I223" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A224" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C224" s="5">
+        <v>46220</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F224" s="1">
+        <v>0</v>
+      </c>
+      <c r="G224" s="6">
+        <v>0</v>
+      </c>
+      <c r="H224" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I224" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A225" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C225" s="5">
+        <v>46220</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F225" s="1">
+        <v>0</v>
+      </c>
+      <c r="G225" s="6">
+        <v>0</v>
+      </c>
+      <c r="H225" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I225" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A226" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C226" s="5">
+        <v>46220</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F226" s="1">
+        <v>0</v>
+      </c>
+      <c r="G226" s="6">
+        <v>0</v>
+      </c>
+      <c r="H226" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I226" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -6964,15 +7602,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -7223,6 +7852,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7237,14 +7875,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7263,19 +7893,27 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1B134A-3809-4A11-9E24-356BB2157EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A3C3CA-5239-44EA-A021-1533AD3DCB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4300" yWindow="50" windowWidth="28040" windowHeight="13670" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="-60" yWindow="30" windowWidth="18920" windowHeight="12370" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="60">
   <si>
     <t>AssociateName</t>
   </si>
@@ -129,10 +129,10 @@
     <t>June</t>
   </si>
   <si>
-    <t>Bradley Kendrick</t>
+    <t>Doni Lantow</t>
   </si>
   <si>
-    <t>Doni Lantow</t>
+    <t>Bradley Kendrick</t>
   </si>
   <si>
     <t>July</t>
@@ -331,8 +331,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I226" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I226" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I238" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I238" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I204">
     <sortCondition ref="C1:C204"/>
   </sortState>
@@ -682,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I226"/>
+  <dimension ref="A1:I238"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -5714,7 +5714,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>10</v>
@@ -5830,7 +5830,7 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>10</v>
@@ -5859,7 +5859,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>10</v>
@@ -6091,7 +6091,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>10</v>
@@ -6149,7 +6149,7 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>10</v>
@@ -6236,7 +6236,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>10</v>
@@ -6526,7 +6526,7 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>10</v>
@@ -6584,7 +6584,7 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       <c r="F205" s="1">
         <v>100</v>
       </c>
-      <c r="G205" s="6">
+      <c r="G205" s="2">
         <v>1</v>
       </c>
       <c r="H205" s="1" t="s">
@@ -6659,7 +6659,7 @@
       <c r="F206" s="1">
         <v>95</v>
       </c>
-      <c r="G206" s="6">
+      <c r="G206" s="2">
         <v>0.95</v>
       </c>
       <c r="H206" s="1" t="s">
@@ -6688,7 +6688,7 @@
       <c r="F207" s="1">
         <v>100</v>
       </c>
-      <c r="G207" s="6">
+      <c r="G207" s="2">
         <v>1</v>
       </c>
       <c r="H207" s="1" t="s">
@@ -6717,7 +6717,7 @@
       <c r="F208" s="1">
         <v>100</v>
       </c>
-      <c r="G208" s="6">
+      <c r="G208" s="2">
         <v>1</v>
       </c>
       <c r="H208" s="1" t="s">
@@ -6746,7 +6746,7 @@
       <c r="F209" s="1">
         <v>100</v>
       </c>
-      <c r="G209" s="6">
+      <c r="G209" s="2">
         <v>1</v>
       </c>
       <c r="H209" s="1" t="s">
@@ -6775,7 +6775,7 @@
       <c r="F210" s="1">
         <v>100</v>
       </c>
-      <c r="G210" s="6">
+      <c r="G210" s="2">
         <v>1</v>
       </c>
       <c r="H210" s="1" t="s">
@@ -6804,7 +6804,7 @@
       <c r="F211" s="1">
         <v>100</v>
       </c>
-      <c r="G211" s="6">
+      <c r="G211" s="2">
         <v>1</v>
       </c>
       <c r="H211" s="1" t="s">
@@ -6833,7 +6833,7 @@
       <c r="F212" s="1">
         <v>90</v>
       </c>
-      <c r="G212" s="6">
+      <c r="G212" s="2">
         <v>0.9</v>
       </c>
       <c r="H212" s="1" t="s">
@@ -6862,7 +6862,7 @@
       <c r="F213" s="1">
         <v>100</v>
       </c>
-      <c r="G213" s="6">
+      <c r="G213" s="2">
         <v>1</v>
       </c>
       <c r="H213" s="1" t="s">
@@ -6891,7 +6891,7 @@
       <c r="F214" s="1">
         <v>100</v>
       </c>
-      <c r="G214" s="6">
+      <c r="G214" s="2">
         <v>1</v>
       </c>
       <c r="H214" s="1" t="s">
@@ -6920,7 +6920,7 @@
       <c r="F215" s="1">
         <v>100</v>
       </c>
-      <c r="G215" s="6">
+      <c r="G215" s="2">
         <v>1</v>
       </c>
       <c r="H215" s="1" t="s">
@@ -6949,7 +6949,7 @@
       <c r="F216" s="1">
         <v>95</v>
       </c>
-      <c r="G216" s="6">
+      <c r="G216" s="2">
         <v>0.95</v>
       </c>
       <c r="H216" s="1" t="s">
@@ -6961,7 +6961,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>10</v>
@@ -6978,7 +6978,7 @@
       <c r="F217" s="1">
         <v>100</v>
       </c>
-      <c r="G217" s="6">
+      <c r="G217" s="2">
         <v>1</v>
       </c>
       <c r="H217" s="1" t="s">
@@ -6990,7 +6990,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>10</v>
@@ -7007,7 +7007,7 @@
       <c r="F218" s="1">
         <v>100</v>
       </c>
-      <c r="G218" s="6">
+      <c r="G218" s="2">
         <v>1</v>
       </c>
       <c r="H218" s="1" t="s">
@@ -7036,7 +7036,7 @@
       <c r="F219" s="1">
         <v>100</v>
       </c>
-      <c r="G219" s="6">
+      <c r="G219" s="2">
         <v>1</v>
       </c>
       <c r="H219" s="1" t="s">
@@ -7065,7 +7065,7 @@
       <c r="F220" s="1">
         <v>85</v>
       </c>
-      <c r="G220" s="6">
+      <c r="G220" s="2">
         <v>0.85</v>
       </c>
       <c r="H220" s="1" t="s">
@@ -7094,7 +7094,7 @@
       <c r="F221" s="1">
         <v>100</v>
       </c>
-      <c r="G221" s="6">
+      <c r="G221" s="2">
         <v>1</v>
       </c>
       <c r="H221" s="1" t="s">
@@ -7123,7 +7123,7 @@
       <c r="F222" s="1">
         <v>100</v>
       </c>
-      <c r="G222" s="6">
+      <c r="G222" s="2">
         <v>1</v>
       </c>
       <c r="H222" s="1" t="s">
@@ -7152,7 +7152,7 @@
       <c r="F223" s="1">
         <v>100</v>
       </c>
-      <c r="G223" s="6">
+      <c r="G223" s="2">
         <v>1</v>
       </c>
       <c r="H223" s="1" t="s">
@@ -7181,7 +7181,7 @@
       <c r="F224" s="1">
         <v>0</v>
       </c>
-      <c r="G224" s="6">
+      <c r="G224" s="2">
         <v>0</v>
       </c>
       <c r="H224" s="1" t="s">
@@ -7193,7 +7193,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>10</v>
@@ -7210,7 +7210,7 @@
       <c r="F225" s="1">
         <v>0</v>
       </c>
-      <c r="G225" s="6">
+      <c r="G225" s="2">
         <v>0</v>
       </c>
       <c r="H225" s="1" t="s">
@@ -7222,7 +7222,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>10</v>
@@ -7239,13 +7239,361 @@
       <c r="F226" s="1">
         <v>0</v>
       </c>
-      <c r="G226" s="6">
+      <c r="G226" s="2">
         <v>0</v>
       </c>
       <c r="H226" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I226" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A227" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C227" s="5">
+        <v>46225</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F227" s="1">
+        <v>100</v>
+      </c>
+      <c r="G227" s="6">
+        <v>1</v>
+      </c>
+      <c r="H227" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I227" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A228" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C228" s="5">
+        <v>46223</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F228" s="1">
+        <v>100</v>
+      </c>
+      <c r="G228" s="6">
+        <v>1</v>
+      </c>
+      <c r="H228" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I228" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A229" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C229" s="5">
+        <v>46224</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F229" s="1">
+        <v>100</v>
+      </c>
+      <c r="G229" s="6">
+        <v>1</v>
+      </c>
+      <c r="H229" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I229" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A230" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C230" s="5">
+        <v>46220</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F230" s="1">
+        <v>95</v>
+      </c>
+      <c r="G230" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H230" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I230" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A231" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C231" s="5">
+        <v>46223</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F231" s="1">
+        <v>100</v>
+      </c>
+      <c r="G231" s="6">
+        <v>1</v>
+      </c>
+      <c r="H231" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I231" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A232" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C232" s="5">
+        <v>46226</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F232" s="1">
+        <v>100</v>
+      </c>
+      <c r="G232" s="6">
+        <v>1</v>
+      </c>
+      <c r="H232" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I232" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A233" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C233" s="5">
+        <v>46223</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F233" s="1">
+        <v>100</v>
+      </c>
+      <c r="G233" s="6">
+        <v>1</v>
+      </c>
+      <c r="H233" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I233" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A234" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C234" s="5">
+        <v>46225</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F234" s="1">
+        <v>100</v>
+      </c>
+      <c r="G234" s="6">
+        <v>1</v>
+      </c>
+      <c r="H234" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I234" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A235" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C235" s="5">
+        <v>46225</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F235" s="1">
+        <v>100</v>
+      </c>
+      <c r="G235" s="6">
+        <v>1</v>
+      </c>
+      <c r="H235" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I235" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A236" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C236" s="5">
+        <v>46225</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F236" s="1">
+        <v>100</v>
+      </c>
+      <c r="G236" s="6">
+        <v>1</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I236" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A237" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C237" s="5">
+        <v>46224</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F237" s="1">
+        <v>0</v>
+      </c>
+      <c r="G237" s="6">
+        <v>0</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I237" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A238" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C238" s="5">
+        <v>46225</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F238" s="1">
+        <v>100</v>
+      </c>
+      <c r="G238" s="6">
+        <v>1</v>
+      </c>
+      <c r="H238" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I238" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -7543,7 +7891,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -7577,7 +7925,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
@@ -7602,6 +7950,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -7852,15 +8209,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7875,6 +8223,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7893,27 +8249,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A3C3CA-5239-44EA-A021-1533AD3DCB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A4EFFF-47DC-4CF8-A847-2D992CB15A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="30" windowWidth="18920" windowHeight="12370" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="-50" yWindow="20" windowWidth="34140" windowHeight="12370" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="60">
   <si>
     <t>AssociateName</t>
   </si>
@@ -331,8 +331,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I238" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I238" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I247" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I247" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I204">
     <sortCondition ref="C1:C204"/>
   </sortState>
@@ -682,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I238"/>
+  <dimension ref="A1:I247"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -7268,7 +7268,7 @@
       <c r="F227" s="1">
         <v>100</v>
       </c>
-      <c r="G227" s="6">
+      <c r="G227" s="2">
         <v>1</v>
       </c>
       <c r="H227" s="1" t="s">
@@ -7297,7 +7297,7 @@
       <c r="F228" s="1">
         <v>100</v>
       </c>
-      <c r="G228" s="6">
+      <c r="G228" s="2">
         <v>1</v>
       </c>
       <c r="H228" s="1" t="s">
@@ -7326,7 +7326,7 @@
       <c r="F229" s="1">
         <v>100</v>
       </c>
-      <c r="G229" s="6">
+      <c r="G229" s="2">
         <v>1</v>
       </c>
       <c r="H229" s="1" t="s">
@@ -7355,7 +7355,7 @@
       <c r="F230" s="1">
         <v>95</v>
       </c>
-      <c r="G230" s="6">
+      <c r="G230" s="2">
         <v>0.95</v>
       </c>
       <c r="H230" s="1" t="s">
@@ -7384,7 +7384,7 @@
       <c r="F231" s="1">
         <v>100</v>
       </c>
-      <c r="G231" s="6">
+      <c r="G231" s="2">
         <v>1</v>
       </c>
       <c r="H231" s="1" t="s">
@@ -7413,7 +7413,7 @@
       <c r="F232" s="1">
         <v>100</v>
       </c>
-      <c r="G232" s="6">
+      <c r="G232" s="2">
         <v>1</v>
       </c>
       <c r="H232" s="1" t="s">
@@ -7442,7 +7442,7 @@
       <c r="F233" s="1">
         <v>100</v>
       </c>
-      <c r="G233" s="6">
+      <c r="G233" s="2">
         <v>1</v>
       </c>
       <c r="H233" s="1" t="s">
@@ -7471,7 +7471,7 @@
       <c r="F234" s="1">
         <v>100</v>
       </c>
-      <c r="G234" s="6">
+      <c r="G234" s="2">
         <v>1</v>
       </c>
       <c r="H234" s="1" t="s">
@@ -7500,7 +7500,7 @@
       <c r="F235" s="1">
         <v>100</v>
       </c>
-      <c r="G235" s="6">
+      <c r="G235" s="2">
         <v>1</v>
       </c>
       <c r="H235" s="1" t="s">
@@ -7529,7 +7529,7 @@
       <c r="F236" s="1">
         <v>100</v>
       </c>
-      <c r="G236" s="6">
+      <c r="G236" s="2">
         <v>1</v>
       </c>
       <c r="H236" s="1" t="s">
@@ -7558,7 +7558,7 @@
       <c r="F237" s="1">
         <v>0</v>
       </c>
-      <c r="G237" s="6">
+      <c r="G237" s="2">
         <v>0</v>
       </c>
       <c r="H237" s="1" t="s">
@@ -7587,13 +7587,274 @@
       <c r="F238" s="1">
         <v>100</v>
       </c>
-      <c r="G238" s="6">
+      <c r="G238" s="2">
         <v>1</v>
       </c>
       <c r="H238" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I238" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A239" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C239" s="5">
+        <v>46227</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F239" s="1">
+        <v>90</v>
+      </c>
+      <c r="G239" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H239" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I239" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A240" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C240" s="5">
+        <v>46227</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F240" s="1">
+        <v>100</v>
+      </c>
+      <c r="G240" s="6">
+        <v>1</v>
+      </c>
+      <c r="H240" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I240" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A241" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C241" s="5">
+        <v>46227</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F241" s="1">
+        <v>100</v>
+      </c>
+      <c r="G241" s="6">
+        <v>1</v>
+      </c>
+      <c r="H241" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I241" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A242" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C242" s="5">
+        <v>46218</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F242" s="1">
+        <v>100</v>
+      </c>
+      <c r="G242" s="6">
+        <v>1</v>
+      </c>
+      <c r="H242" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I242" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A243" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C243" s="5">
+        <v>46224</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F243" s="1">
+        <v>90</v>
+      </c>
+      <c r="G243" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H243" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I243" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A244" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C244" s="5">
+        <v>46212</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F244" s="1">
+        <v>95</v>
+      </c>
+      <c r="G244" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H244" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I244" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A245" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C245" s="5">
+        <v>46216</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F245" s="1">
+        <v>95</v>
+      </c>
+      <c r="G245" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H245" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I245" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A246" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C246" s="5">
+        <v>46225</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F246" s="1">
+        <v>95</v>
+      </c>
+      <c r="G246" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H246" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I246" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A247" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C247" s="5">
+        <v>46224</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F247" s="1">
+        <v>100</v>
+      </c>
+      <c r="G247" s="6">
+        <v>1</v>
+      </c>
+      <c r="H247" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I247" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -8252,14 +8513,14 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A4EFFF-47DC-4CF8-A847-2D992CB15A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE3851B-E045-4011-89D8-AA2A398EAED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50" yWindow="20" windowWidth="34140" windowHeight="12370" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="100" yWindow="0" windowWidth="32650" windowHeight="12920" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="60">
   <si>
     <t>AssociateName</t>
   </si>
@@ -331,10 +331,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I247" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I247" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I204">
-    <sortCondition ref="C1:C204"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I234" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I234" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I196">
+    <sortCondition ref="C1:C196"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
@@ -682,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I247"/>
+  <dimension ref="A1:I234"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -5714,13 +5714,13 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C174" s="5">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>11</v>
@@ -5729,10 +5729,10 @@
         <v>12</v>
       </c>
       <c r="F174" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G174" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H174" s="1" t="s">
         <v>29</v>
@@ -5743,25 +5743,25 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C175" s="5">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F175" s="1">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G175" s="2">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H175" s="1" t="s">
         <v>29</v>
@@ -5772,7 +5772,7 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>19</v>
@@ -5781,16 +5781,16 @@
         <v>46197</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F176" s="1">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G176" s="2">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H176" s="1" t="s">
         <v>29</v>
@@ -5801,25 +5801,25 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C177" s="5">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F177" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G177" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H177" s="1" t="s">
         <v>29</v>
@@ -5830,10 +5830,10 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C178" s="5">
         <v>46198</v>
@@ -5845,10 +5845,10 @@
         <v>12</v>
       </c>
       <c r="F178" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G178" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H178" s="1" t="s">
         <v>29</v>
@@ -5859,7 +5859,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>10</v>
@@ -5874,10 +5874,10 @@
         <v>12</v>
       </c>
       <c r="F179" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G179" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H179" s="1" t="s">
         <v>29</v>
@@ -5888,25 +5888,25 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C180" s="5">
         <v>46198</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F180" s="1">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="G180" s="2">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="H180" s="1" t="s">
         <v>29</v>
@@ -5917,10 +5917,10 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C181" s="5">
         <v>46198</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>10</v>
@@ -5975,7 +5975,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>10</v>
@@ -5984,16 +5984,16 @@
         <v>46198</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F183" s="1">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="G183" s="2">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="H183" s="1" t="s">
         <v>29</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C184" s="5">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>11</v>
@@ -6019,10 +6019,10 @@
         <v>12</v>
       </c>
       <c r="F184" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G184" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H184" s="1" t="s">
         <v>29</v>
@@ -6033,28 +6033,28 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C185" s="5">
-        <v>46198</v>
+        <v>46205</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F185" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G185" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I185" s="1">
         <v>2026</v>
@@ -6062,28 +6062,28 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C186" s="5">
-        <v>46198</v>
+        <v>46209</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F186" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G186" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I186" s="1">
         <v>2026</v>
@@ -6091,13 +6091,13 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C187" s="5">
-        <v>46198</v>
+        <v>46209</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>11</v>
@@ -6112,7 +6112,7 @@
         <v>1</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I187" s="1">
         <v>2026</v>
@@ -6126,7 +6126,7 @@
         <v>10</v>
       </c>
       <c r="C188" s="5">
-        <v>46199</v>
+        <v>46210</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>11</v>
@@ -6141,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I188" s="1">
         <v>2026</v>
@@ -6149,16 +6149,16 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C189" s="5">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>12</v>
@@ -6170,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I189" s="1">
         <v>2026</v>
@@ -6178,25 +6178,25 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C190" s="5">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F190" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G190" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H190" s="1" t="s">
         <v>32</v>
@@ -6207,13 +6207,13 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C191" s="5">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>11</v>
@@ -6236,16 +6236,16 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C192" s="5">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>12</v>
@@ -6265,13 +6265,13 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C193" s="5">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>11</v>
@@ -6294,25 +6294,25 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C194" s="5">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F194" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G194" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H194" s="1" t="s">
         <v>32</v>
@@ -6323,13 +6323,13 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C195" s="5">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>12</v>
@@ -6352,25 +6352,25 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C196" s="5">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F196" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G196" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H196" s="1" t="s">
         <v>32</v>
@@ -6381,13 +6381,13 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C197" s="5">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>11</v>
@@ -6410,13 +6410,13 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C198" s="5">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>11</v>
@@ -6425,10 +6425,10 @@
         <v>12</v>
       </c>
       <c r="F198" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G198" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H198" s="1" t="s">
         <v>32</v>
@@ -6439,13 +6439,13 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C199" s="5">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>11</v>
@@ -6468,25 +6468,25 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C200" s="5">
-        <v>46212</v>
+        <v>46219</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F200" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H200" s="1" t="s">
         <v>32</v>
@@ -6497,16 +6497,16 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C201" s="5">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>12</v>
@@ -6526,13 +6526,13 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C202" s="5">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>11</v>
@@ -6555,25 +6555,25 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C203" s="5">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F203" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G203" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H203" s="1" t="s">
         <v>32</v>
@@ -6584,25 +6584,25 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C204" s="5">
-        <v>46233</v>
+        <v>46216</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F204" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G204" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H204" s="1" t="s">
         <v>32</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C205" s="5">
         <v>46218</v>
@@ -6642,13 +6642,13 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C206" s="5">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>11</v>
@@ -6657,10 +6657,10 @@
         <v>12</v>
       </c>
       <c r="F206" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G206" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H206" s="1" t="s">
         <v>32</v>
@@ -6671,13 +6671,13 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C207" s="5">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>11</v>
@@ -6700,13 +6700,13 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C208" s="5">
-        <v>46219</v>
+        <v>46216</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>11</v>
@@ -6715,10 +6715,10 @@
         <v>12</v>
       </c>
       <c r="F208" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G208" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H208" s="1" t="s">
         <v>32</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C209" s="5">
         <v>46216</v>
@@ -6758,13 +6758,13 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C210" s="5">
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>11</v>
@@ -6773,10 +6773,10 @@
         <v>12</v>
       </c>
       <c r="F210" s="1">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G210" s="2">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H210" s="1" t="s">
         <v>32</v>
@@ -6787,13 +6787,13 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C211" s="5">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>11</v>
@@ -6822,7 +6822,7 @@
         <v>10</v>
       </c>
       <c r="C212" s="5">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>11</v>
@@ -6831,10 +6831,10 @@
         <v>12</v>
       </c>
       <c r="F212" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G212" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H212" s="1" t="s">
         <v>32</v>
@@ -6845,13 +6845,13 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C213" s="5">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>11</v>
@@ -6874,25 +6874,25 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C214" s="5">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F214" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G214" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H214" s="1" t="s">
         <v>32</v>
@@ -6903,13 +6903,13 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C215" s="5">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>11</v>
@@ -6932,13 +6932,13 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C216" s="5">
-        <v>46216</v>
+        <v>46226</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>11</v>
@@ -6947,10 +6947,10 @@
         <v>12</v>
       </c>
       <c r="F216" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G216" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H216" s="1" t="s">
         <v>32</v>
@@ -6961,13 +6961,13 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C217" s="5">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>11</v>
@@ -6990,13 +6990,13 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C218" s="5">
-        <v>46216</v>
+        <v>46225</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>11</v>
@@ -7019,13 +7019,13 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C219" s="5">
-        <v>46216</v>
+        <v>46225</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>11</v>
@@ -7048,25 +7048,25 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C220" s="5">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F220" s="1">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G220" s="2">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H220" s="1" t="s">
         <v>32</v>
@@ -7077,25 +7077,25 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C221" s="5">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F221" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G221" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H221" s="1" t="s">
         <v>32</v>
@@ -7106,13 +7106,13 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C222" s="5">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>11</v>
@@ -7135,13 +7135,13 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C223" s="5">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>11</v>
@@ -7150,10 +7150,10 @@
         <v>12</v>
       </c>
       <c r="F223" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G223" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H223" s="1" t="s">
         <v>32</v>
@@ -7164,25 +7164,25 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C224" s="5">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F224" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G224" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H224" s="1" t="s">
         <v>32</v>
@@ -7193,25 +7193,25 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C225" s="5">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F225" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G225" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H225" s="1" t="s">
         <v>32</v>
@@ -7222,25 +7222,25 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C226" s="5">
-        <v>46220</v>
+        <v>46218</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F226" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G226" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H226" s="1" t="s">
         <v>32</v>
@@ -7251,25 +7251,25 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C227" s="5">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F227" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G227" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H227" s="1" t="s">
         <v>32</v>
@@ -7280,13 +7280,13 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C228" s="5">
-        <v>46223</v>
+        <v>46212</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>11</v>
@@ -7295,10 +7295,10 @@
         <v>12</v>
       </c>
       <c r="F228" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G228" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H228" s="1" t="s">
         <v>32</v>
@@ -7309,25 +7309,25 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C229" s="5">
-        <v>46224</v>
+        <v>46216</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F229" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G229" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H229" s="1" t="s">
         <v>32</v>
@@ -7338,13 +7338,13 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C230" s="5">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>11</v>
@@ -7367,13 +7367,13 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C231" s="5">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>11</v>
@@ -7396,13 +7396,13 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C232" s="5">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>11</v>
@@ -7413,7 +7413,7 @@
       <c r="F232" s="1">
         <v>100</v>
       </c>
-      <c r="G232" s="2">
+      <c r="G232" s="6">
         <v>1</v>
       </c>
       <c r="H232" s="1" t="s">
@@ -7425,13 +7425,13 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C233" s="5">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>11</v>
@@ -7442,7 +7442,7 @@
       <c r="F233" s="1">
         <v>100</v>
       </c>
-      <c r="G233" s="2">
+      <c r="G233" s="6">
         <v>1</v>
       </c>
       <c r="H233" s="1" t="s">
@@ -7454,10 +7454,10 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C234" s="5">
         <v>46225</v>
@@ -7471,390 +7471,13 @@
       <c r="F234" s="1">
         <v>100</v>
       </c>
-      <c r="G234" s="2">
+      <c r="G234" s="6">
         <v>1</v>
       </c>
       <c r="H234" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I234" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A235" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C235" s="5">
-        <v>46225</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E235" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F235" s="1">
-        <v>100</v>
-      </c>
-      <c r="G235" s="2">
-        <v>1</v>
-      </c>
-      <c r="H235" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I235" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A236" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C236" s="5">
-        <v>46225</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E236" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F236" s="1">
-        <v>100</v>
-      </c>
-      <c r="G236" s="2">
-        <v>1</v>
-      </c>
-      <c r="H236" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I236" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A237" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C237" s="5">
-        <v>46224</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E237" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F237" s="1">
-        <v>0</v>
-      </c>
-      <c r="G237" s="2">
-        <v>0</v>
-      </c>
-      <c r="H237" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I237" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A238" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C238" s="5">
-        <v>46225</v>
-      </c>
-      <c r="D238" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E238" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F238" s="1">
-        <v>100</v>
-      </c>
-      <c r="G238" s="2">
-        <v>1</v>
-      </c>
-      <c r="H238" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I238" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A239" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C239" s="5">
-        <v>46227</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E239" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F239" s="1">
-        <v>90</v>
-      </c>
-      <c r="G239" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="H239" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I239" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A240" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C240" s="5">
-        <v>46227</v>
-      </c>
-      <c r="D240" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E240" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F240" s="1">
-        <v>100</v>
-      </c>
-      <c r="G240" s="6">
-        <v>1</v>
-      </c>
-      <c r="H240" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I240" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A241" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C241" s="5">
-        <v>46227</v>
-      </c>
-      <c r="D241" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E241" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F241" s="1">
-        <v>100</v>
-      </c>
-      <c r="G241" s="6">
-        <v>1</v>
-      </c>
-      <c r="H241" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I241" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A242" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C242" s="5">
-        <v>46218</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E242" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F242" s="1">
-        <v>100</v>
-      </c>
-      <c r="G242" s="6">
-        <v>1</v>
-      </c>
-      <c r="H242" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I242" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A243" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C243" s="5">
-        <v>46224</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E243" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F243" s="1">
-        <v>90</v>
-      </c>
-      <c r="G243" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="H243" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I243" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A244" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C244" s="5">
-        <v>46212</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E244" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F244" s="1">
-        <v>95</v>
-      </c>
-      <c r="G244" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="H244" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I244" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A245" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C245" s="5">
-        <v>46216</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E245" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F245" s="1">
-        <v>95</v>
-      </c>
-      <c r="G245" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="H245" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I245" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A246" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C246" s="5">
-        <v>46225</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E246" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F246" s="1">
-        <v>95</v>
-      </c>
-      <c r="G246" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="H246" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I246" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A247" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C247" s="5">
-        <v>46224</v>
-      </c>
-      <c r="D247" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E247" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F247" s="1">
-        <v>100</v>
-      </c>
-      <c r="G247" s="6">
-        <v>1</v>
-      </c>
-      <c r="H247" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I247" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -8220,6 +7843,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -8470,19 +8106,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>
@@ -8492,6 +8115,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8508,21 +8148,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE3851B-E045-4011-89D8-AA2A398EAED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC83BF24-87F9-4496-8FD2-4D77CEB58BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="0" windowWidth="32650" windowHeight="12920" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="2510" yWindow="160" windowWidth="28480" windowHeight="13520" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="60">
   <si>
     <t>AssociateName</t>
   </si>
@@ -331,8 +331,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I234" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I234" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I241" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I241" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I196">
     <sortCondition ref="C1:C196"/>
   </sortState>
@@ -682,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I234"/>
+  <dimension ref="A1:I241"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -7413,7 +7413,7 @@
       <c r="F232" s="1">
         <v>100</v>
       </c>
-      <c r="G232" s="6">
+      <c r="G232" s="2">
         <v>1</v>
       </c>
       <c r="H232" s="1" t="s">
@@ -7442,7 +7442,7 @@
       <c r="F233" s="1">
         <v>100</v>
       </c>
-      <c r="G233" s="6">
+      <c r="G233" s="2">
         <v>1</v>
       </c>
       <c r="H233" s="1" t="s">
@@ -7471,13 +7471,216 @@
       <c r="F234" s="1">
         <v>100</v>
       </c>
-      <c r="G234" s="6">
+      <c r="G234" s="2">
         <v>1</v>
       </c>
       <c r="H234" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I234" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A235" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C235" s="5">
+        <v>46230</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F235" s="1">
+        <v>100</v>
+      </c>
+      <c r="G235" s="6">
+        <v>1</v>
+      </c>
+      <c r="H235" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I235" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A236" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C236" s="5">
+        <v>46224</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F236" s="1">
+        <v>90</v>
+      </c>
+      <c r="G236" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I236" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A237" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C237" s="5">
+        <v>46217</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F237" s="1">
+        <v>100</v>
+      </c>
+      <c r="G237" s="6">
+        <v>1</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I237" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A238" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C238" s="5">
+        <v>46226</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F238" s="1">
+        <v>95</v>
+      </c>
+      <c r="G238" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H238" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I238" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A239" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C239" s="5">
+        <v>46231</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F239" s="1">
+        <v>100</v>
+      </c>
+      <c r="G239" s="6">
+        <v>1</v>
+      </c>
+      <c r="H239" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I239" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A240" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C240" s="5">
+        <v>46226</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F240" s="1">
+        <v>100</v>
+      </c>
+      <c r="G240" s="6">
+        <v>1</v>
+      </c>
+      <c r="H240" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I240" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A241" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C241" s="5">
+        <v>46225</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F241" s="1">
+        <v>100</v>
+      </c>
+      <c r="G241" s="6">
+        <v>1</v>
+      </c>
+      <c r="H241" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I241" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -7843,19 +8046,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -8106,6 +8296,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>
@@ -8115,23 +8318,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8148,4 +8334,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC83BF24-87F9-4496-8FD2-4D77CEB58BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E74024-B571-4297-BBF2-F7458C0D8464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2510" yWindow="160" windowWidth="28480" windowHeight="13520" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="7050" yWindow="150" windowWidth="27410" windowHeight="13660" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="60">
   <si>
     <t>AssociateName</t>
   </si>
@@ -331,8 +331,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I241" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I241" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I246" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I246" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I196">
     <sortCondition ref="C1:C196"/>
   </sortState>
@@ -682,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I241"/>
+  <dimension ref="A1:I246"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -7500,7 +7500,7 @@
       <c r="F235" s="1">
         <v>100</v>
       </c>
-      <c r="G235" s="6">
+      <c r="G235" s="2">
         <v>1</v>
       </c>
       <c r="H235" s="1" t="s">
@@ -7529,7 +7529,7 @@
       <c r="F236" s="1">
         <v>90</v>
       </c>
-      <c r="G236" s="6">
+      <c r="G236" s="2">
         <v>0.9</v>
       </c>
       <c r="H236" s="1" t="s">
@@ -7558,7 +7558,7 @@
       <c r="F237" s="1">
         <v>100</v>
       </c>
-      <c r="G237" s="6">
+      <c r="G237" s="2">
         <v>1</v>
       </c>
       <c r="H237" s="1" t="s">
@@ -7587,7 +7587,7 @@
       <c r="F238" s="1">
         <v>95</v>
       </c>
-      <c r="G238" s="6">
+      <c r="G238" s="2">
         <v>0.95</v>
       </c>
       <c r="H238" s="1" t="s">
@@ -7616,7 +7616,7 @@
       <c r="F239" s="1">
         <v>100</v>
       </c>
-      <c r="G239" s="6">
+      <c r="G239" s="2">
         <v>1</v>
       </c>
       <c r="H239" s="1" t="s">
@@ -7645,7 +7645,7 @@
       <c r="F240" s="1">
         <v>100</v>
       </c>
-      <c r="G240" s="6">
+      <c r="G240" s="2">
         <v>1</v>
       </c>
       <c r="H240" s="1" t="s">
@@ -7674,13 +7674,158 @@
       <c r="F241" s="1">
         <v>100</v>
       </c>
-      <c r="G241" s="6">
+      <c r="G241" s="2">
         <v>1</v>
       </c>
       <c r="H241" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I241" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A242" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C242" s="5">
+        <v>46216</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F242" s="1">
+        <v>100</v>
+      </c>
+      <c r="G242" s="6">
+        <v>1</v>
+      </c>
+      <c r="H242" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I242" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A243" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C243" s="5">
+        <v>46223</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F243" s="1">
+        <v>100</v>
+      </c>
+      <c r="G243" s="6">
+        <v>1</v>
+      </c>
+      <c r="H243" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I243" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A244" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C244" s="5">
+        <v>46230</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F244" s="1">
+        <v>100</v>
+      </c>
+      <c r="G244" s="6">
+        <v>1</v>
+      </c>
+      <c r="H244" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I244" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A245" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C245" s="5">
+        <v>46234</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F245" s="1">
+        <v>100</v>
+      </c>
+      <c r="G245" s="6">
+        <v>1</v>
+      </c>
+      <c r="H245" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I245" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A246" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C246" s="5">
+        <v>46233</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F246" s="1">
+        <v>100</v>
+      </c>
+      <c r="G246" s="6">
+        <v>1</v>
+      </c>
+      <c r="H246" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I246" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -8339,16 +8484,22 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{4360c1e8-deec-49bb-904e-9331088b2a03}" enabled="0" method="" siteId="{4360c1e8-deec-49bb-904e-9331088b2a03}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E74024-B571-4297-BBF2-F7458C0D8464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1DFDF3-1466-425D-991A-BA42094E09C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7050" yWindow="150" windowWidth="27410" windowHeight="13660" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="7760" yWindow="30" windowWidth="22720" windowHeight="13660" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="60">
   <si>
     <t>AssociateName</t>
   </si>
@@ -331,8 +331,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I246" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I246" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I248" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I248" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I196">
     <sortCondition ref="C1:C196"/>
   </sortState>
@@ -682,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I246"/>
+  <dimension ref="A1:I248"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -7703,7 +7703,7 @@
       <c r="F242" s="1">
         <v>100</v>
       </c>
-      <c r="G242" s="6">
+      <c r="G242" s="2">
         <v>1</v>
       </c>
       <c r="H242" s="1" t="s">
@@ -7732,7 +7732,7 @@
       <c r="F243" s="1">
         <v>100</v>
       </c>
-      <c r="G243" s="6">
+      <c r="G243" s="2">
         <v>1</v>
       </c>
       <c r="H243" s="1" t="s">
@@ -7761,7 +7761,7 @@
       <c r="F244" s="1">
         <v>100</v>
       </c>
-      <c r="G244" s="6">
+      <c r="G244" s="2">
         <v>1</v>
       </c>
       <c r="H244" s="1" t="s">
@@ -7790,7 +7790,7 @@
       <c r="F245" s="1">
         <v>100</v>
       </c>
-      <c r="G245" s="6">
+      <c r="G245" s="2">
         <v>1</v>
       </c>
       <c r="H245" s="1" t="s">
@@ -7819,13 +7819,71 @@
       <c r="F246" s="1">
         <v>100</v>
       </c>
-      <c r="G246" s="6">
+      <c r="G246" s="2">
         <v>1</v>
       </c>
       <c r="H246" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I246" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A247" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C247" s="5">
+        <v>46233</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F247" s="1">
+        <v>100</v>
+      </c>
+      <c r="G247" s="6">
+        <v>1</v>
+      </c>
+      <c r="H247" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I247" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A248" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C248" s="5">
+        <v>46234</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F248" s="1">
+        <v>90</v>
+      </c>
+      <c r="G248" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H248" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I248" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -8191,6 +8249,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -8441,19 +8512,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>
@@ -8463,6 +8521,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8481,23 +8556,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{4360c1e8-deec-49bb-904e-9331088b2a03}" enabled="0" method="" siteId="{4360c1e8-deec-49bb-904e-9331088b2a03}" removed="1"/>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBDD90E-398A-4C12-B654-DA6E1FB2C7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0E99A8-9497-4CC9-B8B7-916358FEAD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="40" windowWidth="26470" windowHeight="13660" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="-50" yWindow="50" windowWidth="26620" windowHeight="13660" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="65">
   <si>
     <t>AssociateName</t>
   </si>
@@ -141,6 +141,12 @@
     <t>August</t>
   </si>
   <si>
+    <t>Terra McGee</t>
+  </si>
+  <si>
+    <t>Tiffany Lewis</t>
+  </si>
+  <si>
     <t>ManagerName</t>
   </si>
   <si>
@@ -213,16 +219,10 @@
     <t>doni.lantow@lplfinancial.com</t>
   </si>
   <si>
-    <t>Terra McGee</t>
-  </si>
-  <si>
     <t>Terra.McGee@lplfinancial.com</t>
   </si>
   <si>
     <t>Bradley.Kendrick@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>Tiffany Lewis</t>
   </si>
   <si>
     <t>tiffany.lewis1@lplfinancial.com</t>
@@ -346,8 +346,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I293" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:I293" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I313" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:I313" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I196">
     <sortCondition ref="C1:C196"/>
   </sortState>
@@ -697,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I293"/>
+  <dimension ref="A1:I313"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
@@ -8530,7 +8530,7 @@
       <c r="F270" s="1">
         <v>90</v>
       </c>
-      <c r="G270" s="6">
+      <c r="G270" s="2">
         <v>0.9</v>
       </c>
       <c r="H270" s="1" t="s">
@@ -8559,7 +8559,7 @@
       <c r="F271" s="1">
         <v>100</v>
       </c>
-      <c r="G271" s="6">
+      <c r="G271" s="2">
         <v>1</v>
       </c>
       <c r="H271" s="1" t="s">
@@ -8588,7 +8588,7 @@
       <c r="F272" s="1">
         <v>100</v>
       </c>
-      <c r="G272" s="6">
+      <c r="G272" s="2">
         <v>1</v>
       </c>
       <c r="H272" s="1" t="s">
@@ -8617,7 +8617,7 @@
       <c r="F273" s="1">
         <v>100</v>
       </c>
-      <c r="G273" s="6">
+      <c r="G273" s="2">
         <v>1</v>
       </c>
       <c r="H273" s="1" t="s">
@@ -8646,7 +8646,7 @@
       <c r="F274" s="1">
         <v>100</v>
       </c>
-      <c r="G274" s="6">
+      <c r="G274" s="2">
         <v>1</v>
       </c>
       <c r="H274" s="1" t="s">
@@ -8675,7 +8675,7 @@
       <c r="F275" s="1">
         <v>100</v>
       </c>
-      <c r="G275" s="6">
+      <c r="G275" s="2">
         <v>1</v>
       </c>
       <c r="H275" s="1" t="s">
@@ -8704,7 +8704,7 @@
       <c r="F276" s="1">
         <v>100</v>
       </c>
-      <c r="G276" s="6">
+      <c r="G276" s="2">
         <v>1</v>
       </c>
       <c r="H276" s="1" t="s">
@@ -8733,7 +8733,7 @@
       <c r="F277" s="1">
         <v>100</v>
       </c>
-      <c r="G277" s="6">
+      <c r="G277" s="2">
         <v>1</v>
       </c>
       <c r="H277" s="1" t="s">
@@ -8762,7 +8762,7 @@
       <c r="F278" s="1">
         <v>100</v>
       </c>
-      <c r="G278" s="6">
+      <c r="G278" s="2">
         <v>1</v>
       </c>
       <c r="H278" s="1" t="s">
@@ -8791,7 +8791,7 @@
       <c r="F279" s="1">
         <v>100</v>
       </c>
-      <c r="G279" s="6">
+      <c r="G279" s="2">
         <v>1</v>
       </c>
       <c r="H279" s="1" t="s">
@@ -8820,7 +8820,7 @@
       <c r="F280" s="1">
         <v>100</v>
       </c>
-      <c r="G280" s="6">
+      <c r="G280" s="2">
         <v>1</v>
       </c>
       <c r="H280" s="1" t="s">
@@ -8849,7 +8849,7 @@
       <c r="F281" s="1">
         <v>100</v>
       </c>
-      <c r="G281" s="6">
+      <c r="G281" s="2">
         <v>1</v>
       </c>
       <c r="H281" s="1" t="s">
@@ -8878,7 +8878,7 @@
       <c r="F282" s="1">
         <v>100</v>
       </c>
-      <c r="G282" s="6">
+      <c r="G282" s="2">
         <v>1</v>
       </c>
       <c r="H282" s="1" t="s">
@@ -8907,7 +8907,7 @@
       <c r="F283" s="1">
         <v>100</v>
       </c>
-      <c r="G283" s="6">
+      <c r="G283" s="2">
         <v>1</v>
       </c>
       <c r="H283" s="1" t="s">
@@ -8936,7 +8936,7 @@
       <c r="F284" s="1">
         <v>100</v>
       </c>
-      <c r="G284" s="6">
+      <c r="G284" s="2">
         <v>1</v>
       </c>
       <c r="H284" s="1" t="s">
@@ -8965,7 +8965,7 @@
       <c r="F285" s="1">
         <v>100</v>
       </c>
-      <c r="G285" s="6">
+      <c r="G285" s="2">
         <v>1</v>
       </c>
       <c r="H285" s="1" t="s">
@@ -8994,7 +8994,7 @@
       <c r="F286" s="1">
         <v>100</v>
       </c>
-      <c r="G286" s="6">
+      <c r="G286" s="2">
         <v>1</v>
       </c>
       <c r="H286" s="1" t="s">
@@ -9023,7 +9023,7 @@
       <c r="F287" s="1">
         <v>100</v>
       </c>
-      <c r="G287" s="6">
+      <c r="G287" s="2">
         <v>1</v>
       </c>
       <c r="H287" s="1" t="s">
@@ -9052,7 +9052,7 @@
       <c r="F288" s="1">
         <v>100</v>
       </c>
-      <c r="G288" s="6">
+      <c r="G288" s="2">
         <v>1</v>
       </c>
       <c r="H288" s="1" t="s">
@@ -9081,7 +9081,7 @@
       <c r="F289" s="1">
         <v>100</v>
       </c>
-      <c r="G289" s="6">
+      <c r="G289" s="2">
         <v>1</v>
       </c>
       <c r="H289" s="1" t="s">
@@ -9110,7 +9110,7 @@
       <c r="F290" s="1">
         <v>100</v>
       </c>
-      <c r="G290" s="6">
+      <c r="G290" s="2">
         <v>1</v>
       </c>
       <c r="H290" s="1" t="s">
@@ -9139,7 +9139,7 @@
       <c r="F291" s="1">
         <v>100</v>
       </c>
-      <c r="G291" s="6">
+      <c r="G291" s="2">
         <v>1</v>
       </c>
       <c r="H291" s="1" t="s">
@@ -9168,7 +9168,7 @@
       <c r="F292" s="1">
         <v>95</v>
       </c>
-      <c r="G292" s="6">
+      <c r="G292" s="2">
         <v>0.95</v>
       </c>
       <c r="H292" s="1" t="s">
@@ -9197,13 +9197,593 @@
       <c r="F293" s="1">
         <v>100</v>
       </c>
-      <c r="G293" s="6">
+      <c r="G293" s="2">
         <v>1</v>
       </c>
       <c r="H293" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I293" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A294" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C294" s="5">
+        <v>46251</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F294" s="1">
+        <v>100</v>
+      </c>
+      <c r="G294" s="6">
+        <v>1</v>
+      </c>
+      <c r="H294" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I294" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A295" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C295" s="5">
+        <v>46252</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F295" s="1">
+        <v>95</v>
+      </c>
+      <c r="G295" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H295" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I295" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A296" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C296" s="5">
+        <v>46252</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F296" s="1">
+        <v>0</v>
+      </c>
+      <c r="G296" s="6">
+        <v>0</v>
+      </c>
+      <c r="H296" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I296" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A297" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C297" s="5">
+        <v>46252</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F297" s="1">
+        <v>100</v>
+      </c>
+      <c r="G297" s="6">
+        <v>1</v>
+      </c>
+      <c r="H297" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I297" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A298" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C298" s="5">
+        <v>46251</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F298" s="1">
+        <v>95</v>
+      </c>
+      <c r="G298" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H298" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I298" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A299" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C299" s="5">
+        <v>46251</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F299" s="1">
+        <v>100</v>
+      </c>
+      <c r="G299" s="6">
+        <v>1</v>
+      </c>
+      <c r="H299" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I299" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A300" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C300" s="5">
+        <v>46252</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F300" s="1">
+        <v>90</v>
+      </c>
+      <c r="G300" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H300" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I300" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A301" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C301" s="5">
+        <v>46254</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F301" s="1">
+        <v>95</v>
+      </c>
+      <c r="G301" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H301" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I301" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A302" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C302" s="5">
+        <v>46251</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F302" s="1">
+        <v>100</v>
+      </c>
+      <c r="G302" s="6">
+        <v>1</v>
+      </c>
+      <c r="H302" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I302" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A303" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C303" s="5">
+        <v>46253</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F303" s="1">
+        <v>95</v>
+      </c>
+      <c r="G303" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H303" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I303" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A304" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C304" s="5">
+        <v>46253</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F304" s="1">
+        <v>100</v>
+      </c>
+      <c r="G304" s="6">
+        <v>1</v>
+      </c>
+      <c r="H304" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I304" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A305" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C305" s="5">
+        <v>46252</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E305" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F305" s="1">
+        <v>0</v>
+      </c>
+      <c r="G305" s="6">
+        <v>0</v>
+      </c>
+      <c r="H305" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I305" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A306" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C306" s="5">
+        <v>46251</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E306" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F306" s="1">
+        <v>100</v>
+      </c>
+      <c r="G306" s="6">
+        <v>1</v>
+      </c>
+      <c r="H306" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I306" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A307" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C307" s="5">
+        <v>46251</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F307" s="1">
+        <v>0</v>
+      </c>
+      <c r="G307" s="6">
+        <v>0</v>
+      </c>
+      <c r="H307" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I307" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A308" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C308" s="5">
+        <v>46251</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E308" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F308" s="1">
+        <v>100</v>
+      </c>
+      <c r="G308" s="6">
+        <v>1</v>
+      </c>
+      <c r="H308" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I308" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A309" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C309" s="5">
+        <v>46253</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E309" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F309" s="1">
+        <v>95</v>
+      </c>
+      <c r="G309" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H309" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I309" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A310" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C310" s="5">
+        <v>46251</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E310" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F310" s="1">
+        <v>100</v>
+      </c>
+      <c r="G310" s="6">
+        <v>1</v>
+      </c>
+      <c r="H310" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I310" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A311" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C311" s="5">
+        <v>46252</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E311" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F311" s="1">
+        <v>100</v>
+      </c>
+      <c r="G311" s="6">
+        <v>1</v>
+      </c>
+      <c r="H311" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I311" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A312" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C312" s="5">
+        <v>46254</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E312" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F312" s="1">
+        <v>100</v>
+      </c>
+      <c r="G312" s="6">
+        <v>1</v>
+      </c>
+      <c r="H312" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I312" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A313" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C313" s="5">
+        <v>46255</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E313" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F313" s="1">
+        <v>0</v>
+      </c>
+      <c r="G313" s="6">
+        <v>0</v>
+      </c>
+      <c r="H313" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I313" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -9235,13 +9815,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -9252,13 +9832,13 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -9269,13 +9849,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -9286,13 +9866,13 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -9303,13 +9883,13 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -9320,13 +9900,13 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -9337,13 +9917,13 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -9354,13 +9934,13 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -9371,30 +9951,30 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" t="s">
         <v>49</v>
       </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -9405,13 +9985,13 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -9422,13 +10002,13 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -9439,13 +10019,13 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -9456,13 +10036,13 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -9473,13 +10053,13 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -9490,13 +10070,13 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -9507,30 +10087,30 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -9541,27 +10121,27 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
         <v>62</v>
@@ -9575,10 +10155,10 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
         <v>64</v>
@@ -9869,16 +10449,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0E99A8-9497-4CC9-B8B7-916358FEAD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D96DE6-2394-49A5-8EB6-1A2E0DC753DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-50" yWindow="50" windowWidth="26620" windowHeight="13660" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="948" yWindow="120" windowWidth="19884" windowHeight="16452" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="65">
   <si>
     <t>AssociateName</t>
   </si>
@@ -346,8 +346,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I313" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:I313" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I321" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:I321" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I196">
     <sortCondition ref="C1:C196"/>
   </sortState>
@@ -697,20 +697,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I313"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I321"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7265625" customWidth="1"/>
-    <col min="5" max="6" width="17.453125" customWidth="1"/>
-    <col min="7" max="7" width="18" style="3" customWidth="1"/>
-    <col min="8" max="8" width="20.54296875" customWidth="1"/>
-    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -739,7 +740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -768,7 +769,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -797,7 +798,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -826,7 +827,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -855,7 +856,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -884,7 +885,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -913,7 +914,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -942,7 +943,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -971,7 +972,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -1000,7 +1001,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -1029,7 +1030,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1058,7 +1059,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
@@ -1087,7 +1088,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -1116,7 +1117,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -1145,7 +1146,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -1174,7 +1175,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -1203,7 +1204,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
@@ -1232,7 +1233,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -1261,7 +1262,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -1290,7 +1291,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>9</v>
       </c>
@@ -1319,7 +1320,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1348,7 +1349,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
@@ -1377,7 +1378,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>16</v>
       </c>
@@ -1406,7 +1407,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>15</v>
       </c>
@@ -1435,7 +1436,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
@@ -1464,7 +1465,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -1493,7 +1494,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
@@ -1522,7 +1523,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>14</v>
       </c>
@@ -1551,7 +1552,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,7 +1581,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>24</v>
       </c>
@@ -1609,7 +1610,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>20</v>
       </c>
@@ -1638,7 +1639,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>27</v>
       </c>
@@ -1667,7 +1668,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>26</v>
       </c>
@@ -1696,7 +1697,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>23</v>
       </c>
@@ -1725,7 +1726,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>22</v>
       </c>
@@ -1754,7 +1755,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>18</v>
       </c>
@@ -1783,7 +1784,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>25</v>
       </c>
@@ -1812,7 +1813,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>17</v>
       </c>
@@ -1841,7 +1842,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -1870,7 +1871,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>9</v>
       </c>
@@ -1899,7 +1900,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>27</v>
       </c>
@@ -1928,7 +1929,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,7 +1958,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>25</v>
       </c>
@@ -1986,7 +1987,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>18</v>
       </c>
@@ -2015,7 +2016,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
@@ -2044,7 +2045,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>23</v>
       </c>
@@ -2073,7 +2074,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>13</v>
       </c>
@@ -2102,7 +2103,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>22</v>
       </c>
@@ -2131,7 +2132,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>26</v>
       </c>
@@ -2160,7 +2161,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>13</v>
       </c>
@@ -2189,7 +2190,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>18</v>
       </c>
@@ -2218,7 +2219,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>20</v>
       </c>
@@ -2247,7 +2248,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>18</v>
       </c>
@@ -2276,7 +2277,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>23</v>
       </c>
@@ -2305,7 +2306,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>25</v>
       </c>
@@ -2334,7 +2335,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>27</v>
       </c>
@@ -2363,7 +2364,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>26</v>
       </c>
@@ -2392,7 +2393,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>14</v>
       </c>
@@ -2421,7 +2422,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>24</v>
       </c>
@@ -2450,7 +2451,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>22</v>
       </c>
@@ -2479,7 +2480,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>16</v>
       </c>
@@ -2508,7 +2509,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>17</v>
       </c>
@@ -2537,7 +2538,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>15</v>
       </c>
@@ -2566,7 +2567,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>9</v>
       </c>
@@ -2595,7 +2596,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>13</v>
       </c>
@@ -2624,7 +2625,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>27</v>
       </c>
@@ -2653,7 +2654,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>17</v>
       </c>
@@ -2682,7 +2683,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>26</v>
       </c>
@@ -2711,7 +2712,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>24</v>
       </c>
@@ -2740,7 +2741,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>9</v>
       </c>
@@ -2769,7 +2770,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>22</v>
       </c>
@@ -2798,7 +2799,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>20</v>
       </c>
@@ -2827,7 +2828,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>9</v>
       </c>
@@ -2856,7 +2857,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>16</v>
       </c>
@@ -2885,7 +2886,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>23</v>
       </c>
@@ -2914,7 +2915,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>16</v>
       </c>
@@ -2943,7 +2944,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>14</v>
       </c>
@@ -2972,7 +2973,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>17</v>
       </c>
@@ -3001,7 +3002,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>15</v>
       </c>
@@ -3030,7 +3031,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>15</v>
       </c>
@@ -3059,7 +3060,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>14</v>
       </c>
@@ -3088,7 +3089,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>13</v>
       </c>
@@ -3117,7 +3118,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>20</v>
       </c>
@@ -3146,7 +3147,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>26</v>
       </c>
@@ -3175,7 +3176,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>22</v>
       </c>
@@ -3204,7 +3205,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>9</v>
       </c>
@@ -3233,7 +3234,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>15</v>
       </c>
@@ -3262,7 +3263,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>27</v>
       </c>
@@ -3291,7 +3292,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>16</v>
       </c>
@@ -3320,7 +3321,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>14</v>
       </c>
@@ -3349,7 +3350,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>9</v>
       </c>
@@ -3378,7 +3379,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>24</v>
       </c>
@@ -3407,7 +3408,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>15</v>
       </c>
@@ -3436,7 +3437,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>13</v>
       </c>
@@ -3465,7 +3466,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>13</v>
       </c>
@@ -3494,7 +3495,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>23</v>
       </c>
@@ -3523,7 +3524,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>14</v>
       </c>
@@ -3552,7 +3553,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>17</v>
       </c>
@@ -3581,7 +3582,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>13</v>
       </c>
@@ -3610,7 +3611,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>17</v>
       </c>
@@ -3639,7 +3640,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>16</v>
       </c>
@@ -3668,7 +3669,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>22</v>
       </c>
@@ -3697,7 +3698,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>27</v>
       </c>
@@ -3726,7 +3727,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>26</v>
       </c>
@@ -3755,7 +3756,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>20</v>
       </c>
@@ -3784,7 +3785,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>24</v>
       </c>
@@ -3813,7 +3814,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -3842,7 +3843,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>16</v>
       </c>
@@ -3871,7 +3872,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>15</v>
       </c>
@@ -3900,7 +3901,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>13</v>
       </c>
@@ -3929,7 +3930,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>14</v>
       </c>
@@ -3958,7 +3959,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>17</v>
       </c>
@@ -3987,7 +3988,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>9</v>
       </c>
@@ -4016,7 +4017,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>17</v>
       </c>
@@ -4045,7 +4046,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>16</v>
       </c>
@@ -4074,7 +4075,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>16</v>
       </c>
@@ -4103,7 +4104,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>15</v>
       </c>
@@ -4132,7 +4133,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>13</v>
       </c>
@@ -4161,7 +4162,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>14</v>
       </c>
@@ -4190,7 +4191,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>9</v>
       </c>
@@ -4219,7 +4220,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -4248,7 +4249,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>26</v>
       </c>
@@ -4277,7 +4278,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>22</v>
       </c>
@@ -4306,7 +4307,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>24</v>
       </c>
@@ -4335,7 +4336,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>27</v>
       </c>
@@ -4364,7 +4365,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>20</v>
       </c>
@@ -4393,7 +4394,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>9</v>
       </c>
@@ -4422,7 +4423,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>16</v>
       </c>
@@ -4451,7 +4452,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>22</v>
       </c>
@@ -4480,7 +4481,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>20</v>
       </c>
@@ -4509,7 +4510,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>17</v>
       </c>
@@ -4538,7 +4539,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>15</v>
       </c>
@@ -4567,7 +4568,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>23</v>
       </c>
@@ -4596,7 +4597,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>15</v>
       </c>
@@ -4625,7 +4626,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>24</v>
       </c>
@@ -4654,7 +4655,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>27</v>
       </c>
@@ -4683,7 +4684,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>13</v>
       </c>
@@ -4712,7 +4713,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>23</v>
       </c>
@@ -4741,7 +4742,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>26</v>
       </c>
@@ -4770,7 +4771,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>14</v>
       </c>
@@ -4799,7 +4800,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>13</v>
       </c>
@@ -4828,7 +4829,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>14</v>
       </c>
@@ -4857,7 +4858,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>26</v>
       </c>
@@ -4886,7 +4887,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>22</v>
       </c>
@@ -4915,7 +4916,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>24</v>
       </c>
@@ -4944,7 +4945,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>27</v>
       </c>
@@ -4973,7 +4974,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>20</v>
       </c>
@@ -5002,7 +5003,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>9</v>
       </c>
@@ -5031,7 +5032,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>17</v>
       </c>
@@ -5060,7 +5061,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>24</v>
       </c>
@@ -5089,7 +5090,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>22</v>
       </c>
@@ -5118,7 +5119,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>23</v>
       </c>
@@ -5147,7 +5148,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>20</v>
       </c>
@@ -5176,7 +5177,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>16</v>
       </c>
@@ -5205,7 +5206,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>14</v>
       </c>
@@ -5234,7 +5235,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>17</v>
       </c>
@@ -5263,7 +5264,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>15</v>
       </c>
@@ -5292,7 +5293,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>13</v>
       </c>
@@ -5321,7 +5322,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>24</v>
       </c>
@@ -5350,7 +5351,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>27</v>
       </c>
@@ -5379,7 +5380,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>9</v>
       </c>
@@ -5408,7 +5409,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>26</v>
       </c>
@@ -5437,7 +5438,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>26</v>
       </c>
@@ -5466,7 +5467,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>22</v>
       </c>
@@ -5495,7 +5496,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>27</v>
       </c>
@@ -5524,7 +5525,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>16</v>
       </c>
@@ -5553,7 +5554,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>14</v>
       </c>
@@ -5582,7 +5583,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>17</v>
       </c>
@@ -5611,7 +5612,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>15</v>
       </c>
@@ -5640,7 +5641,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>9</v>
       </c>
@@ -5669,7 +5670,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>13</v>
       </c>
@@ -5698,7 +5699,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>22</v>
       </c>
@@ -5727,7 +5728,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>26</v>
       </c>
@@ -5756,7 +5757,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>24</v>
       </c>
@@ -5785,7 +5786,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>23</v>
       </c>
@@ -5814,7 +5815,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>27</v>
       </c>
@@ -5843,7 +5844,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>20</v>
       </c>
@@ -5872,7 +5873,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>9</v>
       </c>
@@ -5901,7 +5902,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>14</v>
       </c>
@@ -5930,7 +5931,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>17</v>
       </c>
@@ -5959,7 +5960,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>15</v>
       </c>
@@ -5988,7 +5989,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>13</v>
       </c>
@@ -6017,7 +6018,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>16</v>
       </c>
@@ -6046,7 +6047,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>27</v>
       </c>
@@ -6075,7 +6076,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>14</v>
       </c>
@@ -6104,7 +6105,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>26</v>
       </c>
@@ -6133,7 +6134,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>16</v>
       </c>
@@ -6162,7 +6163,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>15</v>
       </c>
@@ -6191,7 +6192,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>17</v>
       </c>
@@ -6220,7 +6221,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>9</v>
       </c>
@@ -6249,7 +6250,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>22</v>
       </c>
@@ -6278,7 +6279,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>24</v>
       </c>
@@ -6307,7 +6308,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>23</v>
       </c>
@@ -6336,7 +6337,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>13</v>
       </c>
@@ -6365,7 +6366,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>20</v>
       </c>
@@ -6394,7 +6395,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>16</v>
       </c>
@@ -6423,7 +6424,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>14</v>
       </c>
@@ -6452,7 +6453,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>17</v>
       </c>
@@ -6481,7 +6482,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>26</v>
       </c>
@@ -6510,7 +6511,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>22</v>
       </c>
@@ -6539,7 +6540,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>23</v>
       </c>
@@ -6568,7 +6569,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>24</v>
       </c>
@@ -6597,7 +6598,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>15</v>
       </c>
@@ -6626,7 +6627,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>27</v>
       </c>
@@ -6655,7 +6656,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>20</v>
       </c>
@@ -6684,7 +6685,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>9</v>
       </c>
@@ -6713,7 +6714,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>13</v>
       </c>
@@ -6742,7 +6743,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>16</v>
       </c>
@@ -6771,7 +6772,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>14</v>
       </c>
@@ -6800,7 +6801,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>17</v>
       </c>
@@ -6829,7 +6830,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>15</v>
       </c>
@@ -6858,7 +6859,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>9</v>
       </c>
@@ -6887,7 +6888,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>13</v>
       </c>
@@ -6916,7 +6917,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>17</v>
       </c>
@@ -6945,7 +6946,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>17</v>
       </c>
@@ -6974,7 +6975,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>26</v>
       </c>
@@ -7003,7 +7004,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>22</v>
       </c>
@@ -7032,7 +7033,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>24</v>
       </c>
@@ -7061,7 +7062,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>23</v>
       </c>
@@ -7090,7 +7091,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>27</v>
       </c>
@@ -7119,7 +7120,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>20</v>
       </c>
@@ -7148,7 +7149,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>14</v>
       </c>
@@ -7177,7 +7178,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>22</v>
       </c>
@@ -7206,7 +7207,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>22</v>
       </c>
@@ -7235,7 +7236,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>22</v>
       </c>
@@ -7264,7 +7265,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>14</v>
       </c>
@@ -7293,7 +7294,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>24</v>
       </c>
@@ -7322,7 +7323,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>24</v>
       </c>
@@ -7351,7 +7352,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>24</v>
       </c>
@@ -7380,7 +7381,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>16</v>
       </c>
@@ -7409,7 +7410,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>16</v>
       </c>
@@ -7438,7 +7439,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>15</v>
       </c>
@@ -7467,7 +7468,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>15</v>
       </c>
@@ -7496,7 +7497,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>27</v>
       </c>
@@ -7525,7 +7526,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>27</v>
       </c>
@@ -7554,7 +7555,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>27</v>
       </c>
@@ -7583,7 +7584,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>9</v>
       </c>
@@ -7612,7 +7613,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>9</v>
       </c>
@@ -7641,7 +7642,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>13</v>
       </c>
@@ -7670,7 +7671,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>13</v>
       </c>
@@ -7699,7 +7700,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>26</v>
       </c>
@@ -7728,7 +7729,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>26</v>
       </c>
@@ -7757,7 +7758,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>26</v>
       </c>
@@ -7786,7 +7787,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>9</v>
       </c>
@@ -7815,7 +7816,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>13</v>
       </c>
@@ -7844,7 +7845,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>15</v>
       </c>
@@ -7873,7 +7874,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>14</v>
       </c>
@@ -7902,7 +7903,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>16</v>
       </c>
@@ -7931,7 +7932,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>17</v>
       </c>
@@ -7960,7 +7961,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>15</v>
       </c>
@@ -7989,7 +7990,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>26</v>
       </c>
@@ -8018,7 +8019,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>22</v>
       </c>
@@ -8047,7 +8048,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>24</v>
       </c>
@@ -8076,7 +8077,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>14</v>
       </c>
@@ -8105,7 +8106,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>23</v>
       </c>
@@ -8134,7 +8135,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>27</v>
       </c>
@@ -8163,7 +8164,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>20</v>
       </c>
@@ -8192,7 +8193,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>13</v>
       </c>
@@ -8221,7 +8222,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>17</v>
       </c>
@@ -8250,7 +8251,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>9</v>
       </c>
@@ -8279,7 +8280,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>15</v>
       </c>
@@ -8308,7 +8309,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>16</v>
       </c>
@@ -8337,7 +8338,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>23</v>
       </c>
@@ -8366,7 +8367,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>23</v>
       </c>
@@ -8395,7 +8396,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>23</v>
       </c>
@@ -8424,7 +8425,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>20</v>
       </c>
@@ -8453,7 +8454,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>20</v>
       </c>
@@ -8482,7 +8483,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>20</v>
       </c>
@@ -8511,7 +8512,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>22</v>
       </c>
@@ -8540,7 +8541,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>22</v>
       </c>
@@ -8569,7 +8570,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>24</v>
       </c>
@@ -8598,7 +8599,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>24</v>
       </c>
@@ -8627,7 +8628,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>27</v>
       </c>
@@ -8656,7 +8657,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>27</v>
       </c>
@@ -8685,7 +8686,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>26</v>
       </c>
@@ -8714,7 +8715,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>26</v>
       </c>
@@ -8743,7 +8744,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>23</v>
       </c>
@@ -8772,7 +8773,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>23</v>
       </c>
@@ -8801,7 +8802,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>20</v>
       </c>
@@ -8830,7 +8831,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>20</v>
       </c>
@@ -8859,7 +8860,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>15</v>
       </c>
@@ -8888,7 +8889,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>15</v>
       </c>
@@ -8917,7 +8918,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>13</v>
       </c>
@@ -8946,7 +8947,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>13</v>
       </c>
@@ -8975,7 +8976,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>14</v>
       </c>
@@ -9004,7 +9005,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>14</v>
       </c>
@@ -9033,7 +9034,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>9</v>
       </c>
@@ -9062,7 +9063,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>9</v>
       </c>
@@ -9091,7 +9092,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>17</v>
       </c>
@@ -9120,7 +9121,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>17</v>
       </c>
@@ -9149,7 +9150,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>16</v>
       </c>
@@ -9178,7 +9179,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>16</v>
       </c>
@@ -9207,7 +9208,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>16</v>
       </c>
@@ -9226,7 +9227,7 @@
       <c r="F294" s="1">
         <v>100</v>
       </c>
-      <c r="G294" s="6">
+      <c r="G294" s="2">
         <v>1</v>
       </c>
       <c r="H294" s="1" t="s">
@@ -9236,7 +9237,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>14</v>
       </c>
@@ -9255,7 +9256,7 @@
       <c r="F295" s="1">
         <v>95</v>
       </c>
-      <c r="G295" s="6">
+      <c r="G295" s="2">
         <v>0.95</v>
       </c>
       <c r="H295" s="1" t="s">
@@ -9265,7 +9266,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>17</v>
       </c>
@@ -9284,7 +9285,7 @@
       <c r="F296" s="1">
         <v>0</v>
       </c>
-      <c r="G296" s="6">
+      <c r="G296" s="2">
         <v>0</v>
       </c>
       <c r="H296" s="1" t="s">
@@ -9294,7 +9295,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>15</v>
       </c>
@@ -9313,7 +9314,7 @@
       <c r="F297" s="1">
         <v>100</v>
       </c>
-      <c r="G297" s="6">
+      <c r="G297" s="2">
         <v>1</v>
       </c>
       <c r="H297" s="1" t="s">
@@ -9323,7 +9324,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>26</v>
       </c>
@@ -9342,7 +9343,7 @@
       <c r="F298" s="1">
         <v>95</v>
       </c>
-      <c r="G298" s="6">
+      <c r="G298" s="2">
         <v>0.95</v>
       </c>
       <c r="H298" s="1" t="s">
@@ -9352,7 +9353,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>26</v>
       </c>
@@ -9371,7 +9372,7 @@
       <c r="F299" s="1">
         <v>100</v>
       </c>
-      <c r="G299" s="6">
+      <c r="G299" s="2">
         <v>1</v>
       </c>
       <c r="H299" s="1" t="s">
@@ -9381,7 +9382,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>22</v>
       </c>
@@ -9400,7 +9401,7 @@
       <c r="F300" s="1">
         <v>90</v>
       </c>
-      <c r="G300" s="6">
+      <c r="G300" s="2">
         <v>0.9</v>
       </c>
       <c r="H300" s="1" t="s">
@@ -9410,7 +9411,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>22</v>
       </c>
@@ -9429,7 +9430,7 @@
       <c r="F301" s="1">
         <v>95</v>
       </c>
-      <c r="G301" s="6">
+      <c r="G301" s="2">
         <v>0.95</v>
       </c>
       <c r="H301" s="1" t="s">
@@ -9439,7 +9440,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>24</v>
       </c>
@@ -9458,7 +9459,7 @@
       <c r="F302" s="1">
         <v>100</v>
       </c>
-      <c r="G302" s="6">
+      <c r="G302" s="2">
         <v>1</v>
       </c>
       <c r="H302" s="1" t="s">
@@ -9468,7 +9469,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>24</v>
       </c>
@@ -9487,7 +9488,7 @@
       <c r="F303" s="1">
         <v>95</v>
       </c>
-      <c r="G303" s="6">
+      <c r="G303" s="2">
         <v>0.95</v>
       </c>
       <c r="H303" s="1" t="s">
@@ -9497,7 +9498,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>23</v>
       </c>
@@ -9516,7 +9517,7 @@
       <c r="F304" s="1">
         <v>100</v>
       </c>
-      <c r="G304" s="6">
+      <c r="G304" s="2">
         <v>1</v>
       </c>
       <c r="H304" s="1" t="s">
@@ -9526,7 +9527,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>9</v>
       </c>
@@ -9545,7 +9546,7 @@
       <c r="F305" s="1">
         <v>0</v>
       </c>
-      <c r="G305" s="6">
+      <c r="G305" s="2">
         <v>0</v>
       </c>
       <c r="H305" s="1" t="s">
@@ -9555,7 +9556,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>23</v>
       </c>
@@ -9574,7 +9575,7 @@
       <c r="F306" s="1">
         <v>100</v>
       </c>
-      <c r="G306" s="6">
+      <c r="G306" s="2">
         <v>1</v>
       </c>
       <c r="H306" s="1" t="s">
@@ -9584,7 +9585,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>27</v>
       </c>
@@ -9603,7 +9604,7 @@
       <c r="F307" s="1">
         <v>0</v>
       </c>
-      <c r="G307" s="6">
+      <c r="G307" s="2">
         <v>0</v>
       </c>
       <c r="H307" s="1" t="s">
@@ -9613,7 +9614,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>13</v>
       </c>
@@ -9632,7 +9633,7 @@
       <c r="F308" s="1">
         <v>100</v>
       </c>
-      <c r="G308" s="6">
+      <c r="G308" s="2">
         <v>1</v>
       </c>
       <c r="H308" s="1" t="s">
@@ -9642,7 +9643,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>27</v>
       </c>
@@ -9661,7 +9662,7 @@
       <c r="F309" s="1">
         <v>95</v>
       </c>
-      <c r="G309" s="6">
+      <c r="G309" s="2">
         <v>0.95</v>
       </c>
       <c r="H309" s="1" t="s">
@@ -9671,7 +9672,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>20</v>
       </c>
@@ -9690,7 +9691,7 @@
       <c r="F310" s="1">
         <v>100</v>
       </c>
-      <c r="G310" s="6">
+      <c r="G310" s="2">
         <v>1</v>
       </c>
       <c r="H310" s="1" t="s">
@@ -9700,7 +9701,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>20</v>
       </c>
@@ -9719,7 +9720,7 @@
       <c r="F311" s="1">
         <v>100</v>
       </c>
-      <c r="G311" s="6">
+      <c r="G311" s="2">
         <v>1</v>
       </c>
       <c r="H311" s="1" t="s">
@@ -9729,7 +9730,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>16</v>
       </c>
@@ -9748,7 +9749,7 @@
       <c r="F312" s="1">
         <v>100</v>
       </c>
-      <c r="G312" s="6">
+      <c r="G312" s="2">
         <v>1</v>
       </c>
       <c r="H312" s="1" t="s">
@@ -9758,7 +9759,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>14</v>
       </c>
@@ -9777,13 +9778,245 @@
       <c r="F313" s="1">
         <v>0</v>
       </c>
-      <c r="G313" s="6">
+      <c r="G313" s="2">
         <v>0</v>
       </c>
       <c r="H313" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I313" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A314" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C314" s="5">
+        <v>46255</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E314" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F314" s="1">
+        <v>100</v>
+      </c>
+      <c r="G314" s="6">
+        <v>1</v>
+      </c>
+      <c r="H314" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I314" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A315" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C315" s="5">
+        <v>46255</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E315" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F315" s="1">
+        <v>0</v>
+      </c>
+      <c r="G315" s="6">
+        <v>0</v>
+      </c>
+      <c r="H315" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I315" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A316" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C316" s="5">
+        <v>46255</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E316" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F316" s="1">
+        <v>100</v>
+      </c>
+      <c r="G316" s="6">
+        <v>1</v>
+      </c>
+      <c r="H316" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I316" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A317" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C317" s="5">
+        <v>46258</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E317" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F317" s="1">
+        <v>100</v>
+      </c>
+      <c r="G317" s="6">
+        <v>1</v>
+      </c>
+      <c r="H317" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I317" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A318" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C318" s="5">
+        <v>46258</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E318" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F318" s="1">
+        <v>100</v>
+      </c>
+      <c r="G318" s="6">
+        <v>1</v>
+      </c>
+      <c r="H318" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I318" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A319" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C319" s="5">
+        <v>46261</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E319" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F319" s="1">
+        <v>100</v>
+      </c>
+      <c r="G319" s="6">
+        <v>1</v>
+      </c>
+      <c r="H319" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I319" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A320" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C320" s="5">
+        <v>46258</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E320" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F320" s="1">
+        <v>95</v>
+      </c>
+      <c r="G320" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H320" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I320" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A321" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C321" s="5">
+        <v>46260</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E321" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F321" s="1">
+        <v>100</v>
+      </c>
+      <c r="G321" s="6">
+        <v>1</v>
+      </c>
+      <c r="H321" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I321" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -9799,15 +10032,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324C68B5-B5AE-49F4-BF99-B0AAB6EC270F}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="32.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="32.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -9824,7 +10057,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -9841,7 +10074,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -9858,7 +10091,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -9875,7 +10108,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -9892,7 +10125,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -9909,7 +10142,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -9926,7 +10159,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -9943,7 +10176,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -9960,7 +10193,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -9977,7 +10210,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -9994,7 +10227,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -10011,7 +10244,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -10028,7 +10261,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -10045,7 +10278,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -10062,7 +10295,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -10079,7 +10312,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -10096,7 +10329,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -10113,7 +10346,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -10130,7 +10363,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -10147,7 +10380,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -10174,28 +10407,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -10446,32 +10657,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10490,6 +10698,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{4360c1e8-deec-49bb-904e-9331088b2a03}" enabled="0" method="" siteId="{4360c1e8-deec-49bb-904e-9331088b2a03}" removed="1"/>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D96DE6-2394-49A5-8EB6-1A2E0DC753DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45088FF4-E0E5-4D94-9D28-A8D4627474EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="948" yWindow="120" windowWidth="19884" windowHeight="16452" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="3570" yWindow="450" windowWidth="26280" windowHeight="19800" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="66">
   <si>
     <t>AssociateName</t>
   </si>
@@ -233,6 +233,9 @@
   <si>
     <t>Connor.Floriani@lplfinancial.com</t>
   </si>
+  <si>
+    <t>September</t>
+  </si>
 </sst>
 </file>
 
@@ -308,6 +311,9 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
@@ -329,9 +335,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -346,8 +349,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I321" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="A1:I321" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I333" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I333" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I196">
     <sortCondition ref="C1:C196"/>
   </sortState>
@@ -358,7 +361,7 @@
     <tableColumn id="15" xr3:uid="{156F7529-7782-4A87-B4E7-76854F1D035A}" name="IssueResolvedFirstContact"/>
     <tableColumn id="10" xr3:uid="{FA20FC87-A813-482F-AA10-876B721360F4}" name="CallFailed"/>
     <tableColumn id="11" xr3:uid="{DF145C57-18CF-4D90-A45D-FAACD0306130}" name="TotalScore"/>
-    <tableColumn id="12" xr3:uid="{0876AC93-D420-4B04-9EE3-448E495D6B83}" name="Percentage" dataDxfId="0" dataCellStyle="Percent"/>
+    <tableColumn id="12" xr3:uid="{0876AC93-D420-4B04-9EE3-448E495D6B83}" name="Percentage" dataDxfId="1" dataCellStyle="Percent"/>
     <tableColumn id="13" xr3:uid="{88DA4CA6-A215-4FB1-8A6D-379852A7EEFA}" name="ReviewMonth"/>
     <tableColumn id="14" xr3:uid="{35631D79-8CE9-47C8-A757-76CCFBACC54F}" name="ReviewYear"/>
   </tableColumns>
@@ -367,7 +370,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}" name="tblAssociateReference" displayName="tblAssociateReference" ref="A1:E21" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}" name="tblAssociateReference" displayName="tblAssociateReference" ref="A1:E21" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:E21" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8E0548F5-70FF-454C-A4FF-1E3FA7D9C27E}" name="AssociateName"/>
@@ -697,21 +700,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I321"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I333"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -740,7 +743,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -769,7 +772,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -798,7 +801,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -827,7 +830,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -856,7 +859,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -885,7 +888,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -914,7 +917,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -943,7 +946,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -972,7 +975,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -1001,7 +1004,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -1030,7 +1033,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1059,7 +1062,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
@@ -1088,7 +1091,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -1117,7 +1120,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -1146,7 +1149,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -1175,7 +1178,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -1204,7 +1207,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
@@ -1233,7 +1236,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -1262,7 +1265,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -1291,7 +1294,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>9</v>
       </c>
@@ -1320,7 +1323,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1349,7 +1352,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
@@ -1378,7 +1381,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>16</v>
       </c>
@@ -1407,7 +1410,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>15</v>
       </c>
@@ -1436,7 +1439,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
@@ -1465,7 +1468,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -1494,7 +1497,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
@@ -1523,7 +1526,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>14</v>
       </c>
@@ -1552,7 +1555,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>14</v>
       </c>
@@ -1581,7 +1584,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>24</v>
       </c>
@@ -1610,7 +1613,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>20</v>
       </c>
@@ -1639,7 +1642,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>27</v>
       </c>
@@ -1668,7 +1671,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>26</v>
       </c>
@@ -1697,7 +1700,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>23</v>
       </c>
@@ -1726,7 +1729,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>22</v>
       </c>
@@ -1755,7 +1758,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>18</v>
       </c>
@@ -1784,7 +1787,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>25</v>
       </c>
@@ -1813,7 +1816,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>17</v>
       </c>
@@ -1842,7 +1845,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -1871,7 +1874,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>9</v>
       </c>
@@ -1900,7 +1903,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>27</v>
       </c>
@@ -1929,7 +1932,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>20</v>
       </c>
@@ -1958,7 +1961,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>25</v>
       </c>
@@ -1987,7 +1990,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>18</v>
       </c>
@@ -2016,7 +2019,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
@@ -2045,7 +2048,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>23</v>
       </c>
@@ -2074,7 +2077,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>13</v>
       </c>
@@ -2103,7 +2106,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>22</v>
       </c>
@@ -2132,7 +2135,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>26</v>
       </c>
@@ -2161,7 +2164,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>13</v>
       </c>
@@ -2190,7 +2193,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>18</v>
       </c>
@@ -2219,7 +2222,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>20</v>
       </c>
@@ -2248,7 +2251,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>18</v>
       </c>
@@ -2277,7 +2280,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>23</v>
       </c>
@@ -2306,7 +2309,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>25</v>
       </c>
@@ -2335,7 +2338,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>27</v>
       </c>
@@ -2364,7 +2367,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>26</v>
       </c>
@@ -2393,7 +2396,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>14</v>
       </c>
@@ -2422,7 +2425,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>24</v>
       </c>
@@ -2451,7 +2454,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>22</v>
       </c>
@@ -2480,7 +2483,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>16</v>
       </c>
@@ -2509,7 +2512,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>17</v>
       </c>
@@ -2538,7 +2541,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>15</v>
       </c>
@@ -2567,7 +2570,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>9</v>
       </c>
@@ -2596,7 +2599,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>13</v>
       </c>
@@ -2625,7 +2628,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>27</v>
       </c>
@@ -2654,7 +2657,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>17</v>
       </c>
@@ -2683,7 +2686,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>26</v>
       </c>
@@ -2712,7 +2715,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>24</v>
       </c>
@@ -2741,7 +2744,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>9</v>
       </c>
@@ -2770,7 +2773,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>22</v>
       </c>
@@ -2799,7 +2802,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>20</v>
       </c>
@@ -2828,7 +2831,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>9</v>
       </c>
@@ -2857,7 +2860,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>16</v>
       </c>
@@ -2886,7 +2889,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>23</v>
       </c>
@@ -2915,7 +2918,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>16</v>
       </c>
@@ -2944,7 +2947,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>14</v>
       </c>
@@ -2973,7 +2976,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>17</v>
       </c>
@@ -3002,7 +3005,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>15</v>
       </c>
@@ -3031,7 +3034,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>15</v>
       </c>
@@ -3060,7 +3063,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>14</v>
       </c>
@@ -3089,7 +3092,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>13</v>
       </c>
@@ -3118,7 +3121,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>20</v>
       </c>
@@ -3147,7 +3150,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>26</v>
       </c>
@@ -3176,7 +3179,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>22</v>
       </c>
@@ -3205,7 +3208,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>9</v>
       </c>
@@ -3234,7 +3237,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>15</v>
       </c>
@@ -3263,7 +3266,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>27</v>
       </c>
@@ -3292,7 +3295,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>16</v>
       </c>
@@ -3321,7 +3324,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>14</v>
       </c>
@@ -3350,7 +3353,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>9</v>
       </c>
@@ -3379,7 +3382,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>24</v>
       </c>
@@ -3408,7 +3411,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>15</v>
       </c>
@@ -3437,7 +3440,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>13</v>
       </c>
@@ -3466,7 +3469,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>13</v>
       </c>
@@ -3495,7 +3498,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>23</v>
       </c>
@@ -3524,7 +3527,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>14</v>
       </c>
@@ -3553,7 +3556,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>17</v>
       </c>
@@ -3582,7 +3585,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>13</v>
       </c>
@@ -3611,7 +3614,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>17</v>
       </c>
@@ -3640,7 +3643,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>16</v>
       </c>
@@ -3669,7 +3672,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>22</v>
       </c>
@@ -3698,7 +3701,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>27</v>
       </c>
@@ -3727,7 +3730,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>26</v>
       </c>
@@ -3756,7 +3759,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>20</v>
       </c>
@@ -3785,7 +3788,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>24</v>
       </c>
@@ -3814,7 +3817,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -3843,7 +3846,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>16</v>
       </c>
@@ -3872,7 +3875,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>15</v>
       </c>
@@ -3901,7 +3904,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>13</v>
       </c>
@@ -3930,7 +3933,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>14</v>
       </c>
@@ -3959,7 +3962,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>17</v>
       </c>
@@ -3988,7 +3991,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>9</v>
       </c>
@@ -4017,7 +4020,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>17</v>
       </c>
@@ -4046,7 +4049,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>16</v>
       </c>
@@ -4075,7 +4078,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>16</v>
       </c>
@@ -4104,7 +4107,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>15</v>
       </c>
@@ -4133,7 +4136,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>13</v>
       </c>
@@ -4162,7 +4165,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>14</v>
       </c>
@@ -4191,7 +4194,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>9</v>
       </c>
@@ -4220,7 +4223,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -4249,7 +4252,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>26</v>
       </c>
@@ -4278,7 +4281,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>22</v>
       </c>
@@ -4307,7 +4310,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>24</v>
       </c>
@@ -4336,7 +4339,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>27</v>
       </c>
@@ -4365,7 +4368,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>20</v>
       </c>
@@ -4394,7 +4397,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>9</v>
       </c>
@@ -4423,7 +4426,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>16</v>
       </c>
@@ -4452,7 +4455,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>22</v>
       </c>
@@ -4481,7 +4484,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>20</v>
       </c>
@@ -4510,7 +4513,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>17</v>
       </c>
@@ -4539,7 +4542,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>15</v>
       </c>
@@ -4568,7 +4571,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>23</v>
       </c>
@@ -4597,7 +4600,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>15</v>
       </c>
@@ -4626,7 +4629,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>24</v>
       </c>
@@ -4655,7 +4658,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>27</v>
       </c>
@@ -4684,7 +4687,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>13</v>
       </c>
@@ -4713,7 +4716,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>23</v>
       </c>
@@ -4742,7 +4745,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>26</v>
       </c>
@@ -4771,7 +4774,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>14</v>
       </c>
@@ -4800,7 +4803,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>13</v>
       </c>
@@ -4829,7 +4832,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>14</v>
       </c>
@@ -4858,7 +4861,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>26</v>
       </c>
@@ -4887,7 +4890,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>22</v>
       </c>
@@ -4916,7 +4919,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>24</v>
       </c>
@@ -4945,7 +4948,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>27</v>
       </c>
@@ -4974,7 +4977,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>20</v>
       </c>
@@ -5003,7 +5006,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>9</v>
       </c>
@@ -5032,7 +5035,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>17</v>
       </c>
@@ -5061,7 +5064,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>24</v>
       </c>
@@ -5090,7 +5093,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>22</v>
       </c>
@@ -5119,7 +5122,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>23</v>
       </c>
@@ -5148,7 +5151,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>20</v>
       </c>
@@ -5177,7 +5180,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>16</v>
       </c>
@@ -5206,7 +5209,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>14</v>
       </c>
@@ -5235,7 +5238,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>17</v>
       </c>
@@ -5264,7 +5267,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>15</v>
       </c>
@@ -5293,7 +5296,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>13</v>
       </c>
@@ -5322,7 +5325,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>24</v>
       </c>
@@ -5351,7 +5354,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>27</v>
       </c>
@@ -5380,7 +5383,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>9</v>
       </c>
@@ -5409,7 +5412,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>26</v>
       </c>
@@ -5438,7 +5441,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>26</v>
       </c>
@@ -5467,7 +5470,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>22</v>
       </c>
@@ -5496,7 +5499,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>27</v>
       </c>
@@ -5525,7 +5528,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>16</v>
       </c>
@@ -5554,7 +5557,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>14</v>
       </c>
@@ -5583,7 +5586,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>17</v>
       </c>
@@ -5612,7 +5615,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>15</v>
       </c>
@@ -5641,7 +5644,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>9</v>
       </c>
@@ -5670,7 +5673,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>13</v>
       </c>
@@ -5699,7 +5702,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>22</v>
       </c>
@@ -5728,7 +5731,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>26</v>
       </c>
@@ -5757,7 +5760,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>24</v>
       </c>
@@ -5786,7 +5789,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>23</v>
       </c>
@@ -5815,7 +5818,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>27</v>
       </c>
@@ -5844,7 +5847,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>20</v>
       </c>
@@ -5873,7 +5876,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>9</v>
       </c>
@@ -5902,7 +5905,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>14</v>
       </c>
@@ -5931,7 +5934,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>17</v>
       </c>
@@ -5960,7 +5963,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>15</v>
       </c>
@@ -5989,7 +5992,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>13</v>
       </c>
@@ -6018,7 +6021,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>16</v>
       </c>
@@ -6047,7 +6050,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>27</v>
       </c>
@@ -6076,7 +6079,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>14</v>
       </c>
@@ -6105,7 +6108,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>26</v>
       </c>
@@ -6134,7 +6137,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>16</v>
       </c>
@@ -6163,7 +6166,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>15</v>
       </c>
@@ -6192,7 +6195,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>17</v>
       </c>
@@ -6221,7 +6224,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>9</v>
       </c>
@@ -6250,7 +6253,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>22</v>
       </c>
@@ -6279,7 +6282,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>24</v>
       </c>
@@ -6308,7 +6311,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>23</v>
       </c>
@@ -6337,7 +6340,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>13</v>
       </c>
@@ -6366,7 +6369,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>20</v>
       </c>
@@ -6395,7 +6398,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>16</v>
       </c>
@@ -6424,7 +6427,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>14</v>
       </c>
@@ -6453,7 +6456,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>17</v>
       </c>
@@ -6482,7 +6485,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>26</v>
       </c>
@@ -6511,7 +6514,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>22</v>
       </c>
@@ -6540,7 +6543,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>23</v>
       </c>
@@ -6569,7 +6572,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>24</v>
       </c>
@@ -6598,7 +6601,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>15</v>
       </c>
@@ -6627,7 +6630,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>27</v>
       </c>
@@ -6656,7 +6659,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>20</v>
       </c>
@@ -6685,7 +6688,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>9</v>
       </c>
@@ -6714,7 +6717,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>13</v>
       </c>
@@ -6743,7 +6746,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>16</v>
       </c>
@@ -6772,7 +6775,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>14</v>
       </c>
@@ -6801,7 +6804,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>17</v>
       </c>
@@ -6830,7 +6833,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>15</v>
       </c>
@@ -6859,7 +6862,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>9</v>
       </c>
@@ -6888,7 +6891,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>13</v>
       </c>
@@ -6917,7 +6920,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>17</v>
       </c>
@@ -6946,7 +6949,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>17</v>
       </c>
@@ -6975,7 +6978,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>26</v>
       </c>
@@ -7004,7 +7007,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>22</v>
       </c>
@@ -7033,7 +7036,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>24</v>
       </c>
@@ -7062,7 +7065,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>23</v>
       </c>
@@ -7091,7 +7094,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>27</v>
       </c>
@@ -7120,7 +7123,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>20</v>
       </c>
@@ -7149,7 +7152,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>14</v>
       </c>
@@ -7178,7 +7181,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>22</v>
       </c>
@@ -7207,7 +7210,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>22</v>
       </c>
@@ -7236,7 +7239,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>22</v>
       </c>
@@ -7265,7 +7268,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>14</v>
       </c>
@@ -7294,7 +7297,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>24</v>
       </c>
@@ -7323,7 +7326,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>24</v>
       </c>
@@ -7352,7 +7355,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>24</v>
       </c>
@@ -7381,7 +7384,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>16</v>
       </c>
@@ -7410,7 +7413,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>16</v>
       </c>
@@ -7439,7 +7442,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>15</v>
       </c>
@@ -7468,7 +7471,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>15</v>
       </c>
@@ -7497,7 +7500,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>27</v>
       </c>
@@ -7526,7 +7529,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>27</v>
       </c>
@@ -7555,7 +7558,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>27</v>
       </c>
@@ -7584,7 +7587,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>9</v>
       </c>
@@ -7613,7 +7616,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>9</v>
       </c>
@@ -7642,7 +7645,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>13</v>
       </c>
@@ -7671,7 +7674,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>13</v>
       </c>
@@ -7700,7 +7703,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>26</v>
       </c>
@@ -7729,7 +7732,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>26</v>
       </c>
@@ -7758,7 +7761,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>26</v>
       </c>
@@ -7787,7 +7790,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>9</v>
       </c>
@@ -7816,7 +7819,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>13</v>
       </c>
@@ -7845,7 +7848,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>15</v>
       </c>
@@ -7874,7 +7877,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>14</v>
       </c>
@@ -7903,7 +7906,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>16</v>
       </c>
@@ -7932,7 +7935,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>17</v>
       </c>
@@ -7961,7 +7964,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>15</v>
       </c>
@@ -7990,7 +7993,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>26</v>
       </c>
@@ -8019,7 +8022,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>22</v>
       </c>
@@ -8048,7 +8051,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>24</v>
       </c>
@@ -8077,7 +8080,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>14</v>
       </c>
@@ -8106,7 +8109,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>23</v>
       </c>
@@ -8135,7 +8138,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>27</v>
       </c>
@@ -8164,7 +8167,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>20</v>
       </c>
@@ -8193,7 +8196,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>13</v>
       </c>
@@ -8222,7 +8225,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>17</v>
       </c>
@@ -8251,7 +8254,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>9</v>
       </c>
@@ -8280,7 +8283,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>15</v>
       </c>
@@ -8309,7 +8312,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>16</v>
       </c>
@@ -8338,7 +8341,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>23</v>
       </c>
@@ -8367,7 +8370,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>23</v>
       </c>
@@ -8396,7 +8399,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>23</v>
       </c>
@@ -8425,7 +8428,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>20</v>
       </c>
@@ -8454,7 +8457,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>20</v>
       </c>
@@ -8483,7 +8486,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>20</v>
       </c>
@@ -8512,7 +8515,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>22</v>
       </c>
@@ -8541,7 +8544,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>22</v>
       </c>
@@ -8570,7 +8573,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>24</v>
       </c>
@@ -8599,7 +8602,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>24</v>
       </c>
@@ -8628,7 +8631,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>27</v>
       </c>
@@ -8657,7 +8660,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>27</v>
       </c>
@@ -8686,7 +8689,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>26</v>
       </c>
@@ -8715,7 +8718,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>26</v>
       </c>
@@ -8744,7 +8747,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>23</v>
       </c>
@@ -8773,7 +8776,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>23</v>
       </c>
@@ -8802,7 +8805,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>20</v>
       </c>
@@ -8831,7 +8834,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>20</v>
       </c>
@@ -8860,7 +8863,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>15</v>
       </c>
@@ -8889,7 +8892,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>15</v>
       </c>
@@ -8918,7 +8921,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>13</v>
       </c>
@@ -8947,7 +8950,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>13</v>
       </c>
@@ -8976,7 +8979,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>14</v>
       </c>
@@ -9005,7 +9008,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>14</v>
       </c>
@@ -9034,7 +9037,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>9</v>
       </c>
@@ -9063,7 +9066,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>9</v>
       </c>
@@ -9092,7 +9095,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>17</v>
       </c>
@@ -9121,7 +9124,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>17</v>
       </c>
@@ -9150,7 +9153,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>16</v>
       </c>
@@ -9179,7 +9182,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>16</v>
       </c>
@@ -9208,7 +9211,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>16</v>
       </c>
@@ -9237,7 +9240,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>14</v>
       </c>
@@ -9266,7 +9269,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>17</v>
       </c>
@@ -9295,7 +9298,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>15</v>
       </c>
@@ -9324,7 +9327,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>26</v>
       </c>
@@ -9353,7 +9356,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>26</v>
       </c>
@@ -9382,7 +9385,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>22</v>
       </c>
@@ -9411,7 +9414,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>22</v>
       </c>
@@ -9440,7 +9443,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>24</v>
       </c>
@@ -9469,7 +9472,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>24</v>
       </c>
@@ -9498,7 +9501,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>23</v>
       </c>
@@ -9527,7 +9530,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>9</v>
       </c>
@@ -9556,7 +9559,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>23</v>
       </c>
@@ -9585,7 +9588,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>27</v>
       </c>
@@ -9614,7 +9617,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>13</v>
       </c>
@@ -9643,7 +9646,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>27</v>
       </c>
@@ -9672,7 +9675,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>20</v>
       </c>
@@ -9701,7 +9704,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>20</v>
       </c>
@@ -9730,7 +9733,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>16</v>
       </c>
@@ -9759,7 +9762,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>14</v>
       </c>
@@ -9788,7 +9791,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>15</v>
       </c>
@@ -9807,7 +9810,7 @@
       <c r="F314" s="1">
         <v>100</v>
       </c>
-      <c r="G314" s="6">
+      <c r="G314" s="2">
         <v>1</v>
       </c>
       <c r="H314" s="1" t="s">
@@ -9817,7 +9820,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>9</v>
       </c>
@@ -9836,7 +9839,7 @@
       <c r="F315" s="1">
         <v>0</v>
       </c>
-      <c r="G315" s="6">
+      <c r="G315" s="2">
         <v>0</v>
       </c>
       <c r="H315" s="1" t="s">
@@ -9846,7 +9849,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>13</v>
       </c>
@@ -9865,7 +9868,7 @@
       <c r="F316" s="1">
         <v>100</v>
       </c>
-      <c r="G316" s="6">
+      <c r="G316" s="2">
         <v>1</v>
       </c>
       <c r="H316" s="1" t="s">
@@ -9875,7 +9878,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>26</v>
       </c>
@@ -9894,7 +9897,7 @@
       <c r="F317" s="1">
         <v>100</v>
       </c>
-      <c r="G317" s="6">
+      <c r="G317" s="2">
         <v>1</v>
       </c>
       <c r="H317" s="1" t="s">
@@ -9904,7 +9907,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>22</v>
       </c>
@@ -9923,7 +9926,7 @@
       <c r="F318" s="1">
         <v>100</v>
       </c>
-      <c r="G318" s="6">
+      <c r="G318" s="2">
         <v>1</v>
       </c>
       <c r="H318" s="1" t="s">
@@ -9933,7 +9936,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>24</v>
       </c>
@@ -9952,7 +9955,7 @@
       <c r="F319" s="1">
         <v>100</v>
       </c>
-      <c r="G319" s="6">
+      <c r="G319" s="2">
         <v>1</v>
       </c>
       <c r="H319" s="1" t="s">
@@ -9962,7 +9965,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>23</v>
       </c>
@@ -9981,7 +9984,7 @@
       <c r="F320" s="1">
         <v>95</v>
       </c>
-      <c r="G320" s="6">
+      <c r="G320" s="2">
         <v>0.95</v>
       </c>
       <c r="H320" s="1" t="s">
@@ -9991,7 +9994,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>20</v>
       </c>
@@ -10010,13 +10013,361 @@
       <c r="F321" s="1">
         <v>100</v>
       </c>
-      <c r="G321" s="6">
+      <c r="G321" s="2">
         <v>1</v>
       </c>
       <c r="H321" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I321" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C322" s="5">
+        <v>46262</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E322" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F322" s="1">
+        <v>100</v>
+      </c>
+      <c r="G322" s="6">
+        <v>1</v>
+      </c>
+      <c r="H322" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I322" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C323" s="5">
+        <v>46262</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E323" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F323" s="1">
+        <v>85</v>
+      </c>
+      <c r="G323" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="H323" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I323" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C324" s="5">
+        <v>46262</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E324" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F324" s="1">
+        <v>0</v>
+      </c>
+      <c r="G324" s="6">
+        <v>0</v>
+      </c>
+      <c r="H324" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I324" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C325" s="5">
+        <v>46262</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E325" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F325" s="1">
+        <v>100</v>
+      </c>
+      <c r="G325" s="6">
+        <v>1</v>
+      </c>
+      <c r="H325" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I325" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C326" s="5">
+        <v>46261</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E326" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F326" s="1">
+        <v>100</v>
+      </c>
+      <c r="G326" s="6">
+        <v>1</v>
+      </c>
+      <c r="H326" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I326" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C327" s="5">
+        <v>46262</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E327" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F327" s="1">
+        <v>95</v>
+      </c>
+      <c r="G327" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H327" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I327" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C328" s="5">
+        <v>46262</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E328" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F328" s="1">
+        <v>0</v>
+      </c>
+      <c r="G328" s="6">
+        <v>0</v>
+      </c>
+      <c r="H328" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I328" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C329" s="5">
+        <v>46268</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E329" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F329" s="1">
+        <v>100</v>
+      </c>
+      <c r="G329" s="6">
+        <v>1</v>
+      </c>
+      <c r="H329" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I329" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C330" s="5">
+        <v>46268</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E330" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F330" s="1">
+        <v>100</v>
+      </c>
+      <c r="G330" s="6">
+        <v>1</v>
+      </c>
+      <c r="H330" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I330" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C331" s="5">
+        <v>46267</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E331" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F331" s="1">
+        <v>95</v>
+      </c>
+      <c r="G331" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H331" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I331" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C332" s="5">
+        <v>46267</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E332" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F332" s="1">
+        <v>100</v>
+      </c>
+      <c r="G332" s="6">
+        <v>1</v>
+      </c>
+      <c r="H332" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I332" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C333" s="5">
+        <v>46268</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E333" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F333" s="1">
+        <v>100</v>
+      </c>
+      <c r="G333" s="6">
+        <v>1</v>
+      </c>
+      <c r="H333" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I333" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -10032,15 +10383,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324C68B5-B5AE-49F4-BF99-B0AAB6EC270F}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -10057,7 +10408,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -10074,7 +10425,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -10091,7 +10442,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -10108,7 +10459,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -10125,7 +10476,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -10142,7 +10493,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -10159,7 +10510,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -10176,7 +10527,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -10193,7 +10544,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -10210,7 +10561,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -10227,7 +10578,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -10244,7 +10595,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -10261,7 +10612,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -10278,7 +10629,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -10295,7 +10646,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -10312,7 +10663,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -10329,7 +10680,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -10346,7 +10697,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -10363,7 +10714,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -10380,7 +10731,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -10658,15 +11009,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
@@ -10677,6 +11019,15 @@
     <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10699,26 +11050,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45088FF4-E0E5-4D94-9D28-A8D4627474EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D40477-0DE8-4624-8F95-684C536B9D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3570" yWindow="450" windowWidth="26280" windowHeight="19800" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="30" yWindow="0" windowWidth="33540" windowHeight="20340" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="66">
   <si>
     <t>AssociateName</t>
   </si>
@@ -241,7 +241,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,6 +260,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,7 +292,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -301,9 +307,9 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -349,8 +355,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I333" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I333" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I335" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I335" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I196">
     <sortCondition ref="C1:C196"/>
   </sortState>
@@ -700,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I333"/>
+  <dimension ref="A1:I335"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -10042,7 +10048,7 @@
       <c r="F322" s="1">
         <v>100</v>
       </c>
-      <c r="G322" s="6">
+      <c r="G322" s="2">
         <v>1</v>
       </c>
       <c r="H322" s="1" t="s">
@@ -10071,7 +10077,7 @@
       <c r="F323" s="1">
         <v>85</v>
       </c>
-      <c r="G323" s="6">
+      <c r="G323" s="2">
         <v>0.85</v>
       </c>
       <c r="H323" s="1" t="s">
@@ -10100,7 +10106,7 @@
       <c r="F324" s="1">
         <v>0</v>
       </c>
-      <c r="G324" s="6">
+      <c r="G324" s="2">
         <v>0</v>
       </c>
       <c r="H324" s="1" t="s">
@@ -10129,7 +10135,7 @@
       <c r="F325" s="1">
         <v>100</v>
       </c>
-      <c r="G325" s="6">
+      <c r="G325" s="2">
         <v>1</v>
       </c>
       <c r="H325" s="1" t="s">
@@ -10158,7 +10164,7 @@
       <c r="F326" s="1">
         <v>100</v>
       </c>
-      <c r="G326" s="6">
+      <c r="G326" s="2">
         <v>1</v>
       </c>
       <c r="H326" s="1" t="s">
@@ -10187,7 +10193,7 @@
       <c r="F327" s="1">
         <v>95</v>
       </c>
-      <c r="G327" s="6">
+      <c r="G327" s="2">
         <v>0.95</v>
       </c>
       <c r="H327" s="1" t="s">
@@ -10216,7 +10222,7 @@
       <c r="F328" s="1">
         <v>0</v>
       </c>
-      <c r="G328" s="6">
+      <c r="G328" s="2">
         <v>0</v>
       </c>
       <c r="H328" s="1" t="s">
@@ -10245,7 +10251,7 @@
       <c r="F329" s="1">
         <v>100</v>
       </c>
-      <c r="G329" s="6">
+      <c r="G329" s="2">
         <v>1</v>
       </c>
       <c r="H329" s="1" t="s">
@@ -10274,7 +10280,7 @@
       <c r="F330" s="1">
         <v>100</v>
       </c>
-      <c r="G330" s="6">
+      <c r="G330" s="2">
         <v>1</v>
       </c>
       <c r="H330" s="1" t="s">
@@ -10303,7 +10309,7 @@
       <c r="F331" s="1">
         <v>95</v>
       </c>
-      <c r="G331" s="6">
+      <c r="G331" s="2">
         <v>0.95</v>
       </c>
       <c r="H331" s="1" t="s">
@@ -10332,7 +10338,7 @@
       <c r="F332" s="1">
         <v>100</v>
       </c>
-      <c r="G332" s="6">
+      <c r="G332" s="2">
         <v>1</v>
       </c>
       <c r="H332" s="1" t="s">
@@ -10361,7 +10367,7 @@
       <c r="F333" s="1">
         <v>100</v>
       </c>
-      <c r="G333" s="6">
+      <c r="G333" s="2">
         <v>1</v>
       </c>
       <c r="H333" s="1" t="s">
@@ -10371,7 +10377,66 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>15</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C334" s="7">
+        <v>46267</v>
+      </c>
+      <c r="D334" t="s">
+        <v>11</v>
+      </c>
+      <c r="E334" t="s">
+        <v>12</v>
+      </c>
+      <c r="F334" s="8">
+        <v>90</v>
+      </c>
+      <c r="G334" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="H334" t="s">
+        <v>65</v>
+      </c>
+      <c r="I334" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>9</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C335" s="7">
+        <v>46268</v>
+      </c>
+      <c r="D335" t="s">
+        <v>11</v>
+      </c>
+      <c r="E335" t="s">
+        <v>12</v>
+      </c>
+      <c r="F335" s="8">
+        <v>100</v>
+      </c>
+      <c r="G335" s="6">
+        <v>1</v>
+      </c>
+      <c r="H335" t="s">
+        <v>65</v>
+      </c>
+      <c r="I335" s="1">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
@@ -11009,6 +11074,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
@@ -11019,15 +11093,6 @@
     <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11050,6 +11115,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -11066,14 +11139,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{4360c1e8-deec-49bb-904e-9331088b2a03}" enabled="0" method="" siteId="{4360c1e8-deec-49bb-904e-9331088b2a03}" removed="1"/>
